--- a/tame_output/ON/bt/strategyON_20240616.xlsx
+++ b/tame_output/ON/bt/strategyON_20240616.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,22 +859,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.8%</t>
+          <t>106.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.3%</t>
+          <t>124.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.1%</t>
+          <t>448.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-639.8%</t>
+          <t>-639.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-251.2%</t>
+          <t>-251.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-198.3%</t>
+          <t>-200.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-208.7%</t>
+          <t>-191.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-120.5%</t>
+          <t>-110.0%</t>
         </is>
       </c>
     </row>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.450567108723414</v>
+        <v>-6.575493967706704</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.376220170284252</v>
+        <v>0.3262494266909362</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.271721300608377</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.274675016255982</v>
+        <v>-6.399601875239272</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4501761307918737</v>
+        <v>0.4002053871985574</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.271721300608377</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.103228553233518</v>
+        <v>-6.228155412216808</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5320822220554127</v>
+        <v>0.4821114784620968</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.100274837585914</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.878195553564695</v>
+        <v>-6.003122412547985</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6211158995392387</v>
+        <v>0.5711451559459229</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8752418379170909</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.814559811330761</v>
+        <v>-5.939486670314051</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6512649974871301</v>
+        <v>0.6012942538938137</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8116060956831563</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.770797630024919</v>
+        <v>-5.895724489008209</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.649964128793262</v>
+        <v>0.5999933851999462</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8116060956831563</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.530367133220059</v>
+        <v>-5.655293992203349</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7478794041400838</v>
+        <v>0.6979086605467675</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5711755988782961</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.458124565048864</v>
+        <v>-5.583051424032154</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7807057452433819</v>
+        <v>0.7307350016500656</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5711755988782961</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.405126242767476</v>
+        <v>-5.530053101750767</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.802583658073277</v>
+        <v>0.7526129144799607</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.5158393398763572</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.296321357287749</v>
+        <v>-5.42124821627104</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8431036834851611</v>
+        <v>0.7931329398918452</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.5158393398763572</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.076300559250739</v>
+        <v>-5.201227418234029</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9326910397105794</v>
+        <v>0.8827202961172635</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.374619494808377</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.943432870187461</v>
+        <v>-5.068359729170751</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.001732298137714</v>
+        <v>0.9517615545443978</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.374619494808377</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.823259786822963</v>
+        <v>-4.948186645806253</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.050947375923815</v>
+        <v>1.000976632330499</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.254446411443878</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.678587641723225</v>
+        <v>-4.803514500706515</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.11890433652515</v>
+        <v>1.068933592931834</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.1097742663441406</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.738462469080917</v>
+        <v>-4.863389328064208</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.080991896983499</v>
+        <v>1.031021153390183</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.1696490937018327</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.651662971301908</v>
+        <v>-4.776589830285198</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.138112189417669</v>
+        <v>1.088141445824353</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.1696490937018327</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.654132677763714</v>
+        <v>-4.779059536747004</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.137196708206359</v>
+        <v>1.087225964613042</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1721188001636389</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.722502864087724</v>
+        <v>-4.847429723071015</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.120855556151457</v>
+        <v>1.07088481255814</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.162843101127424</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.831041045003858</v>
+        <v>-4.955967903987148</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.067876992416894</v>
+        <v>1.017906248823578</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.162843101127424</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.862034204332564</v>
+        <v>-4.986961063315854</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8801892937257989</v>
+        <v>0.8302185501324828</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.162843101127424</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.686559944540095</v>
+        <v>-4.811486803523385</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9549462296345741</v>
+        <v>0.9049754860412582</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.162843101127424</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.797496197181344</v>
+        <v>-4.922423056164634</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8863137573392816</v>
+        <v>0.8363430137459655</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.162843101127424</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.805778271326402</v>
+        <v>-4.930705130309692</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8861323129011638</v>
+        <v>0.8361615693078477</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1711251752724823</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.745925652122679</v>
+        <v>-4.870852511105969</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9202457470147856</v>
+        <v>0.8702750034214695</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1711251752724823</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.659682189096301</v>
+        <v>-4.784609048079592</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9496894027991969</v>
+        <v>0.8997186592058808</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1711251752724823</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.704989008495281</v>
+        <v>-4.829915867478571</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9233424504841306</v>
+        <v>0.8733717068908144</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2119353382817131</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.734022113197582</v>
+        <v>-4.858948972180873</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9122810816363116</v>
+        <v>0.8623103380429955</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2119353382817131</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.641211631746723</v>
+        <v>-4.766138490730013</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8786779661080211</v>
+        <v>0.828707222514705</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1191248568308538</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.68560110107615</v>
+        <v>-4.81052796005944</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.862795654300851</v>
+        <v>0.8128249107075349</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1635143261602814</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.5729298828399</v>
+        <v>-4.69785674182319</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.902939850107074</v>
+        <v>0.8529691065137579</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.05084310792403124</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.460552881657227</v>
+        <v>-4.585479740640517</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9533819464108104</v>
+        <v>0.9034112028174943</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.05084310792403124</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.48833327955858</v>
+        <v>-4.61326013854187</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9537669890188085</v>
+        <v>0.9037962454254924</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.0786235058253843</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.571334560583859</v>
+        <v>-4.696261419567149</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7589221966093502</v>
+        <v>0.7089514530160341</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.09719439035255806</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.67994863902719</v>
+        <v>-4.80487549801048</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8356262259512233</v>
+        <v>0.7856554823579072</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.09719439035255806</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.766547222008293</v>
+        <v>-4.891474080991583</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8154998188611051</v>
+        <v>0.765529075267789</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.09719439035255806</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.728163559450142</v>
+        <v>-4.853090418433432</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8282727252267343</v>
+        <v>0.7783019816334182</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.05881072779440688</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.551047229414976</v>
+        <v>-4.675974088398266</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8958482860861026</v>
+        <v>0.8458775424927865</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.05881072779440688</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.596139474248521</v>
+        <v>-4.721066333231811</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8784947799145975</v>
+        <v>0.8285240363212814</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.1207067709637967</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.416764053009754</v>
+        <v>-4.541690911993044</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9440319237165189</v>
+        <v>0.8940611801232028</v>
       </c>
       <c r="F1957" t="n">
         <v>0.03606998720692201</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.461778266530359</v>
+        <v>-4.58670512551365</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9068336936398662</v>
+        <v>0.8568629500465503</v>
       </c>
       <c r="F1958" t="n">
         <v>0.005721091892317398</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.728782776802794</v>
+        <v>-4.853709635786084</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.805723451869838</v>
+        <v>0.7557527082765221</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1886419461506312</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.829980558239967</v>
+        <v>-4.954907417223257</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7644482611914705</v>
+        <v>0.7144775175981544</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2570507596959504</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.797504972069195</v>
+        <v>-4.922431831052485</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.775038457214096</v>
+        <v>0.7250677136207799</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2570507596959504</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.778466844361898</v>
+        <v>-4.903393703345188</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7791784275052598</v>
+        <v>0.7292076839119437</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3152343710271449</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.809593475512516</v>
+        <v>-4.934520334495806</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9443096439836931</v>
+        <v>0.894338900390377</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3152343710271449</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.823460236846434</v>
+        <v>-4.948387095829724</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9395962684362593</v>
+        <v>0.8896255248429434</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.3530922877609678</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.843717535375392</v>
+        <v>-4.968644394358682</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9375018794216021</v>
+        <v>0.887531135828286</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.3530922877609678</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.695974565140389</v>
+        <v>-4.820901424123679</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.075751715307625</v>
+        <v>1.025780971714309</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.1852849305260847</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.797989247671611</v>
+        <v>-4.922916106654901</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.037739463826618</v>
+        <v>0.9877687202333014</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.1852849305260847</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.791836541618826</v>
+        <v>-4.916763400602116</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.04086289463939</v>
+        <v>0.9908921510460735</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.1791322244733004</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.808645839769328</v>
+        <v>-4.933572698752618</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.033219652119299</v>
+        <v>0.983248908525983</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.195941522623802</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.746347840993206</v>
+        <v>-4.871274699976496</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.124474405426569</v>
+        <v>1.074503661833253</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.195941522623802</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.544557643328048</v>
+        <v>-4.669484502311338</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9137713568820303</v>
+        <v>0.8638006132887142</v>
       </c>
       <c r="F1971" t="n">
         <v>0.00207666954535235</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.484666961685455</v>
+        <v>-4.609593820668745</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.008017861861243</v>
+        <v>0.9580471182679267</v>
       </c>
       <c r="F1972" t="n">
         <v>0.06196735118794583</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.582407506310429</v>
+        <v>-4.707334365293719</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9835493801272965</v>
+        <v>0.9335786365339804</v>
       </c>
       <c r="F1973" t="n">
         <v>0.04607807305496564</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.758745266433358</v>
+        <v>-4.883672125416648</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9115502569027965</v>
+        <v>0.8615795133094806</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.1302596870679638</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.687198943656481</v>
+        <v>-4.812125802639772</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9386604040534758</v>
+        <v>0.8886896604601597</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.1302596870679638</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.642825812017913</v>
+        <v>-4.767752671001203</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9562725241443395</v>
+        <v>0.9063017805510234</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.08588655542939516</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.63487184172314</v>
+        <v>-4.759798700706431</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9594541122622484</v>
+        <v>0.9094833686689323</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.08588655542939516</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.587216111162085</v>
+        <v>-4.712142970145375</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9848981615144754</v>
+        <v>0.9349274179211593</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.03823082486833951</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.459531801367788</v>
+        <v>-4.584458660351078</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.040864258806919</v>
+        <v>0.9908935152136027</v>
       </c>
       <c r="F1979" t="n">
         <v>0.08945348492595695</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.520198391770178</v>
+        <v>-4.645125250753468</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.003352295121835</v>
+        <v>0.9533815515285191</v>
       </c>
       <c r="F1980" t="n">
         <v>0.00775516820742328</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.475359990161779</v>
+        <v>-4.600286849145069</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.025385358375823</v>
+        <v>0.9754146147825071</v>
       </c>
       <c r="F1981" t="n">
         <v>0.01229860115229275</v>
@@ -47137,10 +47137,10 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.576118625918777</v>
+        <v>-4.701045484902068</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9892428437041019</v>
+        <v>0.9392721001107858</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.07652696757471267</v>
@@ -47160,10 +47160,10 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.531915788832877</v>
+        <v>-4.656842647816167</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.012803581066299</v>
+        <v>0.9628328374729831</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.03232413048881222</v>
@@ -47183,10 +47183,10 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.56889481649632</v>
+        <v>-4.69382167547961</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9964219704701698</v>
+        <v>0.9464512268768537</v>
       </c>
       <c r="F1984" t="n">
         <v>0.004649771302518313</v>
@@ -47206,10 +47206,10 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.58895289536116</v>
+        <v>-4.71387975434445</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.039646504107273</v>
+        <v>0.989675760513957</v>
       </c>
       <c r="F1985" t="n">
         <v>0.004649771302518313</v>
@@ -47229,10 +47229,10 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.54902222218327</v>
+        <v>-4.67394908116656</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.054059477972682</v>
+        <v>1.004088734379366</v>
       </c>
       <c r="F1986" t="n">
         <v>0.04458044448040865</v>
@@ -47252,10 +47252,10 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.508551874620565</v>
+        <v>-4.633478733603855</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.065195845236034</v>
+        <v>1.015225101642718</v>
       </c>
       <c r="F1987" t="n">
         <v>0.08505079204311361</v>
@@ -47275,10 +47275,10 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.44332769349336</v>
+        <v>-4.56825455247665</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.108472921779621</v>
+        <v>1.058502178186305</v>
       </c>
       <c r="F1988" t="n">
         <v>0.1502749731703192</v>
@@ -47298,10 +47298,10 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.493821983850416</v>
+        <v>-4.618748842833706</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.084236177936079</v>
+        <v>1.034265434342763</v>
       </c>
       <c r="F1989" t="n">
         <v>0.105254236044245</v>
@@ -47321,10 +47321,10 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.513933639885124</v>
+        <v>-4.638860498868414</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.077448307853436</v>
+        <v>1.02747756426012</v>
       </c>
       <c r="F1990" t="n">
         <v>0.1162815810416642</v>
@@ -47344,10 +47344,10 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.61161421915777</v>
+        <v>-4.736541078141061</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.198933847165589</v>
+        <v>1.148963103572272</v>
       </c>
       <c r="F1991" t="n">
         <v>0.005578385701475397</v>
@@ -47367,10 +47367,10 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.587822650551628</v>
+        <v>-4.712749509534918</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.328563383825863</v>
+        <v>1.278592640232547</v>
       </c>
       <c r="F1992" t="n">
         <v>0.02936995430761768</v>
@@ -47390,10 +47390,10 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.62457706911335</v>
+        <v>-4.74950392809664</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.305569592415033</v>
+        <v>1.255598848821717</v>
       </c>
       <c r="F1993" t="n">
         <v>0.02936995430761768</v>
@@ -47413,10 +47413,10 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.620242766056302</v>
+        <v>-4.745169625039592</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.305496509221632</v>
+        <v>1.255525765628315</v>
       </c>
       <c r="F1994" t="n">
         <v>0.1810200576268216</v>
@@ -47436,10 +47436,10 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.611350304663019</v>
+        <v>-4.736277163646309</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.326607899505736</v>
+        <v>1.27663715591242</v>
       </c>
       <c r="F1995" t="n">
         <v>0.1810200576268216</v>
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.850356481698367</v>
+        <v>3.425497798297196</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.7819765324637</v>
+        <v>-4.776748709054319</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.250212455790048</v>
+        <v>1.2523035851538</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1527334864358583</v>
+        <v>0.3279202940093175</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.25499958495079</v>
+        <v>3.360111669494866</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240616.xlsx
+++ b/tame_output/ON/bt/strategyON_20240616.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>47.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.2%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.9%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-692.6%</t>
+          <t>-695.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.5%</t>
+          <t>451.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-639.2%</t>
+          <t>-642.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.4%</t>
+          <t>-278.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-41.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-251.0%</t>
+          <t>-252.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-21.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.1%</t>
+          <t>-308.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-200.8%</t>
+          <t>-185.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-191.2%</t>
+          <t>-211.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.1%</t>
+          <t>-185.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-110.0%</t>
+          <t>-122.2%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.074651412279923</v>
+        <v>-2.102445317345793</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.286703278216148</v>
+        <v>2.2755857161898</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6699985588688046</v>
+        <v>0.6422046538029349</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.518919402763148</v>
+        <v>3.502243059723626</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.440720139424576</v>
+        <v>-2.468514044490445</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.133360086664736</v>
+        <v>2.122242524638388</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3039298317241519</v>
+        <v>0.2761359266582822</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.292362465782805</v>
+        <v>3.275686122743283</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.649210920876261</v>
+        <v>-2.67700482594213</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.07030206382283</v>
+        <v>2.059184501796483</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.09543905027246746</v>
+        <v>0.06764514520659781</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.187606286650563</v>
+        <v>3.170929943611041</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.896412105641482</v>
+        <v>-2.924206010707351</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.97952034032531</v>
+        <v>1.968402778298962</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1155924037712799</v>
+        <v>0.08779849870541023</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.207797049158418</v>
+        <v>3.191120706118897</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.388797133665579</v>
+        <v>-3.416591038731448</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.783672721159404</v>
+        <v>1.772555159133056</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3767926242528168</v>
+        <v>-0.4045865293186865</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.913472424387693</v>
+        <v>2.896796081348171</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.773977524595651</v>
+        <v>-3.801771429661521</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.628143103600238</v>
+        <v>1.61702554157389</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3767926242528168</v>
+        <v>-0.4045865293186865</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.912014963200556</v>
+        <v>2.895338620161034</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.117660297822314</v>
+        <v>-4.145454202888184</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.492439117764189</v>
+        <v>1.481321555737841</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.484698676280035</v>
+        <v>-0.5124925813459047</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.849040455438841</v>
+        <v>2.83236411239932</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.324172074709336</v>
+        <v>-4.351965979775205</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.405940465665638</v>
+        <v>1.394822903639291</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6912104531670565</v>
+        <v>-0.7190043582329262</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.721239447962886</v>
+        <v>2.704563104923364</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.643516149789837</v>
+        <v>-4.671310054855707</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.279975762333697</v>
+        <v>1.268858200307349</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6912104531670565</v>
+        <v>-0.7190043582329262</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.723012374663146</v>
+        <v>2.706336031623624</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.075321942939625</v>
+        <v>-5.103115848005494</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.093586332541187</v>
+        <v>1.082468770514839</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8276279496083235</v>
+        <v>-0.8554218546741932</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.62749476426579</v>
+        <v>2.610818421226268</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.310015937072177</v>
+        <v>-5.337809842138046</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9879935098902566</v>
+        <v>0.9768759478639089</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8212916823790684</v>
+        <v>-0.849085587444938</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.619581299605434</v>
+        <v>2.602904956565912</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.64567858430263</v>
+        <v>-5.673472489368499</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8523090426540407</v>
+        <v>0.841191480627693</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8212916823790684</v>
+        <v>-0.849085587444938</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.618161891261399</v>
+        <v>2.601485548221877</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.009304829202943</v>
+        <v>-6.037098734268812</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7133461049281569</v>
+        <v>0.7022285429018091</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9195133192461942</v>
+        <v>-0.9473072243120638</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.565716469375365</v>
+        <v>2.549040126335843</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.37443221184169</v>
+        <v>-6.402226116907559</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5665496668784895</v>
+        <v>0.5554321048521418</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.215824103545207</v>
+        <v>-1.243618008611076</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.387184513801789</v>
+        <v>2.370508170762267</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.783020989022368</v>
+        <v>-6.810814894088237</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4018757000209767</v>
+        <v>0.3907581379946294</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.652206785791755</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.140792791508141</v>
+        <v>2.124116448468619</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.059597089338201</v>
+        <v>-7.087390994404069</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2864306923661046</v>
+        <v>0.2753131303397574</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.652206785791755</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.135978223979602</v>
+        <v>2.11930188094008</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.475988963625198</v>
+        <v>-7.503782868691067</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1178679932601829</v>
+        <v>0.1067504312338357</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.652206785791755</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.133972274588479</v>
+        <v>2.117295931548957</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.746755052717844</v>
+        <v>-7.774548957783712</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.01982024829180373</v>
+        <v>0.00870268626545645</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.652206785791755</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.144230965257158</v>
+        <v>2.127554622217636</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.092629874702652</v>
+        <v>-8.120423779768521</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1224301153564245</v>
+        <v>-0.1335476773827717</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.652206785791755</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.140330530402853</v>
+        <v>2.123654187363331</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.256209752887036</v>
+        <v>-8.284003657952905</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1894571465751773</v>
+        <v>-0.2005747086015246</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.652206785791755</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.138735450457854</v>
+        <v>2.122059107418332</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.552871094697235</v>
+        <v>-8.580664999763103</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3043427073700484</v>
+        <v>-0.3154602693963957</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.720949921525633</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.101268544946735</v>
+        <v>2.084592201907213</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.739590803006537</v>
+        <v>-8.767384708072406</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3830568952281723</v>
+        <v>-0.39417445725452</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.720949921525633</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.097242240412332</v>
+        <v>2.08056589737281</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.122592191749169</v>
+        <v>-9.150386096815037</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5363595520468092</v>
+        <v>-0.5474771140731565</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.720949921525633</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.097140139090748</v>
+        <v>2.080463796051226</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.304461982734203</v>
+        <v>-9.332255887800072</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6065359524693927</v>
+        <v>-0.61765351449574</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.902819712510669</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.990589780471157</v>
+        <v>1.973913437431635</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.663992305238205</v>
+        <v>-9.691786210304073</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7449977781729431</v>
+        <v>-0.7561153401992904</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.902819712510669</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.995940083769207</v>
+        <v>1.979263740729685</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.714341368692427</v>
+        <v>-9.742135273758295</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7572213835974546</v>
+        <v>-0.7683389456238019</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.925374870899021</v>
+        <v>-1.953168775964891</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.973646665653852</v>
+        <v>1.95697032261433</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.811960646113823</v>
+        <v>-9.839754551179691</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7932273439442441</v>
+        <v>-0.8043449059705914</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.022994148320417</v>
+        <v>-2.050788053386287</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.918116849822782</v>
+        <v>1.90144050678326</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.959486734119466</v>
+        <v>-9.987280639185334</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8493442228249291</v>
+        <v>-0.8604617848512763</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.170520236326061</v>
+        <v>-2.19831414139193</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.832494753340968</v>
+        <v>1.815818410301447</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16374490944933</v>
+        <v>-10.1915388145152</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.925534295838232</v>
+        <v>-0.9366518578645797</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.29815918094005</v>
+        <v>-2.325953086005919</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.761424583691217</v>
+        <v>1.744748240651696</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.23807788570949</v>
+        <v>-10.26587179077536</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9507849318578621</v>
+        <v>-0.9619024938842089</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.442858704874723</v>
+        <v>-2.470652609940592</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.67908742381485</v>
+        <v>1.662411080775328</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.16460805404204</v>
+        <v>-10.19240195910791</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.906025297697461</v>
+        <v>-0.9171428597238087</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.369388873207274</v>
+        <v>-2.397182778273144</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.73854102430874</v>
+        <v>1.721864681269218</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.33973247142859</v>
+        <v>-10.36752637649446</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9615198439045614</v>
+        <v>-0.9726374059309091</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.544513290593818</v>
+        <v>-2.572307195659687</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.64802159462433</v>
+        <v>1.631345251584809</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.57418456544308</v>
+        <v>-10.60197847050895</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.062519846411953</v>
+        <v>-1.073637408438301</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.544513290593818</v>
+        <v>-2.572307195659687</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.640802429722734</v>
+        <v>1.624126086683213</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.67855929646952</v>
+        <v>-10.70635320153539</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.110941929596508</v>
+        <v>-1.122059491622856</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.648888021620264</v>
+        <v>-2.676681926686133</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.571505400332891</v>
+        <v>1.554829057293369</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.73134545206985</v>
+        <v>-10.75913935713572</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.130940601998082</v>
+        <v>-1.14205816402443</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.744563508202661</v>
+        <v>-2.77235741326853</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.515215898222009</v>
+        <v>1.498539555182487</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.85738224543814</v>
+        <v>-10.88517615050401</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.178661590716283</v>
+        <v>-1.189779152742631</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.719311885392918</v>
+        <v>-2.747105790458788</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.533060600536969</v>
+        <v>1.516384257497448</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.80536673146933</v>
+        <v>-10.8331606365352</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.153865049442357</v>
+        <v>-1.164982611468705</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.719311885392918</v>
+        <v>-2.747105790458788</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.53705093622337</v>
+        <v>1.520374593183848</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.94703857319345</v>
+        <v>-10.97483247825932</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.212009013030747</v>
+        <v>-1.223126575057095</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.719311885392918</v>
+        <v>-2.747105790458788</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.535575709324628</v>
+        <v>1.518899366285107</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.89744772876861</v>
+        <v>-10.92524163383448</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.177119265095941</v>
+        <v>-1.188236827122289</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.669721040968084</v>
+        <v>-2.697514946033954</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.580383626144401</v>
+        <v>1.563707283104879</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.88464033576384</v>
+        <v>-10.91243424082971</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.185047441540715</v>
+        <v>-1.196165003567062</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.718576815976986</v>
+        <v>-2.746370721042855</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.538019027492377</v>
+        <v>1.521342684452855</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.65879518304443</v>
+        <v>-10.6865890881103</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.085130307416742</v>
+        <v>-1.096247869443089</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.676650140389822</v>
+        <v>-2.704444045455691</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.572754105880884</v>
+        <v>1.556077762841362</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.53421652670684</v>
+        <v>-10.5620104317727</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.034159700325647</v>
+        <v>-1.045277262351993</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.676650140389822</v>
+        <v>-2.704444045455691</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.573893250436943</v>
+        <v>1.557216907397421</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.58711181475112</v>
+        <v>-10.61490571981699</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.052684041381253</v>
+        <v>-1.0638016034076</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.671694794301376</v>
+        <v>-2.699488699367245</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.579500232252118</v>
+        <v>1.562823889212597</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.51497863946324</v>
+        <v>-10.54277254452911</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.018097067027464</v>
+        <v>-1.029214629053811</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.671694794301376</v>
+        <v>-2.699488699367245</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.585233936490755</v>
+        <v>1.568557593451233</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.4436122468536</v>
+        <v>-10.47140615191946</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9992877723774711</v>
+        <v>-1.010405334403817</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.600328401691728</v>
+        <v>-2.628122306757597</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.618316509662678</v>
+        <v>1.601640166623157</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17977537964953</v>
+        <v>-10.20756928471539</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9036365068087506</v>
+        <v>-0.9147540688350975</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.600328401691728</v>
+        <v>-2.628122306757597</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.608433028349771</v>
+        <v>1.591756685310249</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.912533578781128</v>
+        <v>-9.940327483846994</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7985743469607649</v>
+        <v>-0.8096919089871117</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.600328401691728</v>
+        <v>-2.628122306757597</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.606598467850397</v>
+        <v>1.589922124810875</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.814626540104637</v>
+        <v>-9.842420445170504</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7597118464636297</v>
+        <v>-0.7708294084899765</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.532342651831171</v>
+        <v>-2.56013655689704</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.64708960279327</v>
+        <v>1.630413259753749</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.790672999128679</v>
+        <v>-9.818466904194546</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7494619239277527</v>
+        <v>-0.7605794859540995</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.508389110855214</v>
+        <v>-2.536183015921083</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.662130233524338</v>
+        <v>1.645453890484817</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.526613060805882</v>
+        <v>-9.554406965871749</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6570982647603865</v>
+        <v>-0.6682158267867329</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.244329172532418</v>
+        <v>-2.272123077598287</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.807305880356264</v>
+        <v>1.790629537316742</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.819533437301045</v>
+        <v>-8.847327342366912</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.377053449018752</v>
+        <v>-0.3881710110450989</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.244329172532418</v>
+        <v>-2.272123077598287</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.804518846695963</v>
+        <v>1.787842503656441</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.779349138934855</v>
+        <v>-8.807143044000721</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3606361057844345</v>
+        <v>-0.3717536678107813</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.204144874166227</v>
+        <v>-2.231938779232096</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.828973049603519</v>
+        <v>1.812296706563997</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.615949267995493</v>
+        <v>-8.64374317306136</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.295909336187933</v>
+        <v>-0.3070268982142799</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.040745003226864</v>
+        <v>-2.068538908292734</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.926379793387893</v>
+        <v>1.909703450348372</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.382468045765894</v>
+        <v>-8.41026195083176</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.194592418458241</v>
+        <v>-0.2057099804845874</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.807263780997266</v>
+        <v>-1.835057686063135</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.074392955563504</v>
+        <v>2.057716612523983</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.232801654758379</v>
+        <v>-8.260595559824246</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1376180723681943</v>
+        <v>-0.1487356343945412</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.71436028975473</v>
+        <v>-1.742154194820599</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.127242839996067</v>
+        <v>2.110566496956546</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.100526181127492</v>
+        <v>-8.128320086193359</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.0893403961688124</v>
+        <v>-0.1004579581951592</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.582084816123843</v>
+        <v>-1.609878721189713</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.201975610921626</v>
+        <v>2.185299267882105</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.909926506454339</v>
+        <v>-7.937720411520206</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0102854656119149</v>
+        <v>-0.0214030276382613</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.39148514145069</v>
+        <v>-1.41927904651656</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.319150476413154</v>
+        <v>2.302474133373633</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.660926707770758</v>
+        <v>-7.688720612836625</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1022207950851763</v>
+        <v>0.09110323305882995</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.39148514145069</v>
+        <v>-1.41927904651656</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.332056817636813</v>
+        <v>2.315380474597291</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.766516697543863</v>
+        <v>-7.79431060260973</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.06799113042328386</v>
+        <v>-0.0791086924496307</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.497075131223795</v>
+        <v>-1.524869036289664</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.140726894173732</v>
+        <v>2.12405055113421</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.78525159966246</v>
+        <v>-7.813045504728326</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.02694074939363666</v>
+        <v>-0.03805831141998306</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.502671140883926</v>
+        <v>-1.530465045949795</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.185913630254739</v>
+        <v>2.169237287215218</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.637311558254861</v>
+        <v>-7.665105463320727</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.08764365551876452</v>
+        <v>-0.09876121754511091</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.482350224975368</v>
+        <v>-1.510144130041238</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.078227257111707</v>
+        <v>2.061550914072185</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.584342036000872</v>
+        <v>-7.612135941066739</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.07516983287064694</v>
+        <v>-0.08628739489699377</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.429380702721379</v>
+        <v>-1.457174607787249</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.101294984210622</v>
+        <v>2.0846186411711</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.540793629230182</v>
+        <v>-7.568587534296048</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.06471108225746391</v>
+        <v>-0.07582864428381075</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.429380702721379</v>
+        <v>-1.457174607787249</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.094334372115529</v>
+        <v>2.077658029076007</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.298645235776323</v>
+        <v>-7.32643914084219</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.04661062950522243</v>
+        <v>0.0354930674788756</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.429380702721379</v>
+        <v>-1.457174607787249</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.108796726496672</v>
+        <v>2.09212038345715</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.190386098653802</v>
+        <v>-7.218180003719668</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.08444640481342613</v>
+        <v>0.0733288427870793</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.429380702721379</v>
+        <v>-1.457174607787249</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.103328846955867</v>
+        <v>2.086652503916345</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.067094963836671</v>
+        <v>-7.094888868902538</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1312609527508553</v>
+        <v>0.1201433907245084</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.306089567904249</v>
+        <v>-1.333883472970118</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.174801621856722</v>
+        <v>2.1581252788172</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.045945764933228</v>
+        <v>-7.073739669999094</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1474216105495576</v>
+        <v>0.1363040485232112</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.284940369000806</v>
+        <v>-1.312734274066675</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.195192119436113</v>
+        <v>2.178515776396591</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.802180322949783</v>
+        <v>-6.82997422801565</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2407084956899861</v>
+        <v>0.2295909336636393</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.284940369000806</v>
+        <v>-1.312734274066675</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.190972827783164</v>
+        <v>2.174296484743642</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.700417502672488</v>
+        <v>-6.728211407738355</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.28353793772092</v>
+        <v>0.2724203756945736</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.271721300608377</v>
+        <v>-1.299515205674246</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.201028582738637</v>
+        <v>2.184352239699115</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.575493967706704</v>
+        <v>-6.47836101378928</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3262494266909362</v>
+        <v>0.3651026082579052</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.271721300608377</v>
+        <v>-1.299515205674246</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.193770657722339</v>
+        <v>2.177094314682817</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.399601875239272</v>
+        <v>-6.302468921321848</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4002053871985574</v>
+        <v>0.4390585687655268</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.271721300608377</v>
+        <v>-1.299515205674246</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.197369781242988</v>
+        <v>2.180693438203466</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.228155412216808</v>
+        <v>-6.131022458299385</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4821114784620968</v>
+        <v>0.5209646600290658</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.100274837585914</v>
+        <v>-1.128068742651783</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.31356516511102</v>
+        <v>2.296888822071498</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.003122412547985</v>
+        <v>-5.905989458630562</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5711451559459229</v>
+        <v>0.6099983375128923</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8752418379170909</v>
+        <v>-0.9030357429829602</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.44760544252861</v>
+        <v>2.430929099489088</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.939486670314051</v>
+        <v>-5.842353716396627</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6012942538938137</v>
+        <v>0.6401474354607832</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8116060956831563</v>
+        <v>-0.8394000007490257</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.490481688923288</v>
+        <v>2.473805345883767</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.895724489008209</v>
+        <v>-5.798591535090786</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5999933851999462</v>
+        <v>0.6388465667669156</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8116060956831563</v>
+        <v>-0.8394000007490257</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.471675947707084</v>
+        <v>2.454999604667562</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.655293992203349</v>
+        <v>-5.558161038285926</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6979086605467675</v>
+        <v>0.736761842113737</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5711755988782961</v>
+        <v>-0.5989695039441654</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.617677322414877</v>
+        <v>2.601000979375355</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.583051424032154</v>
+        <v>-5.485918470114731</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7307350016500656</v>
+        <v>0.769588183217035</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5711755988782961</v>
+        <v>-0.5989695039441654</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.621606636249697</v>
+        <v>2.604930293210176</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.530053101750767</v>
+        <v>-5.432920147833343</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7526129144799607</v>
+        <v>0.7914660960469302</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5158393398763572</v>
+        <v>-0.5436332449422265</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.655486975568201</v>
+        <v>2.638810632528679</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.42124821627104</v>
+        <v>-5.324115262353616</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7931329398918452</v>
+        <v>0.8319861214588147</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5158393398763572</v>
+        <v>-0.5436332449422265</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.652485046788194</v>
+        <v>2.635808703748673</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.201227418234029</v>
+        <v>-5.104094464316606</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8827202961172635</v>
+        <v>0.921573477684233</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.374619494808377</v>
+        <v>-0.4024133998742463</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.738795990839597</v>
+        <v>2.722119647800075</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.068359729170751</v>
+        <v>-4.971226775253328</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9517615545443978</v>
+        <v>0.9906147361113673</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.374619494808377</v>
+        <v>-0.4024133998742463</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.75469017364142</v>
+        <v>2.738013830601898</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.948186645806253</v>
+        <v>-4.851053691888829</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.000976632330499</v>
+        <v>1.039829813897469</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.254446411443878</v>
+        <v>-0.2822403165097473</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.827939868100421</v>
+        <v>2.811263525060899</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.803514500706515</v>
+        <v>-4.706381546789092</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.068933592931834</v>
+        <v>1.107786774498803</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1097742663441406</v>
+        <v>-0.1375681714100099</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.924831257721703</v>
+        <v>2.908154914682182</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.863389328064208</v>
+        <v>-4.766256374146784</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.031021153390183</v>
+        <v>1.069874334957152</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1696490937018327</v>
+        <v>-0.197442998767702</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.874943852708514</v>
+        <v>2.858267509668992</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.776589830285198</v>
+        <v>-4.679456876367775</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.088141445824353</v>
+        <v>1.126994627391322</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1696490937018327</v>
+        <v>-0.197442998767702</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.89734434603108</v>
+        <v>2.880668002991559</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.779059536747004</v>
+        <v>-4.681926582829581</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.087225964613042</v>
+        <v>1.126079146180012</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1721188001636389</v>
+        <v>-0.1999127052295082</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.895934923527408</v>
+        <v>2.879258580487887</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.847429723071015</v>
+        <v>-4.750296769153591</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.07088481255814</v>
+        <v>1.10973799412511</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.1906370061932933</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.91250726542384</v>
+        <v>2.895830922384318</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.955967903987148</v>
+        <v>-4.858834950069725</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.017906248823578</v>
+        <v>1.056759430390548</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.1906370061932933</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.902943974055731</v>
+        <v>2.886267631016209</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.986961063315854</v>
+        <v>-4.88982810939843</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8302185501324828</v>
+        <v>0.8690717316994523</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.1906370061932933</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.727653539096118</v>
+        <v>2.710977196056596</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.811486803523385</v>
+        <v>-4.714353849605962</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9049754860412582</v>
+        <v>0.9438286676082275</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.1906370061932933</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.732220771087905</v>
+        <v>2.715544428048384</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.922423056164634</v>
+        <v>-4.825290102247211</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8363430137459655</v>
+        <v>0.875196195312935</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.1906370061932933</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.707962799849112</v>
+        <v>2.691286456809591</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.930705130309692</v>
+        <v>-4.833572176392269</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8361615693078477</v>
+        <v>0.8750147508748172</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1711251752724823</v>
+        <v>-0.1989190803383517</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.706124940581983</v>
+        <v>2.689448597542461</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.870852511105969</v>
+        <v>-4.773719557188546</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8702750034214695</v>
+        <v>0.9091281849884387</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1711251752724823</v>
+        <v>-0.1989190803383517</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.716297327014115</v>
+        <v>2.699620983974594</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.784609048079592</v>
+        <v>-4.687476094162168</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8997186592058808</v>
+        <v>0.9385718407728503</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1711251752724823</v>
+        <v>-0.1989190803383517</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.711243597587976</v>
+        <v>2.694567254548454</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.829915867478571</v>
+        <v>-4.732782913561148</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8733717068908144</v>
+        <v>0.9122248884577839</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2119353382817131</v>
+        <v>-0.2397292433475824</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.678533275226963</v>
+        <v>2.661856932187441</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.858948972180873</v>
+        <v>-4.761816018263449</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8623103380429955</v>
+        <v>0.901163519609965</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2119353382817131</v>
+        <v>-0.2397292433475824</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.679085148260064</v>
+        <v>2.662408805220543</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.766138490730013</v>
+        <v>-4.669005536812589</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.828707222514705</v>
+        <v>0.8675604040816745</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1191248568308538</v>
+        <v>-0.1469187618967231</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.664044129021946</v>
+        <v>2.647367785982424</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.81052796005944</v>
+        <v>-4.713395006142017</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8128249107075349</v>
+        <v>0.8516780922745042</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1635143261602814</v>
+        <v>-0.1913082312261508</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.63928392334889</v>
+        <v>2.622607580309368</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.69785674182319</v>
+        <v>-4.600723787905767</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8529691065137579</v>
+        <v>0.8918222880807274</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.05084310792403124</v>
+        <v>-0.07863701298990056</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.701962362802363</v>
+        <v>2.685286019762841</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.585479740640517</v>
+        <v>-4.488346786723094</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9034112028174943</v>
+        <v>0.9422643843844638</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.05084310792403124</v>
+        <v>-0.07863701298990056</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.70745365863303</v>
+        <v>2.690777315593508</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.61326013854187</v>
+        <v>-4.516127184624446</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9037962454254924</v>
+        <v>0.9426494269924617</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.0786235058253843</v>
+        <v>-0.1064174108912536</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.702282621660757</v>
+        <v>2.685606278621236</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.696261419567149</v>
+        <v>-4.599128465649725</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7089514530160341</v>
+        <v>0.7478046345830034</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.09719439035255806</v>
+        <v>-0.1249882954184274</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.529495810945106</v>
+        <v>2.512819467905585</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.80487549801048</v>
+        <v>-4.707742544093056</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7856554823579072</v>
+        <v>0.8245086639248767</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.09719439035255806</v>
+        <v>-0.1249882954184274</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.649645471664312</v>
+        <v>2.63296912862479</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.891474080991583</v>
+        <v>-4.794341127074159</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.765529075267789</v>
+        <v>0.8043822568347585</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.09719439035255806</v>
+        <v>-0.1249882954184274</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.664158497766635</v>
+        <v>2.647482154727113</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.853090418433432</v>
+        <v>-4.755957464516008</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7783019816334182</v>
+        <v>0.8171551632003875</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.05881072779440688</v>
+        <v>-0.0866046328602762</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.684608136643894</v>
+        <v>2.667931793604373</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.675974088398266</v>
+        <v>-4.578841134480842</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8458775424927865</v>
+        <v>0.8847307240597559</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.05881072779440688</v>
+        <v>-0.0866046328602762</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.681337165489196</v>
+        <v>2.664660822449675</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.721066333231811</v>
+        <v>-4.623933379314388</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8285240363212814</v>
+        <v>0.8673772178882508</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1207067709637967</v>
+        <v>-0.148500676029666</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.644882931349475</v>
+        <v>2.628206588309954</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.541690911993044</v>
+        <v>-4.44455795807562</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8940611801232028</v>
+        <v>0.9329143616901723</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.03606998720692201</v>
+        <v>0.008276082141052687</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.732735961558321</v>
+        <v>2.716059618518799</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.58670512551365</v>
+        <v>-4.489572171596226</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8568629500465503</v>
+        <v>0.8957161316135196</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.005721091892317398</v>
+        <v>-0.02207281317355192</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.695334079701148</v>
+        <v>2.678657736661626</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.853709635786084</v>
+        <v>-4.756576681868661</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7557527082765221</v>
+        <v>0.7946058898434913</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1886419461506312</v>
+        <v>-0.2164358512165005</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.584407819214324</v>
+        <v>2.567731476174803</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.954907417223257</v>
+        <v>-4.857774463305834</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7144775175981544</v>
+        <v>0.7533306991651236</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2570507596959504</v>
+        <v>-0.2848446647618197</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.542566452983634</v>
+        <v>2.525890109944113</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.922431831052485</v>
+        <v>-4.825298877135062</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7250677136207799</v>
+        <v>0.7639208951877494</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2570507596959504</v>
+        <v>-0.2848446647618197</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.540166414537951</v>
+        <v>2.52349007149843</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.903393703345188</v>
+        <v>-4.806260749427764</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7292076839119437</v>
+        <v>0.7680608654789132</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3152343710271449</v>
+        <v>-0.3430282760930142</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.50178096694748</v>
+        <v>2.485104623907958</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.934520334495806</v>
+        <v>-4.837387380578383</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.894338900390377</v>
+        <v>0.9331920819573463</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3152343710271449</v>
+        <v>-0.3430282760930142</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.67936283588616</v>
+        <v>2.662686492846638</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.948387095829724</v>
+        <v>-4.851254141912301</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8896255248429434</v>
+        <v>0.9284787064099127</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3530922877609678</v>
+        <v>-0.3808861928268372</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.657481414832</v>
+        <v>2.640805071792478</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.968644394358682</v>
+        <v>-4.871511440441259</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.887531135828286</v>
+        <v>0.9263843173952555</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3530922877609678</v>
+        <v>-0.3808861928268372</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.663489945228926</v>
+        <v>2.646813602189404</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.820901424123679</v>
+        <v>-4.723768470206256</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.025780971714309</v>
+        <v>1.064634153281278</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1852849305260847</v>
+        <v>-0.213078835591954</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.843327007361878</v>
+        <v>2.826650664322356</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.922916106654901</v>
+        <v>-4.825783152737477</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9877687202333014</v>
+        <v>1.026621901800271</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1852849305260847</v>
+        <v>-0.213078835591954</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.846120628893359</v>
+        <v>2.829444285853837</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.916763400602116</v>
+        <v>-4.819630446684693</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9908921510460735</v>
+        <v>1.029745332613043</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1791322244733004</v>
+        <v>-0.2069261295391697</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.850474600916687</v>
+        <v>2.833798257877166</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.933572698752618</v>
+        <v>-4.836439744835195</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.983248908525983</v>
+        <v>1.022102090092952</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.195941522623802</v>
+        <v>-0.2237354276896714</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.839469498766497</v>
+        <v>2.822793155726975</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.871274699976496</v>
+        <v>-4.774141746059072</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.074503661833253</v>
+        <v>1.113356843400222</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.195941522623802</v>
+        <v>-0.2237354276896714</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.905805052563318</v>
+        <v>2.889128709523796</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.669484502311338</v>
+        <v>-4.572351548393915</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8638006132887142</v>
+        <v>0.9026537948556834</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.00207666954535235</v>
+        <v>-0.02571723552051697</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.733196840254208</v>
+        <v>2.716520497214687</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.609593820668745</v>
+        <v>-4.512460866751321</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9580471182679267</v>
+        <v>0.9969002998348961</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.06196735118794583</v>
+        <v>0.03417344612207651</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.839421481561939</v>
+        <v>2.822745138522418</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.707334365293719</v>
+        <v>-4.610201411376296</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9335786365339804</v>
+        <v>0.9724318181009499</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.04607807305496564</v>
+        <v>0.01828416798909632</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.844515650798195</v>
+        <v>2.827839307758674</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.883672125416648</v>
+        <v>-4.786539171499225</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8615795133094806</v>
+        <v>0.9004326948764498</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1302596870679638</v>
+        <v>-0.1580535921338331</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.737248975549109</v>
+        <v>2.720572632509588</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.812125802639772</v>
+        <v>-4.714992848722348</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8886896604601597</v>
+        <v>0.9275428420271292</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1302596870679638</v>
+        <v>-0.1580535921338331</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.735740593589038</v>
+        <v>2.719064250549516</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.767752671001203</v>
+        <v>-4.670619717083779</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9063017805510234</v>
+        <v>0.9451549621179929</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.08588655542939516</v>
+        <v>-0.1136804604952645</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.762227340007615</v>
+        <v>2.745550996968094</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.759798700706431</v>
+        <v>-4.662665746789007</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9094833686689323</v>
+        <v>0.9483365502359018</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.08588655542939516</v>
+        <v>-0.1136804604952645</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.762227340007615</v>
+        <v>2.745550996968094</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.712142970145375</v>
+        <v>-4.615010016227951</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9349274179211593</v>
+        <v>0.9737805994881288</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.03823082486833951</v>
+        <v>-0.06602472993420883</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.797202535372053</v>
+        <v>2.780526192332531</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.584458660351078</v>
+        <v>-4.487325706433655</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9908935152136027</v>
+        <v>1.029746696780572</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.08945348492595695</v>
+        <v>0.06165957986008763</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.878705494623356</v>
+        <v>2.862029151583834</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.645125250753468</v>
+        <v>-4.547992296836044</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9533815515285191</v>
+        <v>0.9922347330954886</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.00775516820742328</v>
+        <v>-0.02003873685844604</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.816441177068108</v>
+        <v>2.799764834028586</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.600286849145069</v>
+        <v>-4.503153895227646</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9754146147825071</v>
+        <v>1.014267796349476</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.01229860115229275</v>
+        <v>-0.01549530391357656</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.823264939445658</v>
+        <v>2.806588596406137</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.701045484902068</v>
+        <v>-4.603912530984644</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9392721001107858</v>
+        <v>0.9781252816777553</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.07652696757471267</v>
+        <v>-0.104320872640582</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.774130537840533</v>
+        <v>2.757454194801011</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.656842647816167</v>
+        <v>-4.559709693898744</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9628328374729831</v>
+        <v>1.001686019039953</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.03232413048881222</v>
+        <v>-0.06011803555468154</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.80653184261991</v>
+        <v>2.789855499580389</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.69382167547961</v>
+        <v>-4.596688721562186</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9464512268768537</v>
+        <v>0.9853044084438229</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.004649771302518313</v>
+        <v>-0.023144133763351</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.827126184163956</v>
+        <v>2.810449841124434</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.71387975434445</v>
+        <v>-4.616746800427027</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.989675760513957</v>
+        <v>1.028528942080926</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.004649771302518313</v>
+        <v>-0.023144133763351</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.878373949346996</v>
+        <v>2.861697606307474</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.67394908116656</v>
+        <v>-4.576816127249137</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.004088734379366</v>
+        <v>1.042941915946336</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.04458044448040865</v>
+        <v>0.01678653941453934</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.900773057847983</v>
+        <v>2.884096714808461</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.633478733603855</v>
+        <v>-4.536345779686432</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.015225101642718</v>
+        <v>1.054078283209688</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.08505079204311361</v>
+        <v>0.05725688697724429</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.920003494623876</v>
+        <v>2.903327151584354</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.56825455247665</v>
+        <v>-4.471121598559226</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.058502178186305</v>
+        <v>1.097355359753275</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1502749731703192</v>
+        <v>0.1224810681044499</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.976325407392904</v>
+        <v>2.959649064353383</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.618748842833706</v>
+        <v>-4.521615888916283</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.034265434342763</v>
+        <v>1.073118615909733</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.105254236044245</v>
+        <v>0.07746033097837568</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.94527393741654</v>
+        <v>2.928597594377019</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.638860498868414</v>
+        <v>-4.541727544950991</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.02747756426012</v>
+        <v>1.06633074582709</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1162815810416642</v>
+        <v>0.08848767597579488</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.953147136746232</v>
+        <v>2.93647079370671</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.736541078141061</v>
+        <v>-4.639408124223637</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.148963103572272</v>
+        <v>1.187816285139242</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.005578385701475397</v>
+        <v>-0.02221551936439392</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.04728299056333</v>
+        <v>3.030606647523808</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.712749509534918</v>
+        <v>-4.615616555617494</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.278592640232547</v>
+        <v>1.317445821799516</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.02936995430761768</v>
+        <v>0.001576049241748367</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.181670840944832</v>
+        <v>3.16499449790531</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.74950392809664</v>
+        <v>-4.652370974179217</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.255598848821717</v>
+        <v>1.294452030388686</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.02936995430761768</v>
+        <v>0.001576049241748367</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.173378816958691</v>
+        <v>3.156702473919169</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.745169625039592</v>
+        <v>-4.648036671122169</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.255525765628315</v>
+        <v>1.294378947195285</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1810200576268216</v>
+        <v>0.1532261525609523</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.262562074533993</v>
+        <v>3.245885731494471</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.736277163646309</v>
+        <v>-4.639144209728886</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.27663715591242</v>
+        <v>1.315490337479389</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1810200576268216</v>
+        <v>0.1532261525609523</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.280116480260784</v>
+        <v>3.263440137221262</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.425497798297196</v>
+        <v>3.753317901765136</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.776748709054319</v>
+        <v>-4.807620326698763</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.2523035851538</v>
+        <v>1.239954938096022</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3279202940093175</v>
+        <v>0.1252783168443715</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.360111669494866</v>
+        <v>3.238526483195898</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240616.xlsx
+++ b/tame_output/ON/bt/strategyON_20240616.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.5%</t>
+          <t>125.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-695.4%</t>
+          <t>-692.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-51.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.8%</t>
+          <t>453.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-642.3%</t>
+          <t>-636.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-278.5%</t>
+          <t>-277.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>-272.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>109.8%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-252.2%</t>
+          <t>-249.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-308.9%</t>
+          <t>-306.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-185.2%</t>
+          <t>-223.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-211.5%</t>
+          <t>-207.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-185.7%</t>
+          <t>-184.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-122.2%</t>
+          <t>-119.7%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.102445317345793</v>
+        <v>-2.074651412279923</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.2755857161898</v>
+        <v>2.286703278216148</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6422046538029349</v>
+        <v>0.6699985588688046</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.502243059723626</v>
+        <v>3.518919402763148</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.468514044490445</v>
+        <v>-2.440720139424576</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.122242524638388</v>
+        <v>2.133360086664736</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.2761359266582822</v>
+        <v>0.3039298317241519</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.275686122743283</v>
+        <v>3.292362465782805</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.67700482594213</v>
+        <v>-2.649210920876261</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.059184501796483</v>
+        <v>2.07030206382283</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.06764514520659781</v>
+        <v>0.09543905027246746</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.170929943611041</v>
+        <v>3.187606286650563</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.924206010707351</v>
+        <v>-2.896412105641482</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.968402778298962</v>
+        <v>1.97952034032531</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.08779849870541023</v>
+        <v>0.1155924037712799</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.191120706118897</v>
+        <v>3.207797049158418</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.416591038731448</v>
+        <v>-3.388797133665579</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.772555159133056</v>
+        <v>1.783672721159404</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4045865293186865</v>
+        <v>-0.3767926242528168</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.896796081348171</v>
+        <v>2.913472424387693</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.801771429661521</v>
+        <v>-3.773977524595651</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.61702554157389</v>
+        <v>1.628143103600238</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4045865293186865</v>
+        <v>-0.3767926242528168</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.895338620161034</v>
+        <v>2.912014963200556</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.145454202888184</v>
+        <v>-4.117660297822314</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.481321555737841</v>
+        <v>1.492439117764189</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.5124925813459047</v>
+        <v>-0.484698676280035</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.83236411239932</v>
+        <v>2.849040455438841</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.351965979775205</v>
+        <v>-4.324172074709336</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.394822903639291</v>
+        <v>1.405940465665638</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.7190043582329262</v>
+        <v>-0.6912104531670565</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.704563104923364</v>
+        <v>2.721239447962886</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.671310054855707</v>
+        <v>-4.643516149789837</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.268858200307349</v>
+        <v>1.279975762333697</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.7190043582329262</v>
+        <v>-0.6912104531670565</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.706336031623624</v>
+        <v>2.723012374663146</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.103115848005494</v>
+        <v>-5.075321942939625</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.082468770514839</v>
+        <v>1.093586332541187</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8554218546741932</v>
+        <v>-0.8276279496083235</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.610818421226268</v>
+        <v>2.62749476426579</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.337809842138046</v>
+        <v>-5.310015937072177</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9768759478639089</v>
+        <v>0.9879935098902566</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.849085587444938</v>
+        <v>-0.8212916823790684</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.602904956565912</v>
+        <v>2.619581299605434</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.673472489368499</v>
+        <v>-5.64567858430263</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.841191480627693</v>
+        <v>0.8523090426540407</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.849085587444938</v>
+        <v>-0.8212916823790684</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.601485548221877</v>
+        <v>2.618161891261399</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.037098734268812</v>
+        <v>-6.009304829202943</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7022285429018091</v>
+        <v>0.7133461049281569</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9473072243120638</v>
+        <v>-0.9195133192461942</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.549040126335843</v>
+        <v>2.565716469375365</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.402226116907559</v>
+        <v>-6.37443221184169</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5554321048521418</v>
+        <v>0.5665496668784895</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.243618008611076</v>
+        <v>-1.215824103545207</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.370508170762267</v>
+        <v>2.387184513801789</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.810814894088237</v>
+        <v>-6.783020989022368</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3907581379946294</v>
+        <v>0.4018757000209767</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.652206785791755</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.124116448468619</v>
+        <v>2.140792791508141</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.087390994404069</v>
+        <v>-7.059597089338201</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2753131303397574</v>
+        <v>0.2864306923661046</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.652206785791755</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.11930188094008</v>
+        <v>2.135978223979602</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.503782868691067</v>
+        <v>-7.475988963625198</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1067504312338357</v>
+        <v>0.1178679932601829</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.652206785791755</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.117295931548957</v>
+        <v>2.133972274588479</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.774548957783712</v>
+        <v>-7.746755052717844</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.00870268626545645</v>
+        <v>0.01982024829180373</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.652206785791755</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.127554622217636</v>
+        <v>2.144230965257158</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.120423779768521</v>
+        <v>-8.092629874702652</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1335476773827717</v>
+        <v>-0.1224301153564245</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.652206785791755</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.123654187363331</v>
+        <v>2.140330530402853</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.284003657952905</v>
+        <v>-8.256209752887036</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2005747086015246</v>
+        <v>-0.1894571465751773</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.652206785791755</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.122059107418332</v>
+        <v>2.138735450457854</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.580664999763103</v>
+        <v>-8.552871094697235</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3154602693963957</v>
+        <v>-0.3043427073700484</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.720949921525633</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.084592201907213</v>
+        <v>2.101268544946735</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.767384708072406</v>
+        <v>-8.739590803006537</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.39417445725452</v>
+        <v>-0.3830568952281723</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.720949921525633</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.08056589737281</v>
+        <v>2.097242240412332</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.150386096815037</v>
+        <v>-9.122592191749169</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5474771140731565</v>
+        <v>-0.5363595520468092</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.720949921525633</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.080463796051226</v>
+        <v>2.097140139090748</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.332255887800072</v>
+        <v>-9.304461982734203</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.61765351449574</v>
+        <v>-0.6065359524693927</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.902819712510669</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.973913437431635</v>
+        <v>1.990589780471157</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.691786210304073</v>
+        <v>-9.663992305238205</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7561153401992904</v>
+        <v>-0.7449977781729431</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.902819712510669</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.979263740729685</v>
+        <v>1.995940083769207</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.742135273758295</v>
+        <v>-9.714341368692427</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7683389456238019</v>
+        <v>-0.7572213835974546</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.953168775964891</v>
+        <v>-1.925374870899021</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.95697032261433</v>
+        <v>1.973646665653852</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.839754551179691</v>
+        <v>-9.811960646113823</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8043449059705914</v>
+        <v>-0.7932273439442441</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.050788053386287</v>
+        <v>-2.022994148320417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.90144050678326</v>
+        <v>1.918116849822782</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937495</v>
+        <v>3.492448711937496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.987280639185334</v>
+        <v>-9.959486734119466</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8604617848512763</v>
+        <v>-0.8493442228249291</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.19831414139193</v>
+        <v>-2.170520236326061</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.815818410301447</v>
+        <v>1.832494753340968</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.1915388145152</v>
+        <v>-10.16374490944933</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9366518578645797</v>
+        <v>-0.925534295838232</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.325953086005919</v>
+        <v>-2.29815918094005</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.744748240651696</v>
+        <v>1.761424583691217</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729888</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.26587179077536</v>
+        <v>-10.23807788570949</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9619024938842089</v>
+        <v>-0.9507849318578621</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.470652609940592</v>
+        <v>-2.442858704874723</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.662411080775328</v>
+        <v>1.67908742381485</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49997173944063</v>
+        <v>3.499971739440631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.19240195910791</v>
+        <v>-10.16460805404204</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9171428597238087</v>
+        <v>-0.906025297697461</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.397182778273144</v>
+        <v>-2.369388873207274</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.721864681269218</v>
+        <v>1.73854102430874</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608597</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.36752637649446</v>
+        <v>-10.33973247142859</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9726374059309091</v>
+        <v>-0.9615198439045614</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.572307195659687</v>
+        <v>-2.544513290593818</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.631345251584809</v>
+        <v>1.64802159462433</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.60197847050895</v>
+        <v>-10.57418456544308</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.073637408438301</v>
+        <v>-1.062519846411953</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.572307195659687</v>
+        <v>-2.544513290593818</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.624126086683213</v>
+        <v>1.640802429722734</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764393</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.70635320153539</v>
+        <v>-10.67855929646952</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.122059491622856</v>
+        <v>-1.110941929596508</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.676681926686133</v>
+        <v>-2.648888021620264</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.554829057293369</v>
+        <v>1.571505400332891</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.75913935713572</v>
+        <v>-10.73134545206985</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.14205816402443</v>
+        <v>-1.130940601998082</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.77235741326853</v>
+        <v>-2.744563508202661</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.498539555182487</v>
+        <v>1.515215898222009</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.88517615050401</v>
+        <v>-10.85738224543814</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.189779152742631</v>
+        <v>-1.178661590716283</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.747105790458788</v>
+        <v>-2.719311885392918</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.516384257497448</v>
+        <v>1.533060600536969</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367402532254</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.8331606365352</v>
+        <v>-10.80536673146933</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.164982611468705</v>
+        <v>-1.153865049442357</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.747105790458788</v>
+        <v>-2.719311885392918</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.520374593183848</v>
+        <v>1.53705093622337</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158918</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.97483247825932</v>
+        <v>-10.94703857319345</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.223126575057095</v>
+        <v>-1.212009013030747</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.747105790458788</v>
+        <v>-2.719311885392918</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.518899366285107</v>
+        <v>1.535575709324628</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.92524163383448</v>
+        <v>-10.89744772876861</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.188236827122289</v>
+        <v>-1.177119265095941</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.697514946033954</v>
+        <v>-2.669721040968084</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.563707283104879</v>
+        <v>1.580383626144401</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.91243424082971</v>
+        <v>-10.85286134501705</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.196165003567062</v>
+        <v>-1.172335845241998</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.746370721042855</v>
+        <v>-2.706002154065726</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.521342684452855</v>
+        <v>1.545563824639133</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68516138161528</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.6865890881103</v>
+        <v>-10.62701619229763</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.096247869443089</v>
+        <v>-1.072418711118024</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.704444045455691</v>
+        <v>-2.664075478478563</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.556077762841362</v>
+        <v>1.58029890302764</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.5620104317727</v>
+        <v>-10.50243753596004</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.045277262351993</v>
+        <v>-1.021448104026929</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.704444045455691</v>
+        <v>-2.664075478478563</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.557216907397421</v>
+        <v>1.581438047583698</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.61490571981699</v>
+        <v>-10.55533282400433</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.0638016034076</v>
+        <v>-1.039972445082536</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.699488699367245</v>
+        <v>-2.659120132390116</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.562823889212597</v>
+        <v>1.587045029398874</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.54277254452911</v>
+        <v>-10.48319964871645</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.029214629053811</v>
+        <v>-1.005385470728747</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.699488699367245</v>
+        <v>-2.659120132390116</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.568557593451233</v>
+        <v>1.59277873363751</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.47140615191946</v>
+        <v>-10.4118332561068</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.010405334403817</v>
+        <v>-0.9865761760787528</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.628122306757597</v>
+        <v>-2.587753739780469</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.601640166623157</v>
+        <v>1.625861306809434</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.20756928471539</v>
+        <v>-10.14799638890273</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9147540688350975</v>
+        <v>-0.8909249105100332</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.628122306757597</v>
+        <v>-2.587753739780469</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.591756685310249</v>
+        <v>1.615977825496526</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.940327483846994</v>
+        <v>-9.880754588034334</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8096919089871117</v>
+        <v>-0.7858627506620475</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.628122306757597</v>
+        <v>-2.587753739780469</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.589922124810875</v>
+        <v>1.614143264997153</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.842420445170504</v>
+        <v>-9.782847549357843</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7708294084899765</v>
+        <v>-0.7470002501649122</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.56013655689704</v>
+        <v>-2.519767989919912</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.630413259753749</v>
+        <v>1.654634399940025</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.818466904194546</v>
+        <v>-9.758894008381885</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7605794859540995</v>
+        <v>-0.7367503276290353</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.536183015921083</v>
+        <v>-2.495814448943955</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.645453890484817</v>
+        <v>1.669675030671094</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.554406965871749</v>
+        <v>-9.494834070059088</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6682158267867329</v>
+        <v>-0.6443866684616686</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.272123077598287</v>
+        <v>-2.231754510621159</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.790629537316742</v>
+        <v>1.814850677503019</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.847327342366912</v>
+        <v>-8.787754446554251</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3881710110450989</v>
+        <v>-0.3643418527200346</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.272123077598287</v>
+        <v>-2.231754510621159</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.787842503656441</v>
+        <v>1.812063643842718</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.807143044000721</v>
+        <v>-8.747570148188061</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3717536678107813</v>
+        <v>-0.3479245094857171</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.231938779232096</v>
+        <v>-2.191570212254968</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.812296706563997</v>
+        <v>1.836517846750274</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.64374317306136</v>
+        <v>-8.584170277248699</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3070268982142799</v>
+        <v>-0.2831977398892156</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.068538908292734</v>
+        <v>-2.028170341315605</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.909703450348372</v>
+        <v>1.933924590534648</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.41026195083176</v>
+        <v>-8.3506890550191</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2057099804845874</v>
+        <v>-0.1818808221595232</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.835057686063135</v>
+        <v>-1.794689119086007</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.057716612523983</v>
+        <v>2.08193775271026</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.260595559824246</v>
+        <v>-8.201022664011585</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1487356343945412</v>
+        <v>-0.1249064760694769</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.742154194820599</v>
+        <v>-1.701785627843471</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.110566496956546</v>
+        <v>2.134787637142822</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.128320086193359</v>
+        <v>-8.068747190380698</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1004579581951592</v>
+        <v>-0.07662879987009497</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.609878721189713</v>
+        <v>-1.569510154212584</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.185299267882105</v>
+        <v>2.209520408068381</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.937720411520206</v>
+        <v>-7.878147515707545</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0214030276382613</v>
+        <v>0.002426130686802974</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.41927904651656</v>
+        <v>-1.378910479539431</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.302474133373633</v>
+        <v>2.32669527355991</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.688720612836625</v>
+        <v>-7.629147717023964</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.09110323305882995</v>
+        <v>0.1149323913838942</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.41927904651656</v>
+        <v>-1.378910479539431</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.315380474597291</v>
+        <v>2.339601614783569</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.79431060260973</v>
+        <v>-7.734737706797069</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.0791086924496307</v>
+        <v>-0.05527953412456643</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.524869036289664</v>
+        <v>-1.484500469312536</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.12405055113421</v>
+        <v>2.148271691320487</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.813045504728326</v>
+        <v>-7.753472608915666</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03805831141998306</v>
+        <v>-0.01422915309491879</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.530465045949795</v>
+        <v>-1.490096478972667</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.169237287215218</v>
+        <v>2.193458427401495</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.665105463320727</v>
+        <v>-7.605532567508066</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.09876121754511091</v>
+        <v>-0.07493205922004664</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.510144130041238</v>
+        <v>-1.469775563064109</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.061550914072185</v>
+        <v>2.085772054258462</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.612135941066739</v>
+        <v>-7.552563045254078</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08628739489699377</v>
+        <v>-0.0624582365719295</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.457174607787249</v>
+        <v>-1.41680604081012</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.0846186411711</v>
+        <v>2.108839781357377</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.568587534296048</v>
+        <v>-7.509014638483388</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07582864428381075</v>
+        <v>-0.05199948595874648</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.457174607787249</v>
+        <v>-1.41680604081012</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.077658029076007</v>
+        <v>2.101879169262284</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.32643914084219</v>
+        <v>-7.266866245029529</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.0354930674788756</v>
+        <v>0.05932222580393987</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.457174607787249</v>
+        <v>-1.41680604081012</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.09212038345715</v>
+        <v>2.116341523643427</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.218180003719668</v>
+        <v>-7.158607107907008</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.0733288427870793</v>
+        <v>0.09715800111214357</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.457174607787249</v>
+        <v>-1.41680604081012</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.086652503916345</v>
+        <v>2.110873644102622</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.094888868902538</v>
+        <v>-7.035315973089877</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1201433907245084</v>
+        <v>0.1439725490495727</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.333883472970118</v>
+        <v>-1.29351490599299</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.1581252788172</v>
+        <v>2.182346419003477</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.073739669999094</v>
+        <v>-7.014166774186434</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1363040485232112</v>
+        <v>0.1601332068482755</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.312734274066675</v>
+        <v>-1.272365707089547</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.178515776396591</v>
+        <v>2.202736916582869</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.82997422801565</v>
+        <v>-6.770401332202989</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2295909336636393</v>
+        <v>0.2534200919887035</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.312734274066675</v>
+        <v>-1.272365707089547</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.174296484743642</v>
+        <v>2.198517624929919</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.728211407738355</v>
+        <v>-6.668638511925694</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2724203756945736</v>
+        <v>0.2962495340196378</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.299515205674246</v>
+        <v>-1.259146638697118</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.184352239699115</v>
+        <v>2.208573379885392</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.47836101378928</v>
+        <v>-6.41878811797662</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3651026082579052</v>
+        <v>0.3889317665829695</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.299515205674246</v>
+        <v>-1.259146638697118</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.177094314682817</v>
+        <v>2.201315454869095</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.302468921321848</v>
+        <v>-6.242896025509188</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4390585687655268</v>
+        <v>0.4628877270905911</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.299515205674246</v>
+        <v>-1.259146638697118</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.180693438203466</v>
+        <v>2.204914578389743</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.131022458299385</v>
+        <v>-6.071449562486724</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5209646600290658</v>
+        <v>0.5447938183541301</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.128068742651783</v>
+        <v>-1.087700175674655</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.296888822071498</v>
+        <v>2.321109962257775</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.905989458630562</v>
+        <v>-5.846416562817901</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6099983375128923</v>
+        <v>0.6338274958379566</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9030357429829602</v>
+        <v>-0.8626671760058319</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.430929099489088</v>
+        <v>2.455150239675365</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.842353716396627</v>
+        <v>-5.782780820583967</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6401474354607832</v>
+        <v>0.6639765937858475</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8394000007490257</v>
+        <v>-0.7990314337718973</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.473805345883767</v>
+        <v>2.498026486070044</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.798591535090786</v>
+        <v>-5.739018639278125</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6388465667669156</v>
+        <v>0.6626757250919799</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8394000007490257</v>
+        <v>-0.7990314337718973</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.454999604667562</v>
+        <v>2.479220744853839</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.558161038285926</v>
+        <v>-5.498588142473265</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.736761842113737</v>
+        <v>0.7605910004388012</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5989695039441654</v>
+        <v>-0.5586009369670371</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.601000979375355</v>
+        <v>2.625222119561633</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.485918470114731</v>
+        <v>-5.42634557430207</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.769588183217035</v>
+        <v>0.7934173415420993</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5989695039441654</v>
+        <v>-0.5586009369670371</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.604930293210176</v>
+        <v>2.629151433396453</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.432920147833343</v>
+        <v>-5.373347252020682</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7914660960469302</v>
+        <v>0.8152952543719945</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5436332449422265</v>
+        <v>-0.5032646779650982</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.638810632528679</v>
+        <v>2.663031772714956</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.324115262353616</v>
+        <v>-5.264542366540955</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8319861214588147</v>
+        <v>0.8558152797838789</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5436332449422265</v>
+        <v>-0.5032646779650982</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.635808703748673</v>
+        <v>2.66002984393495</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.104094464316606</v>
+        <v>-5.044521568503945</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.921573477684233</v>
+        <v>0.9454026360092973</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4024133998742463</v>
+        <v>-0.362044832897118</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.722119647800075</v>
+        <v>2.746340787986352</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.971226775253328</v>
+        <v>-4.911653879440667</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9906147361113673</v>
+        <v>1.014443894436432</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4024133998742463</v>
+        <v>-0.362044832897118</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.738013830601898</v>
+        <v>2.762234970788175</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.851053691888829</v>
+        <v>-4.791480796076169</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.039829813897469</v>
+        <v>1.063658972222533</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2822403165097473</v>
+        <v>-0.241871749532619</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.811263525060899</v>
+        <v>2.835484665247177</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.706381546789092</v>
+        <v>-4.646808650976431</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.107786774498803</v>
+        <v>1.131615932823868</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1375681714100099</v>
+        <v>-0.09719960443288161</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.908154914682182</v>
+        <v>2.932376054868459</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.766256374146784</v>
+        <v>-4.706683478334123</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.069874334957152</v>
+        <v>1.093703493282217</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.197442998767702</v>
+        <v>-0.1570744317905737</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.858267509668992</v>
+        <v>2.88248864985527</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.679456876367775</v>
+        <v>-4.619883980555114</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.126994627391322</v>
+        <v>1.150823785716387</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.197442998767702</v>
+        <v>-0.1570744317905737</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.880668002991559</v>
+        <v>2.904889143177836</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.681926582829581</v>
+        <v>-4.62235368701692</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.126079146180012</v>
+        <v>1.149908304505076</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1999127052295082</v>
+        <v>-0.1595441382523799</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.879258580487887</v>
+        <v>2.903479720674164</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.750296769153591</v>
+        <v>-4.69072387334093</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.10973799412511</v>
+        <v>1.133567152450174</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1906370061932933</v>
+        <v>-0.150268439216165</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.895830922384318</v>
+        <v>2.920052062570595</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.858834950069725</v>
+        <v>-4.799262054257064</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.056759430390548</v>
+        <v>1.080588588715612</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1906370061932933</v>
+        <v>-0.150268439216165</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.886267631016209</v>
+        <v>2.910488771202486</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.88982810939843</v>
+        <v>-4.83025521358577</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8690717316994523</v>
+        <v>0.8929008900245166</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1906370061932933</v>
+        <v>-0.150268439216165</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.710977196056596</v>
+        <v>2.735198336242873</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.714353849605962</v>
+        <v>-4.654780953793301</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9438286676082275</v>
+        <v>0.9676578259332917</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1906370061932933</v>
+        <v>-0.150268439216165</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.715544428048384</v>
+        <v>2.739765568234661</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.825290102247211</v>
+        <v>-4.76571720643455</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.875196195312935</v>
+        <v>0.8990253536379993</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1906370061932933</v>
+        <v>-0.150268439216165</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.691286456809591</v>
+        <v>2.715507596995868</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.833572176392269</v>
+        <v>-4.773999280579608</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8750147508748172</v>
+        <v>0.8988439091998814</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1989190803383517</v>
+        <v>-0.1585505133612233</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.689448597542461</v>
+        <v>2.713669737728738</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.773719557188546</v>
+        <v>-4.714146661375885</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9091281849884387</v>
+        <v>0.932957343313503</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1989190803383517</v>
+        <v>-0.1585505133612233</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.699620983974594</v>
+        <v>2.723842124160871</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.687476094162168</v>
+        <v>-4.627903198349507</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9385718407728503</v>
+        <v>0.9624009990979145</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1989190803383517</v>
+        <v>-0.1585505133612233</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.694567254548454</v>
+        <v>2.718788394734731</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.732782913561148</v>
+        <v>-4.673210017748487</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9122248884577839</v>
+        <v>0.9360540467828482</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2397292433475824</v>
+        <v>-0.1993606763704541</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.661856932187441</v>
+        <v>2.686078072373718</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.761816018263449</v>
+        <v>-4.702243122450788</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.901163519609965</v>
+        <v>0.9249926779350293</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2397292433475824</v>
+        <v>-0.1993606763704541</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.662408805220543</v>
+        <v>2.686629945406819</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.669005536812589</v>
+        <v>-4.609432640999929</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8675604040816745</v>
+        <v>0.8913895624067387</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1469187618967231</v>
+        <v>-0.1065501949195948</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.647367785982424</v>
+        <v>2.671588926168701</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.713395006142017</v>
+        <v>-4.653822110329356</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8516780922745042</v>
+        <v>0.8755072505995685</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1913082312261508</v>
+        <v>-0.1509396642490224</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.622607580309368</v>
+        <v>2.646828720495645</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.600723787905767</v>
+        <v>-4.541150892093106</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8918222880807274</v>
+        <v>0.9156514464057917</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.07863701298990056</v>
+        <v>-0.03826844601277224</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.685286019762841</v>
+        <v>2.709507159949118</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.488346786723094</v>
+        <v>-4.428773890910433</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9422643843844638</v>
+        <v>0.9660935427095281</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.07863701298990056</v>
+        <v>-0.03826844601277224</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.690777315593508</v>
+        <v>2.714998455779785</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.516127184624446</v>
+        <v>-4.456554288811786</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9426494269924617</v>
+        <v>0.966478585317526</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1064174108912536</v>
+        <v>-0.0660488439141253</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.685606278621236</v>
+        <v>2.709827418807513</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.599128465649725</v>
+        <v>-4.539555569837065</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7478046345830034</v>
+        <v>0.7716337929080677</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1249882954184274</v>
+        <v>-0.08461972844129906</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.512819467905585</v>
+        <v>2.537040608091861</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.707742544093056</v>
+        <v>-4.648169648280396</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8245086639248767</v>
+        <v>0.8483378222499409</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1249882954184274</v>
+        <v>-0.08461972844129906</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.63296912862479</v>
+        <v>2.657190268811068</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.794341127074159</v>
+        <v>-4.734768231261499</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8043822568347585</v>
+        <v>0.8282114151598228</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1249882954184274</v>
+        <v>-0.08461972844129906</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.647482154727113</v>
+        <v>2.671703294913391</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.755957464516008</v>
+        <v>-4.696384568703348</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8171551632003875</v>
+        <v>0.8409843215254518</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.0866046328602762</v>
+        <v>-0.04623606588314788</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.667931793604373</v>
+        <v>2.69215293379065</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.578841134480842</v>
+        <v>-4.519268238668182</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8847307240597559</v>
+        <v>0.9085598823848202</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.0866046328602762</v>
+        <v>-0.04623606588314788</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.664660822449675</v>
+        <v>2.688881962635952</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.623933379314388</v>
+        <v>-4.564360483501727</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8673772178882508</v>
+        <v>0.8912063762133151</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.148500676029666</v>
+        <v>-0.1081321090525377</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.628206588309954</v>
+        <v>2.652427728496231</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.44455795807562</v>
+        <v>-4.38498506226296</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9329143616901723</v>
+        <v>0.9567435200152365</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.008276082141052687</v>
+        <v>0.048644649118181</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.716059618518799</v>
+        <v>2.740280758705076</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.489572171596226</v>
+        <v>-4.429999275783565</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8957161316135196</v>
+        <v>0.9195452899385839</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.02207281317355192</v>
+        <v>0.0182957538035764</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.678657736661626</v>
+        <v>2.702878876847903</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.756576681868661</v>
+        <v>-4.697003786056</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7946058898434913</v>
+        <v>0.8184350481685556</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2164358512165005</v>
+        <v>-0.1760672842393722</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.567731476174803</v>
+        <v>2.59195261636108</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.857774463305834</v>
+        <v>-4.798201567493173</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7533306991651236</v>
+        <v>0.7771598574901879</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2848446647618197</v>
+        <v>-0.2444760977846914</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.525890109944113</v>
+        <v>2.55011125013039</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.825298877135062</v>
+        <v>-4.765725981322401</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7639208951877494</v>
+        <v>0.7877500535128137</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2848446647618197</v>
+        <v>-0.2444760977846914</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.52349007149843</v>
+        <v>2.547711211684707</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.806260749427764</v>
+        <v>-4.746687853615104</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7680608654789132</v>
+        <v>0.7918900238039774</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3430282760930142</v>
+        <v>-0.3026597091158859</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.485104623907958</v>
+        <v>2.509325764094235</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.837387380578383</v>
+        <v>-4.777814484765722</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9331920819573463</v>
+        <v>0.9570212402824105</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3430282760930142</v>
+        <v>-0.3026597091158859</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.662686492846638</v>
+        <v>2.686907633032916</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.851254141912301</v>
+        <v>-4.79168124609964</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9284787064099127</v>
+        <v>0.952307864734977</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3808861928268372</v>
+        <v>-0.3405176258497088</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.640805071792478</v>
+        <v>2.665026211978755</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.871511440441259</v>
+        <v>-4.811938544628598</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9263843173952555</v>
+        <v>0.9502134757203198</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3808861928268372</v>
+        <v>-0.3405176258497088</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.646813602189404</v>
+        <v>2.671034742375681</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.723768470206256</v>
+        <v>-4.664195574393595</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.064634153281278</v>
+        <v>1.088463311606343</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.213078835591954</v>
+        <v>-0.1727102686148257</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.826650664322356</v>
+        <v>2.850871804508633</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.825783152737477</v>
+        <v>-4.766210256924817</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.026621901800271</v>
+        <v>1.050451060125335</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.213078835591954</v>
+        <v>-0.1727102686148257</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.829444285853837</v>
+        <v>2.853665426040114</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.819630446684693</v>
+        <v>-4.760057550872032</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.029745332613043</v>
+        <v>1.053574490938107</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2069261295391697</v>
+        <v>-0.1665575625620414</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.833798257877166</v>
+        <v>2.858019398063443</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.836439744835195</v>
+        <v>-4.776866849022534</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.022102090092952</v>
+        <v>1.045931248418017</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2237354276896714</v>
+        <v>-0.183366860712543</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.822793155726975</v>
+        <v>2.847014295913252</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.774141746059072</v>
+        <v>-4.714568850246412</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.113356843400222</v>
+        <v>1.137186001725287</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2237354276896714</v>
+        <v>-0.183366860712543</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.889128709523796</v>
+        <v>2.913349849710073</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.572351548393915</v>
+        <v>-4.512778652581254</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9026537948556834</v>
+        <v>0.9264829531807477</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.02571723552051697</v>
+        <v>0.01465133145661135</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.716520497214687</v>
+        <v>2.740741637400964</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.512460866751321</v>
+        <v>-4.452887970938661</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9969002998348961</v>
+        <v>1.02072945815996</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.03417344612207651</v>
+        <v>0.07454201309920483</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.822745138522418</v>
+        <v>2.846966278708695</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.610201411376296</v>
+        <v>-4.550628515563635</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9724318181009499</v>
+        <v>0.9962609764260142</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.01828416798909632</v>
+        <v>0.05865273496622464</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.827839307758674</v>
+        <v>2.852060447944951</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.786539171499225</v>
+        <v>-4.726966275686564</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9004326948764498</v>
+        <v>0.9242618532015141</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1580535921338331</v>
+        <v>-0.1176850251567048</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.720572632509588</v>
+        <v>2.744793772695865</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.714992848722348</v>
+        <v>-4.655419952909687</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9275428420271292</v>
+        <v>0.9513720003521935</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1580535921338331</v>
+        <v>-0.1176850251567048</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.719064250549516</v>
+        <v>2.743285390735793</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.670619717083779</v>
+        <v>-4.611046821271119</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9451549621179929</v>
+        <v>0.9689841204430572</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1136804604952645</v>
+        <v>-0.07331189351813616</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.745550996968094</v>
+        <v>2.769772137154371</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.662665746789007</v>
+        <v>-4.603092850976346</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9483365502359018</v>
+        <v>0.9721657085609661</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1136804604952645</v>
+        <v>-0.07331189351813616</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.745550996968094</v>
+        <v>2.769772137154371</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.615010016227951</v>
+        <v>-4.555437120415291</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9737805994881288</v>
+        <v>0.9976097578131931</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.06602472993420883</v>
+        <v>-0.02565616295708051</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.780526192332531</v>
+        <v>2.804747332518808</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.487325706433655</v>
+        <v>-4.427752810620994</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.029746696780572</v>
+        <v>1.053575855105636</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.06165957986008763</v>
+        <v>0.1020281468372159</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.862029151583834</v>
+        <v>2.886250291770111</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.547992296836044</v>
+        <v>-4.488419401023384</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9922347330954886</v>
+        <v>1.016063891420553</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.02003873685844604</v>
+        <v>0.02032983011868228</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.799764834028586</v>
+        <v>2.823985974214863</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.503153895227646</v>
+        <v>-4.443580999414985</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.014267796349476</v>
+        <v>1.038096954674541</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.01549530391357656</v>
+        <v>0.02487326306355175</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.806588596406137</v>
+        <v>2.830809736592414</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.603912530984644</v>
+        <v>-4.544339635171983</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9781252816777553</v>
+        <v>1.00195444000282</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.104320872640582</v>
+        <v>-0.06395230566345367</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.757454194801011</v>
+        <v>2.781675334987288</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.559709693898744</v>
+        <v>-4.500136798086083</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.001686019039953</v>
+        <v>1.025515177365017</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.06011803555468154</v>
+        <v>-0.01974946857755322</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.789855499580389</v>
+        <v>2.814076639766665</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.596688721562186</v>
+        <v>-4.537115825749526</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9853044084438229</v>
+        <v>1.009133566768887</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.023144133763351</v>
+        <v>0.01722443321377731</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.810449841124434</v>
+        <v>2.834670981310711</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.616746800427027</v>
+        <v>-4.557173904614366</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.028528942080926</v>
+        <v>1.052358100405991</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.023144133763351</v>
+        <v>0.01722443321377731</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.861697606307474</v>
+        <v>2.885918746493751</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.576816127249137</v>
+        <v>-4.517243231436476</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.042941915946336</v>
+        <v>1.0667710742714</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.01678653941453934</v>
+        <v>0.05715510639166765</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.884096714808461</v>
+        <v>2.908317854994738</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.536345779686432</v>
+        <v>-4.476772883873771</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.054078283209688</v>
+        <v>1.077907441534752</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.05725688697724429</v>
+        <v>0.09762545395437261</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.903327151584354</v>
+        <v>2.927548291770631</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.471121598559226</v>
+        <v>-4.411548702746566</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.097355359753275</v>
+        <v>1.121184518078339</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1224810681044499</v>
+        <v>0.1628496350815782</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.959649064353383</v>
+        <v>2.98387020453966</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.521615888916283</v>
+        <v>-4.462042993103622</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.073118615909733</v>
+        <v>1.096947774234797</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.07746033097837568</v>
+        <v>0.117828897955504</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.928597594377019</v>
+        <v>2.952818734563296</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.541727544950991</v>
+        <v>-4.48215464913833</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.06633074582709</v>
+        <v>1.090159904152154</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.08848767597579488</v>
+        <v>0.1288562429529232</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.93647079370671</v>
+        <v>2.960691933892988</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.639408124223637</v>
+        <v>-4.579835228410976</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.187816285139242</v>
+        <v>1.211645443464306</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.02221551936439392</v>
+        <v>0.0181530476127344</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.030606647523808</v>
+        <v>3.054827787710085</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.615616555617494</v>
+        <v>-4.556043659804834</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.317445821799516</v>
+        <v>1.34127498012458</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.001576049241748367</v>
+        <v>0.04194461621887668</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.16499449790531</v>
+        <v>3.189215638091587</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.652370974179217</v>
+        <v>-4.592798078366556</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.294452030388686</v>
+        <v>1.31828118871375</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.001576049241748367</v>
+        <v>0.04194461621887668</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.156702473919169</v>
+        <v>3.180923614105446</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.648036671122169</v>
+        <v>-4.588463775309508</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.294378947195285</v>
+        <v>1.318208105520349</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1532261525609523</v>
+        <v>0.1935947195380806</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.245885731494471</v>
+        <v>3.270106871680748</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.639144209728886</v>
+        <v>-4.579571313916225</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.315490337479389</v>
+        <v>1.339319495804454</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1532261525609523</v>
+        <v>0.1935947195380806</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.263440137221262</v>
+        <v>3.28766127740754</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.753317901765136</v>
+        <v>3.818894628465421</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.807620326698763</v>
+        <v>-4.748047430886102</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.239954938096022</v>
+        <v>1.263784096421087</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1252783168443715</v>
+        <v>0.1656468838214998</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.238526483195898</v>
+        <v>3.262747623382175</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240616.xlsx
+++ b/tame_output/ON/bt/strategyON_20240616.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,16 +610,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>-0.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>106.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.3%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-692.6%</t>
+          <t>-696.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>88.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.2%</t>
+          <t>451.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-636.4%</t>
+          <t>-655.6%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.4%</t>
+          <t>-278.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-41.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-272.3%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>105.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-249.8%</t>
+          <t>-257.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.1%</t>
+          <t>-309.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-223.3%</t>
+          <t>-183.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-207.4%</t>
+          <t>-212.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.1%</t>
+          <t>-186.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-119.7%</t>
+          <t>-136.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1996"/>
+  <dimension ref="A1:G1997"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.074651412279923</v>
+        <v>-2.109831591159216</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.286703278216148</v>
+        <v>2.272631206664431</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6699985588688046</v>
+        <v>0.634818379989511</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.518919402763148</v>
+        <v>3.497811295435572</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.440720139424576</v>
+        <v>-2.475900318303869</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.133360086664736</v>
+        <v>2.119288015113018</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3039298317241519</v>
+        <v>0.2687496528448583</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.292362465782805</v>
+        <v>3.271254358455229</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.649210920876261</v>
+        <v>-2.684391099755554</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.07030206382283</v>
+        <v>2.056229992271113</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.09543905027246746</v>
+        <v>0.06025887139317387</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.187606286650563</v>
+        <v>3.166498179322986</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.896412105641482</v>
+        <v>-2.931592284520775</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.97952034032531</v>
+        <v>1.965448268773593</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1155924037712799</v>
+        <v>0.08041222489198629</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.207797049158418</v>
+        <v>3.186688941830842</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.388797133665579</v>
+        <v>-3.423977312544872</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.783672721159404</v>
+        <v>1.769600649607687</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3767926242528168</v>
+        <v>-0.4119728031321104</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.913472424387693</v>
+        <v>2.892364317060117</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.773977524595651</v>
+        <v>-3.809157703474944</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.628143103600238</v>
+        <v>1.614071032048521</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3767926242528168</v>
+        <v>-0.4119728031321104</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.912014963200556</v>
+        <v>2.89090685587298</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.117660297822314</v>
+        <v>-4.152840476701607</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.492439117764189</v>
+        <v>1.478367046212472</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.484698676280035</v>
+        <v>-0.5198788551593286</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.849040455438841</v>
+        <v>2.827932348111265</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.324172074709336</v>
+        <v>-4.359352253588629</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.405940465665638</v>
+        <v>1.391868394113921</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6912104531670565</v>
+        <v>-0.7263906320463501</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.721239447962886</v>
+        <v>2.70013134063531</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.643516149789837</v>
+        <v>-4.678696328669131</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.279975762333697</v>
+        <v>1.26590369078198</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6912104531670565</v>
+        <v>-0.7263906320463501</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.723012374663146</v>
+        <v>2.70190426733557</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.075321942939625</v>
+        <v>-5.110502121818918</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.093586332541187</v>
+        <v>1.079514260989469</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8276279496083235</v>
+        <v>-0.8628081284876171</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.62749476426579</v>
+        <v>2.606386656938214</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.310015937072177</v>
+        <v>-5.34519611595147</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9879935098902566</v>
+        <v>0.9739214383385391</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8212916823790684</v>
+        <v>-0.8564718612583619</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.619581299605434</v>
+        <v>2.598473192277858</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.64567858430263</v>
+        <v>-5.680858763181923</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8523090426540407</v>
+        <v>0.8382369711023232</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8212916823790684</v>
+        <v>-0.8564718612583619</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.618161891261399</v>
+        <v>2.597053783933823</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.009304829202943</v>
+        <v>-6.044485008082236</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7133461049281569</v>
+        <v>0.6992740333764393</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9195133192461942</v>
+        <v>-0.9546934981254878</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.565716469375365</v>
+        <v>2.544608362047789</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.37443221184169</v>
+        <v>-6.409612390720983</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5665496668784895</v>
+        <v>0.552477595326772</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.215824103545207</v>
+        <v>-1.2510042824245</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.387184513801789</v>
+        <v>2.366076406474213</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.783020989022368</v>
+        <v>-6.818201167901661</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4018757000209767</v>
+        <v>0.3878036284692601</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.659593059605179</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.140792791508141</v>
+        <v>2.119684684180565</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.059597089338201</v>
+        <v>-7.094777268217493</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2864306923661046</v>
+        <v>0.2723586208143876</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.659593059605179</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.135978223979602</v>
+        <v>2.114870116652026</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.475988963625198</v>
+        <v>-7.511169142504491</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1178679932601829</v>
+        <v>0.1037959217084659</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.659593059605179</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.133972274588479</v>
+        <v>2.112864167260903</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.746755052717844</v>
+        <v>-7.781935231597136</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.01982024829180373</v>
+        <v>0.005748176740087096</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.659593059605179</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.144230965257158</v>
+        <v>2.123122857929582</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.092629874702652</v>
+        <v>-8.127810053581944</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1224301153564245</v>
+        <v>-0.1365021869081411</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.659593059605179</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.140330530402853</v>
+        <v>2.119222423075277</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.256209752887036</v>
+        <v>-8.291389931766329</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1894571465751773</v>
+        <v>-0.203529218126894</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.659593059605179</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.138735450457854</v>
+        <v>2.117627343130278</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.552871094697235</v>
+        <v>-8.588051273576527</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3043427073700484</v>
+        <v>-0.3184147789217651</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.728336195339057</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.101268544946735</v>
+        <v>2.080160437619159</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.739590803006537</v>
+        <v>-8.77477098188583</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3830568952281723</v>
+        <v>-0.3971289667798894</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.728336195339057</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.097242240412332</v>
+        <v>2.076134133084756</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.122592191749169</v>
+        <v>-9.157772370628461</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5363595520468092</v>
+        <v>-0.5504316235985258</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.728336195339057</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.097140139090748</v>
+        <v>2.076032031763172</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.304461982734203</v>
+        <v>-9.339642161613495</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6065359524693927</v>
+        <v>-0.6206080240211098</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.910205986324092</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.990589780471157</v>
+        <v>1.969481673143581</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.663992305238205</v>
+        <v>-9.699172484117497</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7449977781729431</v>
+        <v>-0.7590698497246602</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.910205986324092</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.995940083769207</v>
+        <v>1.974831976441631</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.714341368692427</v>
+        <v>-9.749521547571719</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7572213835974546</v>
+        <v>-0.7712934551491712</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.925374870899021</v>
+        <v>-1.960555049778314</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.973646665653852</v>
+        <v>1.952538558326276</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.811960646113823</v>
+        <v>-9.847140824993115</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7932273439442441</v>
+        <v>-0.8072994154959612</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.022994148320417</v>
+        <v>-2.058174327199711</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.918116849822782</v>
+        <v>1.897008742495206</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937496</v>
+        <v>3.492448711937495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.959486734119466</v>
+        <v>-9.994666912998758</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8493442228249291</v>
+        <v>-0.8634162943766461</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.170520236326061</v>
+        <v>-2.205700415205354</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.832494753340968</v>
+        <v>1.811386646013392</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16374490944933</v>
+        <v>-10.19892508832862</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.925534295838232</v>
+        <v>-0.9396063673899491</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.29815918094005</v>
+        <v>-2.333339359819343</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.761424583691217</v>
+        <v>1.740316476363641</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.496851904729888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.23807788570949</v>
+        <v>-10.27325806458879</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9507849318578621</v>
+        <v>-0.9648570034095791</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.442858704874723</v>
+        <v>-2.478038883754016</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.67908742381485</v>
+        <v>1.657979316487274</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440631</v>
+        <v>3.49997173944063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.16460805404204</v>
+        <v>-10.19978823292134</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.906025297697461</v>
+        <v>-0.9200973692491781</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.369388873207274</v>
+        <v>-2.404569052086567</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.73854102430874</v>
+        <v>1.717432916981164</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.33973247142859</v>
+        <v>-10.37491265030788</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9615198439045614</v>
+        <v>-0.9755919154562784</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.544513290593818</v>
+        <v>-2.579693469473111</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.64802159462433</v>
+        <v>1.626913487296755</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.57418456544308</v>
+        <v>-10.60936474432237</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.062519846411953</v>
+        <v>-1.07659191796367</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.544513290593818</v>
+        <v>-2.579693469473111</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.640802429722734</v>
+        <v>1.619694322395159</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.67855929646952</v>
+        <v>-10.71373947534882</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.110941929596508</v>
+        <v>-1.125014001148225</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.648888021620264</v>
+        <v>-2.684068200499557</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.571505400332891</v>
+        <v>1.550397293005315</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.73134545206985</v>
+        <v>-10.76652563094914</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.130940601998082</v>
+        <v>-1.145012673549799</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.744563508202661</v>
+        <v>-2.779743687081954</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.515215898222009</v>
+        <v>1.494107790894433</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.85738224543814</v>
+        <v>-10.89256242431743</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.178661590716283</v>
+        <v>-1.192733662268</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.719311885392918</v>
+        <v>-2.754492064272211</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.533060600536969</v>
+        <v>1.511952493209393</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.57367402532254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.80536673146933</v>
+        <v>-10.84054691034862</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.153865049442357</v>
+        <v>-1.167937120994075</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.719311885392918</v>
+        <v>-2.754492064272211</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.53705093622337</v>
+        <v>1.515942828895794</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.600038265158918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.94703857319345</v>
+        <v>-10.98221875207274</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.212009013030747</v>
+        <v>-1.226081084582464</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.719311885392918</v>
+        <v>-2.754492064272211</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.535575709324628</v>
+        <v>1.514467601997052</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.89744772876861</v>
+        <v>-10.93262790764791</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.177119265095941</v>
+        <v>-1.191191336647659</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.669721040968084</v>
+        <v>-2.704901219847378</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.580383626144401</v>
+        <v>1.559275518816825</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.85286134501705</v>
+        <v>-10.91982051464313</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.172335845241998</v>
+        <v>-1.199119513092432</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.706002154065726</v>
+        <v>-2.753756994856279</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.545563824639133</v>
+        <v>1.516910920164801</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.68516138161528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.62701619229763</v>
+        <v>-10.69397536192372</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.072418711118024</v>
+        <v>-1.099202378968458</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.664075478478563</v>
+        <v>-2.711830319269115</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.58029890302764</v>
+        <v>1.551645998553308</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.50243753596004</v>
+        <v>-10.56939670558613</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.021448104026929</v>
+        <v>-1.048231771877363</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.664075478478563</v>
+        <v>-2.711830319269115</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.581438047583698</v>
+        <v>1.552785143109367</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.55533282400433</v>
+        <v>-10.62229199363041</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.039972445082536</v>
+        <v>-1.066756112932969</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.659120132390116</v>
+        <v>-2.706874973180669</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.587045029398874</v>
+        <v>1.558392124924542</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.48319964871645</v>
+        <v>-10.55015881834253</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.005385470728747</v>
+        <v>-1.032169138579181</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.659120132390116</v>
+        <v>-2.706874973180669</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.59277873363751</v>
+        <v>1.564125829163179</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.4118332561068</v>
+        <v>-10.47879242573289</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9865761760787528</v>
+        <v>-1.013359843929187</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.587753739780469</v>
+        <v>-2.635508580571021</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.625861306809434</v>
+        <v>1.597208402335103</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.747702660232407</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.14799638890273</v>
+        <v>-10.21495555852882</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8909249105100332</v>
+        <v>-0.9177085783604668</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.587753739780469</v>
+        <v>-2.635508580571021</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.615977825496526</v>
+        <v>1.587324921022195</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436223</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.880754588034334</v>
+        <v>-9.947713757660418</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7858627506620475</v>
+        <v>-0.8126464185124811</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.587753739780469</v>
+        <v>-2.635508580571021</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.614143264997153</v>
+        <v>1.585490360522821</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311942</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.782847549357843</v>
+        <v>-9.849806718983928</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7470002501649122</v>
+        <v>-0.7737839180153459</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.519767989919912</v>
+        <v>-2.567522830710464</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.654634399940025</v>
+        <v>1.625981495465694</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097238</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.758894008381885</v>
+        <v>-9.82585317800797</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7367503276290353</v>
+        <v>-0.7635339954794689</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.495814448943955</v>
+        <v>-2.543569289734507</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.669675030671094</v>
+        <v>1.641022126196762</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.494834070059088</v>
+        <v>-9.561793239685173</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6443866684616686</v>
+        <v>-0.6711703363121027</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.231754510621159</v>
+        <v>-2.279509351411711</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.814850677503019</v>
+        <v>1.786197773028688</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.787754446554251</v>
+        <v>-8.854713616180335</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3643418527200346</v>
+        <v>-0.3911255205704682</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.231754510621159</v>
+        <v>-2.279509351411711</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.812063643842718</v>
+        <v>1.783410739368387</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388723</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.747570148188061</v>
+        <v>-8.814529317814145</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3479245094857171</v>
+        <v>-0.3747081773361507</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.191570212254968</v>
+        <v>-2.23932505304552</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.836517846750274</v>
+        <v>1.807864942275943</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626468</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.584170277248699</v>
+        <v>-8.651129446874783</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2831977398892156</v>
+        <v>-0.3099814077396492</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.028170341315605</v>
+        <v>-2.075925182106158</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.933924590534648</v>
+        <v>1.905271686060317</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291808</v>
+        <v>3.787330429291806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.3506890550191</v>
+        <v>-8.417648224645184</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1818808221595232</v>
+        <v>-0.2086644900099572</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.794689119086007</v>
+        <v>-1.842443959876559</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.08193775271026</v>
+        <v>2.053284848235929</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.201022664011585</v>
+        <v>-8.26798183363767</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1249064760694769</v>
+        <v>-0.1516901439199105</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.701785627843471</v>
+        <v>-1.749540468634023</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.134787637142822</v>
+        <v>2.106134732668491</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390424</v>
+        <v>3.763182248390422</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.068747190380698</v>
+        <v>-8.135706360006782</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.07662879987009497</v>
+        <v>-0.1034124677205286</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.569510154212584</v>
+        <v>-1.617264995003136</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.209520408068381</v>
+        <v>2.18086750359405</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105949</v>
+        <v>3.784718794105947</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.878147515707545</v>
+        <v>-7.94510668533363</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.002426130686802974</v>
+        <v>-0.02435753716363109</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.378910479539431</v>
+        <v>-1.426665320329983</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.32669527355991</v>
+        <v>2.298042369085579</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960982</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.629147717023964</v>
+        <v>-7.696106886650049</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1149323913838942</v>
+        <v>0.08814872353346015</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.378910479539431</v>
+        <v>-1.426665320329983</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.339601614783569</v>
+        <v>2.310948710309237</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.69293185560764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.734737706797069</v>
+        <v>-7.801696876423153</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.05527953412456643</v>
+        <v>-0.08206320197500006</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.484500469312536</v>
+        <v>-1.532255310103088</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.148271691320487</v>
+        <v>2.119618786846156</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.753472608915666</v>
+        <v>-7.82043177854175</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.01422915309491879</v>
+        <v>-0.04101282094535286</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.490096478972667</v>
+        <v>-1.537851319763219</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.193458427401495</v>
+        <v>2.164805522927164</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710808</v>
+        <v>3.760333686710807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.605532567508066</v>
+        <v>-7.672491737134151</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.07493205922004664</v>
+        <v>-0.1017157270704807</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.469775563064109</v>
+        <v>-1.517530403854662</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.085772054258462</v>
+        <v>2.057119149784131</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409202</v>
+        <v>3.7235662294092</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.552563045254078</v>
+        <v>-7.619522214880162</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.0624582365719295</v>
+        <v>-0.08924190442236313</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.41680604081012</v>
+        <v>-1.464560881600673</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.108839781357377</v>
+        <v>2.080186876883046</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098104</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.509014638483388</v>
+        <v>-7.575973808109472</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.05199948595874648</v>
+        <v>-0.07878315380918011</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.41680604081012</v>
+        <v>-1.464560881600673</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.101879169262284</v>
+        <v>2.073226264787952</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.782922533493415</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.266866245029529</v>
+        <v>-7.333825414655614</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.05932222580393987</v>
+        <v>0.03253855795350624</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.41680604081012</v>
+        <v>-1.464560881600673</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.116341523643427</v>
+        <v>2.087688619169096</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722813</v>
+        <v>3.828551486722811</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.158607107907008</v>
+        <v>-7.225566277533092</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.09715800111214357</v>
+        <v>0.07037433326170994</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.41680604081012</v>
+        <v>-1.464560881600673</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.110873644102622</v>
+        <v>2.082220739628291</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792041</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.035315973089877</v>
+        <v>-7.102275142715961</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1439725490495727</v>
+        <v>0.1171888811991391</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.29351490599299</v>
+        <v>-1.341269746783542</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.182346419003477</v>
+        <v>2.153693514529146</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919904</v>
+        <v>3.812453678919902</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.014166774186434</v>
+        <v>-7.081125943812518</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1601332068482755</v>
+        <v>0.1333495389978414</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.272365707089547</v>
+        <v>-1.320120547880099</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.202736916582869</v>
+        <v>2.174084012108537</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318088</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.770401332202989</v>
+        <v>-6.837360501829074</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2534200919887035</v>
+        <v>0.2266364241382699</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.272365707089547</v>
+        <v>-1.320120547880099</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.198517624929919</v>
+        <v>2.169864720455588</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.668638511925694</v>
+        <v>-6.735597681551779</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2962495340196378</v>
+        <v>0.2694658661692038</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.259146638697118</v>
+        <v>-1.30690147948767</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.208573379885392</v>
+        <v>2.179920475411061</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.82635497427918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.41878811797662</v>
+        <v>-6.610674146585994</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3889317665829695</v>
+        <v>0.31217735513922</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.259146638697118</v>
+        <v>-1.30690147948767</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.201315454869095</v>
+        <v>2.172662550394763</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.242896025509188</v>
+        <v>-6.434782054118562</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4628877270905911</v>
+        <v>0.3861333156468412</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.259146638697118</v>
+        <v>-1.30690147948767</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.204914578389743</v>
+        <v>2.176261673915412</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.071449562486724</v>
+        <v>-6.263335591096099</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5447938183541301</v>
+        <v>0.4680394069103806</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.087700175674655</v>
+        <v>-1.135455016465207</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.321109962257775</v>
+        <v>2.292457057783444</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.846416562817901</v>
+        <v>-6.038302591427276</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6338274958379566</v>
+        <v>0.5570730843942067</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8626671760058319</v>
+        <v>-0.910422016796384</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.455150239675365</v>
+        <v>2.426497335201034</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988307</v>
+        <v>3.764617879883069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.782780820583967</v>
+        <v>-5.974666849193341</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6639765937858475</v>
+        <v>0.5872221823420976</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7990314337718973</v>
+        <v>-0.8467862745624495</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.498026486070044</v>
+        <v>2.469373581595712</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074778</v>
+        <v>3.798814771074777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.739018639278125</v>
+        <v>-5.9309046678875</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6626757250919799</v>
+        <v>0.58592131364823</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7990314337718973</v>
+        <v>-0.8467862745624495</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.479220744853839</v>
+        <v>2.450567840379508</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242288</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.498588142473265</v>
+        <v>-5.69047417108264</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7605910004388012</v>
+        <v>0.6838365889950513</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5586009369670371</v>
+        <v>-0.6063557777575892</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.625222119561633</v>
+        <v>2.596569215087301</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.42634557430207</v>
+        <v>-5.618231602911445</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7934173415420993</v>
+        <v>0.7166629300983494</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5586009369670371</v>
+        <v>-0.6063557777575892</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.629151433396453</v>
+        <v>2.600498528922122</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.373347252020682</v>
+        <v>-5.565233280630057</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8152952543719945</v>
+        <v>0.7385408429282445</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5032646779650982</v>
+        <v>-0.5510195187556504</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.663031772714956</v>
+        <v>2.634378868240625</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.264542366540955</v>
+        <v>-5.45642839515033</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8558152797838789</v>
+        <v>0.779060868340129</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5032646779650982</v>
+        <v>-0.5510195187556504</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.66002984393495</v>
+        <v>2.631376939460618</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.044521568503945</v>
+        <v>-5.236407597113319</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9454026360092973</v>
+        <v>0.8686482245655474</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.362044832897118</v>
+        <v>-0.4097996736876701</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.746340787986352</v>
+        <v>2.717687883512021</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539943</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.911653879440667</v>
+        <v>-5.103539908050042</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.014443894436432</v>
+        <v>0.9376894829926816</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.362044832897118</v>
+        <v>-0.4097996736876701</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.762234970788175</v>
+        <v>2.733582066313844</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496257</v>
+        <v>3.845047386496256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.791480796076169</v>
+        <v>-4.983366824685543</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.063658972222533</v>
+        <v>0.986904560778783</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.241871749532619</v>
+        <v>-0.2896265903231712</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.835484665247177</v>
+        <v>2.806831760772845</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576992</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.646808650976431</v>
+        <v>-4.838694679585806</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.131615932823868</v>
+        <v>1.054861521380118</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.09719960443288161</v>
+        <v>-0.1449544452234338</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.932376054868459</v>
+        <v>2.903723150394128</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942098</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.706683478334123</v>
+        <v>-4.898569506943498</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.093703493282217</v>
+        <v>1.016949081838467</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1570744317905737</v>
+        <v>-0.2048292725811259</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.88248864985527</v>
+        <v>2.853835745380938</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.76264747767451</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.619883980555114</v>
+        <v>-4.811770009164489</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.150823785716387</v>
+        <v>1.074069374272637</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1570744317905737</v>
+        <v>-0.2048292725811259</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.904889143177836</v>
+        <v>2.876236238703504</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.62235368701692</v>
+        <v>-4.814239715626295</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.149908304505076</v>
+        <v>1.073153893061326</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1595441382523799</v>
+        <v>-0.207298979042932</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.903479720674164</v>
+        <v>2.874826816199833</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.69072387334093</v>
+        <v>-4.882609901950305</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.133567152450174</v>
+        <v>1.056812741006424</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.150268439216165</v>
+        <v>-0.1980232800067171</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.920052062570595</v>
+        <v>2.891399158096263</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.799262054257064</v>
+        <v>-4.991148082866439</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.080588588715612</v>
+        <v>1.003834177271862</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.150268439216165</v>
+        <v>-0.1980232800067171</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.910488771202486</v>
+        <v>2.881835866728155</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.83025521358577</v>
+        <v>-5.022141242195144</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8929008900245166</v>
+        <v>0.8161464785807668</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.150268439216165</v>
+        <v>-0.1980232800067171</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.735198336242873</v>
+        <v>2.706545431768542</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.654780953793301</v>
+        <v>-4.846666982402676</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9676578259332917</v>
+        <v>0.890903414489542</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.150268439216165</v>
+        <v>-0.1980232800067171</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.739765568234661</v>
+        <v>2.711112663760329</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.76571720643455</v>
+        <v>-4.957603235043925</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8990253536379993</v>
+        <v>0.8222709421942493</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.150268439216165</v>
+        <v>-0.1980232800067171</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.715507596995868</v>
+        <v>2.686854692521536</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77321029711129</v>
+        <v>3.773210297111288</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.773999280579608</v>
+        <v>-4.965885309188983</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8988439091998814</v>
+        <v>0.8220894977561315</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1585505133612233</v>
+        <v>-0.2063053541517755</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.713669737728738</v>
+        <v>2.685016833254407</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264159</v>
+        <v>3.784343952264157</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.714146661375885</v>
+        <v>-4.90603268998526</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.932957343313503</v>
+        <v>0.8562029318697533</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1585505133612233</v>
+        <v>-0.2063053541517755</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.723842124160871</v>
+        <v>2.695189219686539</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742295</v>
+        <v>3.786949957742293</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.627903198349507</v>
+        <v>-4.819789226958882</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9624009990979145</v>
+        <v>0.8856465876541646</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1585505133612233</v>
+        <v>-0.2063053541517755</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.718788394734731</v>
+        <v>2.6901354902604</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316043</v>
+        <v>3.752027499316041</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.673210017748487</v>
+        <v>-4.865096046357862</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9360540467828482</v>
+        <v>0.8592996353390983</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1993606763704541</v>
+        <v>-0.2471155171610063</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.686078072373718</v>
+        <v>2.657425167899387</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803187</v>
+        <v>3.753571165803185</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.702243122450788</v>
+        <v>-4.894129151060163</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9249926779350293</v>
+        <v>0.8482382664912793</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1993606763704541</v>
+        <v>-0.2471155171610063</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.686629945406819</v>
+        <v>2.657977040932488</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809493</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.609432640999929</v>
+        <v>-4.801318669609303</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8913895624067387</v>
+        <v>0.8146351509629888</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1065501949195948</v>
+        <v>-0.1543050357101469</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.671588926168701</v>
+        <v>2.64293602169437</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560422</v>
+        <v>3.74828581656042</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.653822110329356</v>
+        <v>-4.845708138938731</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8755072505995685</v>
+        <v>0.7987528391558187</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1509396642490224</v>
+        <v>-0.1986945050395746</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.646828720495645</v>
+        <v>2.618175816021314</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472732</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.541150892093106</v>
+        <v>-4.733036920702481</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9156514464057917</v>
+        <v>0.8388970349620417</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.03826844601277224</v>
+        <v>-0.08602328680332438</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.709507159949118</v>
+        <v>2.680854255474787</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798532</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.428773890910433</v>
+        <v>-4.620659919519808</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9660935427095281</v>
+        <v>0.8893391312657781</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.03826844601277224</v>
+        <v>-0.08602328680332438</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.714998455779785</v>
+        <v>2.686345551305454</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498861</v>
+        <v>3.689597840498859</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.456554288811786</v>
+        <v>-4.64844031742116</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.966478585317526</v>
+        <v>0.8897241738737762</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.0660488439141253</v>
+        <v>-0.1138036847046774</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.709827418807513</v>
+        <v>2.681174514333181</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.539555569837065</v>
+        <v>-4.731441598446439</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7716337929080677</v>
+        <v>0.6948793814643179</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.08461972844129906</v>
+        <v>-0.1323745692318512</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.537040608091861</v>
+        <v>2.50838770361753</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.648169648280396</v>
+        <v>-4.84005567688977</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8483378222499409</v>
+        <v>0.771583410806191</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.08461972844129906</v>
+        <v>-0.1323745692318512</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.657190268811068</v>
+        <v>2.628537364336736</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190763</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.734768231261499</v>
+        <v>-4.926654259870873</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8282114151598228</v>
+        <v>0.7514570037160728</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.08461972844129906</v>
+        <v>-0.1323745692318512</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.671703294913391</v>
+        <v>2.643050390439059</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.74117406991342</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.696384568703348</v>
+        <v>-4.888270597312722</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8409843215254518</v>
+        <v>0.764229910081702</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.04623606588314788</v>
+        <v>-0.09399090667370003</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.69215293379065</v>
+        <v>2.663500029316318</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.75114719753248</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.519268238668182</v>
+        <v>-4.711154267277556</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9085598823848202</v>
+        <v>0.8318054709410703</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.04623606588314788</v>
+        <v>-0.09399090667370003</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.688881962635952</v>
+        <v>2.66022905816162</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793897</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.564360483501727</v>
+        <v>-4.756246512111102</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8912063762133151</v>
+        <v>0.8144519647695652</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1081321090525377</v>
+        <v>-0.1558869498430898</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.652427728496231</v>
+        <v>2.6237748240219</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.38498506226296</v>
+        <v>-4.576871090872334</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9567435200152365</v>
+        <v>0.8799891085714866</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.048644649118181</v>
+        <v>0.0008898083276288604</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.740280758705076</v>
+        <v>2.711627854230745</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.429999275783565</v>
+        <v>-4.62188530439294</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9195452899385839</v>
+        <v>0.8427908784948341</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.0182957538035764</v>
+        <v>-0.02945908698697575</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.702878876847903</v>
+        <v>2.674225972373572</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.697003786056</v>
+        <v>-4.888889814665375</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8184350481685556</v>
+        <v>0.7416806367248059</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1760672842393722</v>
+        <v>-0.2238221250299243</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.59195261636108</v>
+        <v>2.563299711886749</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.798201567493173</v>
+        <v>-4.990087596102548</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7771598574901879</v>
+        <v>0.7004054460464382</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2444760977846914</v>
+        <v>-0.2922309385752435</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.55011125013039</v>
+        <v>2.521458345656058</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.765725981322401</v>
+        <v>-4.957612009931776</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7877500535128137</v>
+        <v>0.7109956420690637</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2444760977846914</v>
+        <v>-0.2922309385752435</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.547711211684707</v>
+        <v>2.519058307210376</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.746687853615104</v>
+        <v>-4.938573882224478</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7918900238039774</v>
+        <v>0.7151356123602275</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3026597091158859</v>
+        <v>-0.3504145499064381</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.509325764094235</v>
+        <v>2.480672859619903</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131247</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.777814484765722</v>
+        <v>-4.969700513375097</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9570212402824105</v>
+        <v>0.8802668288386608</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3026597091158859</v>
+        <v>-0.3504145499064381</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.686907633032916</v>
+        <v>2.658254728558584</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.79168124609964</v>
+        <v>-4.983567274709015</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.952307864734977</v>
+        <v>0.8755534532912272</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3405176258497088</v>
+        <v>-0.388272466640261</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.665026211978755</v>
+        <v>2.636373307504424</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.811938544628598</v>
+        <v>-5.003824573237972</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9502134757203198</v>
+        <v>0.8734590642765698</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3405176258497088</v>
+        <v>-0.388272466640261</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.671034742375681</v>
+        <v>2.64238183790135</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.664195574393595</v>
+        <v>-4.85608160300297</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.088463311606343</v>
+        <v>1.011708900162593</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1727102686148257</v>
+        <v>-0.2204651094053778</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.850871804508633</v>
+        <v>2.822218900034302</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.766210256924817</v>
+        <v>-4.958096285534191</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.050451060125335</v>
+        <v>0.9736966486815852</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1727102686148257</v>
+        <v>-0.2204651094053778</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.853665426040114</v>
+        <v>2.825012521565783</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.760057550872032</v>
+        <v>-4.951943579481407</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.053574490938107</v>
+        <v>0.9768200794943573</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1665575625620414</v>
+        <v>-0.2143124033525936</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.858019398063443</v>
+        <v>2.829366493589112</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.776866849022534</v>
+        <v>-4.968752877631909</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.045931248418017</v>
+        <v>0.9691768369742668</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.183366860712543</v>
+        <v>-0.2311217015030952</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.847014295913252</v>
+        <v>2.818361391438921</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.714568850246412</v>
+        <v>-4.906454878855786</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.137186001725287</v>
+        <v>1.060431590281537</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.183366860712543</v>
+        <v>-0.2311217015030952</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.913349849710073</v>
+        <v>2.884696945235742</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.512778652581254</v>
+        <v>-4.704664681190629</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9264829531807477</v>
+        <v>0.849728541736998</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.01465133145661135</v>
+        <v>-0.03310350933394079</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.740741637400964</v>
+        <v>2.712088732926632</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.452887970938661</v>
+        <v>-4.644773999548035</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.02072945815996</v>
+        <v>0.9439750467162105</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.07454201309920483</v>
+        <v>0.02678717230865268</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.846966278708695</v>
+        <v>2.818313374234364</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.550628515563635</v>
+        <v>-4.74251454417301</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9962609764260142</v>
+        <v>0.9195065649822642</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.05865273496622464</v>
+        <v>0.0108978941756725</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.852060447944951</v>
+        <v>2.823407543470619</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.726966275686564</v>
+        <v>-4.918852304295939</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9242618532015141</v>
+        <v>0.8475074417577644</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1176850251567048</v>
+        <v>-0.1654398659472569</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.744793772695865</v>
+        <v>2.716140868221533</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.655419952909687</v>
+        <v>-4.847305981519062</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9513720003521935</v>
+        <v>0.8746175889084435</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1176850251567048</v>
+        <v>-0.1654398659472569</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.743285390735793</v>
+        <v>2.714632486261462</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.611046821271119</v>
+        <v>-4.802932849880493</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9689841204430572</v>
+        <v>0.8922297089993072</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.07331189351813616</v>
+        <v>-0.1210667343086883</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.769772137154371</v>
+        <v>2.741119232680039</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863224</v>
+        <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.603092850976346</v>
+        <v>-4.794978879585721</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9721657085609661</v>
+        <v>0.8954112971172161</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.07331189351813616</v>
+        <v>-0.1210667343086883</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.769772137154371</v>
+        <v>2.741119232680039</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.555437120415291</v>
+        <v>-4.747323149024665</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9976097578131931</v>
+        <v>0.9208553463694431</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.02565616295708051</v>
+        <v>-0.07341100374763265</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.804747332518808</v>
+        <v>2.776094428044477</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.427752810620994</v>
+        <v>-4.619638839230369</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.053575855105636</v>
+        <v>0.9768214436618865</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.1020281468372159</v>
+        <v>0.05427330604666381</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.886250291770111</v>
+        <v>2.85759738729578</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.488419401023384</v>
+        <v>-4.680305429632758</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.016063891420553</v>
+        <v>0.9393094799768029</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.02032983011868228</v>
+        <v>-0.02742501067186986</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.823985974214863</v>
+        <v>2.795333069740532</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690027</v>
+        <v>3.816866067690025</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.443580999414985</v>
+        <v>-4.63546702802436</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.038096954674541</v>
+        <v>0.9613425432307909</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.02487326306355175</v>
+        <v>-0.02288157772700039</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.830809736592414</v>
+        <v>2.802156832118082</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.544339635171983</v>
+        <v>-4.736225663781358</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.00195444000282</v>
+        <v>0.9252000285590696</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.06395230566345367</v>
+        <v>-0.1117071464540058</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.781675334987288</v>
+        <v>2.753022430512957</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163217</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.500136798086083</v>
+        <v>-4.692022826695458</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.025515177365017</v>
+        <v>0.9487607659212669</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.01974946857755322</v>
+        <v>-0.06750430936810536</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.814076639766665</v>
+        <v>2.785423735292334</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022902</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.537115825749526</v>
+        <v>-4.7290018543589</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.009133566768887</v>
+        <v>0.9323791553251375</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.01722443321377731</v>
+        <v>-0.03053040757677483</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.834670981310711</v>
+        <v>2.80601807683638</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.557173904614366</v>
+        <v>-4.749059933223741</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.052358100405991</v>
+        <v>0.9756036889622408</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.01722443321377731</v>
+        <v>-0.03053040757677483</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.885918746493751</v>
+        <v>2.85726584201942</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078277</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.517243231436476</v>
+        <v>-4.709129260045851</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.0667710742714</v>
+        <v>0.9900166628276501</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.05715510639166765</v>
+        <v>0.009400265601115509</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.908317854994738</v>
+        <v>2.879664950520407</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232396</v>
+        <v>3.864518876232394</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.476772883873771</v>
+        <v>-4.668658912483146</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.077907441534752</v>
+        <v>1.001153030091002</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.09762545395437261</v>
+        <v>0.04987061316382047</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.927548291770631</v>
+        <v>2.8988953872963</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162111</v>
+        <v>3.842576394162108</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.411548702746566</v>
+        <v>-4.60343473135594</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.121184518078339</v>
+        <v>1.044430106634589</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1628496350815782</v>
+        <v>0.1150947942910261</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.98387020453966</v>
+        <v>2.955217300065328</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639817</v>
+        <v>3.840090220639814</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.462042993103622</v>
+        <v>-4.653929021712996</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.096947774234797</v>
+        <v>1.020193362791047</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.117828897955504</v>
+        <v>0.07007405716495185</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.952818734563296</v>
+        <v>2.924165830088964</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84519884274992</v>
+        <v>3.845198842749916</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.48215464913833</v>
+        <v>-4.674040677747705</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.090159904152154</v>
+        <v>1.013405492708404</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1288562429529232</v>
+        <v>0.08110140216237105</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.960691933892988</v>
+        <v>2.932039029418656</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393545</v>
+        <v>3.828690479393542</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.579835228410976</v>
+        <v>-4.771721257020351</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.211645443464306</v>
+        <v>1.134891032020556</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.0181530476127344</v>
+        <v>-0.02960179317781775</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.054827787710085</v>
+        <v>3.026174883235754</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714883</v>
+        <v>3.813251854714879</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.556043659804834</v>
+        <v>-4.747929688414208</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.34127498012458</v>
+        <v>1.264520568680831</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.04194461621887668</v>
+        <v>-0.00581022457167546</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.189215638091587</v>
+        <v>3.160562733617256</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756012</v>
+        <v>3.814259761756008</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.592798078366556</v>
+        <v>-4.784684106975931</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.31828118871375</v>
+        <v>1.241526777270001</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.04194461621887668</v>
+        <v>-0.00581022457167546</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.180923614105446</v>
+        <v>3.152270709631115</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654186</v>
+        <v>3.803426852654183</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.588463775309508</v>
+        <v>-4.780349803918883</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.318208105520349</v>
+        <v>1.241453694076599</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1935947195380806</v>
+        <v>0.1458398787475285</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.270106871680748</v>
+        <v>3.241453967206417</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717117</v>
+        <v>3.796293177717113</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.579571313916225</v>
+        <v>-4.7714573425256</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.339319495804454</v>
+        <v>1.262565084360704</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1935947195380806</v>
+        <v>0.1458398787475285</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.28766127740754</v>
+        <v>3.259008372933208</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,45 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.818894628465421</v>
+        <v>3.794453975702623</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.748047430886102</v>
+        <v>-4.939933459495477</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.263784096421087</v>
+        <v>1.187029684977337</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1656468838214998</v>
+        <v>0.1178920430309477</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.262747623382175</v>
+        <v>3.234094718907844</v>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" s="2" t="n">
+        <v>45459</v>
+      </c>
+      <c r="B1997" t="n">
+        <v>3.753242104809164</v>
+      </c>
+      <c r="C1997" t="n">
+        <v>3.106915025327306</v>
+      </c>
+      <c r="D1997" t="n">
+        <v>-4.939933459495477</v>
+      </c>
+      <c r="E1997" t="n">
+        <v>1.187029684977337</v>
+      </c>
+      <c r="F1997" t="n">
+        <v>0.1178920430309477</v>
+      </c>
+      <c r="G1997" t="n">
+        <v>3.099978822313674</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240616.xlsx
+++ b/tame_output/ON/bt/strategyON_20240616.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.5%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.5%</t>
+          <t>106.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.5%</t>
+          <t>125.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-696.1%</t>
+          <t>-692.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.3%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.6%</t>
+          <t>452.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-655.6%</t>
+          <t>-628.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-278.8%</t>
+          <t>-277.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>-271.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>105.8%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-257.5%</t>
+          <t>-246.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-309.6%</t>
+          <t>-306.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-14.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-183.3%</t>
+          <t>-213.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-212.2%</t>
+          <t>-209.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-186.2%</t>
+          <t>-184.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-136.0%</t>
+          <t>-127.6%</t>
         </is>
       </c>
     </row>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.109831591159216</v>
+        <v>-2.074651412279923</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.272631206664431</v>
+        <v>2.286703278216148</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.634818379989511</v>
+        <v>0.6699985588688046</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.497811295435572</v>
+        <v>3.518919402763148</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.475900318303869</v>
+        <v>-2.440720139424576</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.119288015113018</v>
+        <v>2.133360086664736</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.2687496528448583</v>
+        <v>0.3039298317241519</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.271254358455229</v>
+        <v>3.292362465782805</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.684391099755554</v>
+        <v>-2.649210920876261</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.056229992271113</v>
+        <v>2.07030206382283</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.06025887139317387</v>
+        <v>0.09543905027246746</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.166498179322986</v>
+        <v>3.187606286650563</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.931592284520775</v>
+        <v>-2.896412105641482</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.965448268773593</v>
+        <v>1.97952034032531</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.08041222489198629</v>
+        <v>0.1155924037712799</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.186688941830842</v>
+        <v>3.207797049158418</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.423977312544872</v>
+        <v>-3.388797133665579</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.769600649607687</v>
+        <v>1.783672721159404</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4119728031321104</v>
+        <v>-0.3767926242528168</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.892364317060117</v>
+        <v>2.913472424387693</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.809157703474944</v>
+        <v>-3.773977524595651</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.614071032048521</v>
+        <v>1.628143103600238</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4119728031321104</v>
+        <v>-0.3767926242528168</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.89090685587298</v>
+        <v>2.912014963200556</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.152840476701607</v>
+        <v>-4.117660297822314</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.478367046212472</v>
+        <v>1.492439117764189</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.5198788551593286</v>
+        <v>-0.484698676280035</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.827932348111265</v>
+        <v>2.849040455438841</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.359352253588629</v>
+        <v>-4.324172074709336</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.391868394113921</v>
+        <v>1.405940465665638</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.7263906320463501</v>
+        <v>-0.6912104531670565</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.70013134063531</v>
+        <v>2.721239447962886</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.678696328669131</v>
+        <v>-4.643516149789837</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.26590369078198</v>
+        <v>1.279975762333697</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.7263906320463501</v>
+        <v>-0.6912104531670565</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.70190426733557</v>
+        <v>2.723012374663146</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.110502121818918</v>
+        <v>-5.075321942939625</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.079514260989469</v>
+        <v>1.093586332541187</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8628081284876171</v>
+        <v>-0.8276279496083235</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.606386656938214</v>
+        <v>2.62749476426579</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.34519611595147</v>
+        <v>-5.310015937072177</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9739214383385391</v>
+        <v>0.9879935098902566</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8564718612583619</v>
+        <v>-0.8212916823790684</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.598473192277858</v>
+        <v>2.619581299605434</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.680858763181923</v>
+        <v>-5.64567858430263</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8382369711023232</v>
+        <v>0.8523090426540407</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8564718612583619</v>
+        <v>-0.8212916823790684</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.597053783933823</v>
+        <v>2.618161891261399</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.044485008082236</v>
+        <v>-6.009304829202943</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6992740333764393</v>
+        <v>0.7133461049281569</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9546934981254878</v>
+        <v>-0.9195133192461942</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.544608362047789</v>
+        <v>2.565716469375365</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.409612390720983</v>
+        <v>-6.37443221184169</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.552477595326772</v>
+        <v>0.5665496668784895</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.2510042824245</v>
+        <v>-1.215824103545207</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.366076406474213</v>
+        <v>2.387184513801789</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.818201167901661</v>
+        <v>-6.783020989022368</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3878036284692601</v>
+        <v>0.4018757000209767</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.659593059605179</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.119684684180565</v>
+        <v>2.140792791508141</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.094777268217493</v>
+        <v>-7.059597089338201</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2723586208143876</v>
+        <v>0.2864306923661046</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.659593059605179</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.114870116652026</v>
+        <v>2.135978223979602</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.511169142504491</v>
+        <v>-7.475988963625198</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1037959217084659</v>
+        <v>0.1178679932601829</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.659593059605179</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.112864167260903</v>
+        <v>2.133972274588479</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.781935231597136</v>
+        <v>-7.746755052717844</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.005748176740087096</v>
+        <v>0.01982024829180373</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.659593059605179</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.123122857929582</v>
+        <v>2.144230965257158</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.127810053581944</v>
+        <v>-8.092629874702652</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1365021869081411</v>
+        <v>-0.1224301153564245</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.659593059605179</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.119222423075277</v>
+        <v>2.140330530402853</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.291389931766329</v>
+        <v>-8.256209752887036</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.203529218126894</v>
+        <v>-0.1894571465751773</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.659593059605179</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.117627343130278</v>
+        <v>2.138735450457854</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.588051273576527</v>
+        <v>-8.552871094697235</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3184147789217651</v>
+        <v>-0.3043427073700484</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.728336195339057</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.080160437619159</v>
+        <v>2.101268544946735</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.77477098188583</v>
+        <v>-8.739590803006537</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3971289667798894</v>
+        <v>-0.3830568952281723</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.728336195339057</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.076134133084756</v>
+        <v>2.097242240412332</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.157772370628461</v>
+        <v>-9.122592191749169</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5504316235985258</v>
+        <v>-0.5363595520468092</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.728336195339057</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.076032031763172</v>
+        <v>2.097140139090748</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.339642161613495</v>
+        <v>-9.304461982734203</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6206080240211098</v>
+        <v>-0.6065359524693927</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.910205986324092</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.969481673143581</v>
+        <v>1.990589780471157</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.699172484117497</v>
+        <v>-9.663992305238205</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7590698497246602</v>
+        <v>-0.7449977781729431</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.910205986324092</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.974831976441631</v>
+        <v>1.995940083769207</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.749521547571719</v>
+        <v>-9.714341368692427</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7712934551491712</v>
+        <v>-0.7572213835974546</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.960555049778314</v>
+        <v>-1.925374870899021</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.952538558326276</v>
+        <v>1.973646665653852</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.847140824993115</v>
+        <v>-9.811960646113823</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8072994154959612</v>
+        <v>-0.7932273439442441</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.058174327199711</v>
+        <v>-2.022994148320417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.897008742495206</v>
+        <v>1.918116849822782</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.994666912998758</v>
+        <v>-9.959486734119466</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8634162943766461</v>
+        <v>-0.8493442228249291</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.205700415205354</v>
+        <v>-2.170520236326061</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.811386646013392</v>
+        <v>1.832494753340968</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.19892508832862</v>
+        <v>-10.16374490944933</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9396063673899491</v>
+        <v>-0.925534295838232</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.333339359819343</v>
+        <v>-2.29815918094005</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.740316476363641</v>
+        <v>1.761424583691217</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.27325806458879</v>
+        <v>-10.23807788570949</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9648570034095791</v>
+        <v>-0.9507849318578621</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.478038883754016</v>
+        <v>-2.442858704874723</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.657979316487274</v>
+        <v>1.67908742381485</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.19978823292134</v>
+        <v>-10.16460805404204</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9200973692491781</v>
+        <v>-0.906025297697461</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.404569052086567</v>
+        <v>-2.369388873207274</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.717432916981164</v>
+        <v>1.73854102430874</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.37491265030788</v>
+        <v>-10.33973247142859</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9755919154562784</v>
+        <v>-0.9615198439045614</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.579693469473111</v>
+        <v>-2.544513290593818</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.626913487296755</v>
+        <v>1.64802159462433</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.60936474432237</v>
+        <v>-10.57418456544308</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.07659191796367</v>
+        <v>-1.062519846411953</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.579693469473111</v>
+        <v>-2.544513290593818</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.619694322395159</v>
+        <v>1.640802429722734</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.71373947534882</v>
+        <v>-10.67855929646952</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.125014001148225</v>
+        <v>-1.110941929596508</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.684068200499557</v>
+        <v>-2.648888021620264</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.550397293005315</v>
+        <v>1.571505400332891</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.76652563094914</v>
+        <v>-10.73134545206985</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.145012673549799</v>
+        <v>-1.130940601998082</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.779743687081954</v>
+        <v>-2.744563508202661</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.494107790894433</v>
+        <v>1.515215898222009</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.89256242431743</v>
+        <v>-10.85738224543814</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.192733662268</v>
+        <v>-1.178661590716283</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.754492064272211</v>
+        <v>-2.719311885392918</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.511952493209393</v>
+        <v>1.533060600536969</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.84054691034862</v>
+        <v>-10.80536673146933</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.167937120994075</v>
+        <v>-1.153865049442357</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.754492064272211</v>
+        <v>-2.719311885392918</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.515942828895794</v>
+        <v>1.53705093622337</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.98221875207274</v>
+        <v>-10.94703857319345</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.226081084582464</v>
+        <v>-1.212009013030747</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.754492064272211</v>
+        <v>-2.719311885392918</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.514467601997052</v>
+        <v>1.535575709324628</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940715</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.93262790764791</v>
+        <v>-10.89744772876861</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.191191336647659</v>
+        <v>-1.177119265095941</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.704901219847378</v>
+        <v>-2.669721040968084</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.559275518816825</v>
+        <v>1.580383626144401</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.91982051464313</v>
+        <v>-10.85286134501705</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.199119513092432</v>
+        <v>-1.172335845241998</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.753756994856279</v>
+        <v>-2.706002154065726</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.516910920164801</v>
+        <v>1.545563824639133</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.69397536192372</v>
+        <v>-10.62701619229763</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.099202378968458</v>
+        <v>-1.072418711118024</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.711830319269115</v>
+        <v>-2.664075478478563</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.551645998553308</v>
+        <v>1.58029890302764</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.56939670558613</v>
+        <v>-10.50243753596004</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.048231771877363</v>
+        <v>-1.021448104026929</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.711830319269115</v>
+        <v>-2.664075478478563</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.552785143109367</v>
+        <v>1.581438047583698</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.62229199363041</v>
+        <v>-10.55533282400433</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.066756112932969</v>
+        <v>-1.039972445082536</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.706874973180669</v>
+        <v>-2.659120132390116</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.558392124924542</v>
+        <v>1.587045029398874</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.55015881834253</v>
+        <v>-10.48319964871645</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.032169138579181</v>
+        <v>-1.005385470728747</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.706874973180669</v>
+        <v>-2.659120132390116</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.564125829163179</v>
+        <v>1.59277873363751</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.47879242573289</v>
+        <v>-10.4118332561068</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.013359843929187</v>
+        <v>-0.9865761760787528</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.635508580571021</v>
+        <v>-2.587753739780469</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.597208402335103</v>
+        <v>1.625861306809434</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.21495555852882</v>
+        <v>-10.14799638890273</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9177085783604668</v>
+        <v>-0.8909249105100332</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.635508580571021</v>
+        <v>-2.587753739780469</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.587324921022195</v>
+        <v>1.615977825496526</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.947713757660418</v>
+        <v>-9.880754588034334</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8126464185124811</v>
+        <v>-0.7858627506620475</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.635508580571021</v>
+        <v>-2.587753739780469</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.585490360522821</v>
+        <v>1.614143264997153</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.849806718983928</v>
+        <v>-9.782847549357843</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7737839180153459</v>
+        <v>-0.7470002501649122</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.567522830710464</v>
+        <v>-2.519767989919912</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.625981495465694</v>
+        <v>1.654634399940025</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.82585317800797</v>
+        <v>-9.758894008381885</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7635339954794689</v>
+        <v>-0.7367503276290353</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.543569289734507</v>
+        <v>-2.495814448943955</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.641022126196762</v>
+        <v>1.669675030671094</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.561793239685173</v>
+        <v>-9.494834070059088</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6711703363121027</v>
+        <v>-0.6443866684616686</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.279509351411711</v>
+        <v>-2.231754510621159</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.786197773028688</v>
+        <v>1.814850677503019</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.854713616180335</v>
+        <v>-8.787754446554251</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3911255205704682</v>
+        <v>-0.3643418527200346</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.279509351411711</v>
+        <v>-2.231754510621159</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.783410739368387</v>
+        <v>1.812063643842718</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.814529317814145</v>
+        <v>-8.747570148188061</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3747081773361507</v>
+        <v>-0.3479245094857171</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.23932505304552</v>
+        <v>-2.191570212254968</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.807864942275943</v>
+        <v>1.836517846750274</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.651129446874783</v>
+        <v>-8.584170277248699</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3099814077396492</v>
+        <v>-0.2831977398892156</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.075925182106158</v>
+        <v>-2.028170341315605</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.905271686060317</v>
+        <v>1.933924590534648</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.417648224645184</v>
+        <v>-8.3506890550191</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2086644900099572</v>
+        <v>-0.1818808221595232</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.842443959876559</v>
+        <v>-1.794689119086007</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.053284848235929</v>
+        <v>2.08193775271026</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.26798183363767</v>
+        <v>-8.201022664011585</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1516901439199105</v>
+        <v>-0.1249064760694769</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.749540468634023</v>
+        <v>-1.701785627843471</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.106134732668491</v>
+        <v>2.134787637142822</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.135706360006782</v>
+        <v>-8.068747190380698</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1034124677205286</v>
+        <v>-0.07662879987009497</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.617264995003136</v>
+        <v>-1.569510154212584</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.18086750359405</v>
+        <v>2.209520408068381</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.94510668533363</v>
+        <v>-7.878147515707545</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02435753716363109</v>
+        <v>0.002426130686802974</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.426665320329983</v>
+        <v>-1.378910479539431</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.298042369085579</v>
+        <v>2.32669527355991</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.696106886650049</v>
+        <v>-7.629147717023964</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08814872353346015</v>
+        <v>0.1149323913838942</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.426665320329983</v>
+        <v>-1.378910479539431</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.310948710309237</v>
+        <v>2.339601614783569</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.801696876423153</v>
+        <v>-7.734737706797069</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08206320197500006</v>
+        <v>-0.05527953412456643</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.532255310103088</v>
+        <v>-1.484500469312536</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.119618786846156</v>
+        <v>2.148271691320487</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.82043177854175</v>
+        <v>-7.753472608915666</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.04101282094535286</v>
+        <v>-0.01422915309491879</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.537851319763219</v>
+        <v>-1.490096478972667</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.164805522927164</v>
+        <v>2.193458427401495</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.672491737134151</v>
+        <v>-7.605532567508066</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1017157270704807</v>
+        <v>-0.07493205922004664</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.517530403854662</v>
+        <v>-1.469775563064109</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.057119149784131</v>
+        <v>2.085772054258462</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.619522214880162</v>
+        <v>-7.552563045254078</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08924190442236313</v>
+        <v>-0.0624582365719295</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.464560881600673</v>
+        <v>-1.41680604081012</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.080186876883046</v>
+        <v>2.108839781357377</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.575973808109472</v>
+        <v>-7.509014638483388</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07878315380918011</v>
+        <v>-0.05199948595874648</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.464560881600673</v>
+        <v>-1.41680604081012</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.073226264787952</v>
+        <v>2.101879169262284</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.333825414655614</v>
+        <v>-7.266866245029529</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03253855795350624</v>
+        <v>0.05932222580393987</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.464560881600673</v>
+        <v>-1.41680604081012</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.087688619169096</v>
+        <v>2.116341523643427</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.225566277533092</v>
+        <v>-7.158607107907008</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07037433326170994</v>
+        <v>0.09715800111214357</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.464560881600673</v>
+        <v>-1.41680604081012</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.082220739628291</v>
+        <v>2.110873644102622</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.102275142715961</v>
+        <v>-7.035315973089877</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1171888811991391</v>
+        <v>0.1439725490495727</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.341269746783542</v>
+        <v>-1.29351490599299</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.153693514529146</v>
+        <v>2.182346419003477</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.081125943812518</v>
+        <v>-7.014166774186434</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1333495389978414</v>
+        <v>0.1601332068482755</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.320120547880099</v>
+        <v>-1.272365707089547</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.174084012108537</v>
+        <v>2.202736916582869</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.837360501829074</v>
+        <v>-6.770401332202989</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2266364241382699</v>
+        <v>0.2534200919887035</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.320120547880099</v>
+        <v>-1.272365707089547</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.169864720455588</v>
+        <v>2.198517624929919</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.735597681551779</v>
+        <v>-6.668638511925694</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2694658661692038</v>
+        <v>0.2962495340196378</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.30690147948767</v>
+        <v>-1.259146638697118</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.179920475411061</v>
+        <v>2.208573379885392</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.610674146585994</v>
+        <v>-6.41878811797662</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.31217735513922</v>
+        <v>0.3889317665829695</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.30690147948767</v>
+        <v>-1.259146638697118</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.172662550394763</v>
+        <v>2.201315454869095</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.434782054118562</v>
+        <v>-6.242896025509188</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3861333156468412</v>
+        <v>0.4628877270905911</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.30690147948767</v>
+        <v>-1.259146638697118</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.176261673915412</v>
+        <v>2.204914578389743</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.263335591096099</v>
+        <v>-6.071449562486724</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4680394069103806</v>
+        <v>0.5447938183541301</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.135455016465207</v>
+        <v>-1.087700175674655</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.292457057783444</v>
+        <v>2.321109962257775</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.038302591427276</v>
+        <v>-5.846416562817901</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5570730843942067</v>
+        <v>0.6338274958379566</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.910422016796384</v>
+        <v>-0.8626671760058319</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.426497335201034</v>
+        <v>2.455150239675365</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.974666849193341</v>
+        <v>-5.782780820583967</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5872221823420976</v>
+        <v>0.6639765937858475</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8467862745624495</v>
+        <v>-0.7990314337718973</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.469373581595712</v>
+        <v>2.498026486070044</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.9309046678875</v>
+        <v>-5.739018639278125</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.58592131364823</v>
+        <v>0.6626757250919799</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8467862745624495</v>
+        <v>-0.7990314337718973</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.450567840379508</v>
+        <v>2.479220744853839</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.69047417108264</v>
+        <v>-5.498588142473265</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6838365889950513</v>
+        <v>0.7605910004388012</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6063557777575892</v>
+        <v>-0.5586009369670371</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.596569215087301</v>
+        <v>2.625222119561633</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.618231602911445</v>
+        <v>-5.42634557430207</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7166629300983494</v>
+        <v>0.7934173415420993</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6063557777575892</v>
+        <v>-0.5586009369670371</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.600498528922122</v>
+        <v>2.629151433396453</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.565233280630057</v>
+        <v>-5.373347252020682</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7385408429282445</v>
+        <v>0.8152952543719945</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5510195187556504</v>
+        <v>-0.5032646779650982</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.634378868240625</v>
+        <v>2.663031772714956</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.45642839515033</v>
+        <v>-5.264542366540955</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.779060868340129</v>
+        <v>0.8558152797838789</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5510195187556504</v>
+        <v>-0.5032646779650982</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.631376939460618</v>
+        <v>2.66002984393495</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.236407597113319</v>
+        <v>-5.044521568503945</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8686482245655474</v>
+        <v>0.9454026360092973</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4097996736876701</v>
+        <v>-0.362044832897118</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.717687883512021</v>
+        <v>2.746340787986352</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.103539908050042</v>
+        <v>-4.911653879440667</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9376894829926816</v>
+        <v>1.014443894436432</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4097996736876701</v>
+        <v>-0.362044832897118</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.733582066313844</v>
+        <v>2.762234970788175</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.983366824685543</v>
+        <v>-4.791480796076169</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.986904560778783</v>
+        <v>1.063658972222533</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2896265903231712</v>
+        <v>-0.241871749532619</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.806831760772845</v>
+        <v>2.835484665247177</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.838694679585806</v>
+        <v>-4.646808650976431</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.054861521380118</v>
+        <v>1.131615932823868</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1449544452234338</v>
+        <v>-0.09719960443288161</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.903723150394128</v>
+        <v>2.932376054868459</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.898569506943498</v>
+        <v>-4.706683478334123</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.016949081838467</v>
+        <v>1.093703493282217</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2048292725811259</v>
+        <v>-0.1570744317905737</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.853835745380938</v>
+        <v>2.88248864985527</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.811770009164489</v>
+        <v>-4.619883980555114</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.074069374272637</v>
+        <v>1.150823785716387</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2048292725811259</v>
+        <v>-0.1570744317905737</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.876236238703504</v>
+        <v>2.904889143177836</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.814239715626295</v>
+        <v>-4.62235368701692</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.073153893061326</v>
+        <v>1.149908304505076</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.207298979042932</v>
+        <v>-0.1595441382523799</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.874826816199833</v>
+        <v>2.903479720674164</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.882609901950305</v>
+        <v>-4.69072387334093</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.056812741006424</v>
+        <v>1.133567152450174</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1980232800067171</v>
+        <v>-0.150268439216165</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.891399158096263</v>
+        <v>2.920052062570595</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.991148082866439</v>
+        <v>-4.799262054257064</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.003834177271862</v>
+        <v>1.080588588715612</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1980232800067171</v>
+        <v>-0.150268439216165</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.881835866728155</v>
+        <v>2.910488771202486</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.022141242195144</v>
+        <v>-4.83025521358577</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8161464785807668</v>
+        <v>0.8929008900245166</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1980232800067171</v>
+        <v>-0.150268439216165</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.706545431768542</v>
+        <v>2.735198336242873</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.846666982402676</v>
+        <v>-4.654780953793301</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.890903414489542</v>
+        <v>0.9676578259332917</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1980232800067171</v>
+        <v>-0.150268439216165</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.711112663760329</v>
+        <v>2.739765568234661</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.957603235043925</v>
+        <v>-4.76571720643455</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8222709421942493</v>
+        <v>0.8990253536379993</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1980232800067171</v>
+        <v>-0.150268439216165</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.686854692521536</v>
+        <v>2.715507596995868</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.965885309188983</v>
+        <v>-4.773999280579608</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8220894977561315</v>
+        <v>0.8988439091998814</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2063053541517755</v>
+        <v>-0.1585505133612233</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.685016833254407</v>
+        <v>2.713669737728738</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.90603268998526</v>
+        <v>-4.714146661375885</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8562029318697533</v>
+        <v>0.932957343313503</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2063053541517755</v>
+        <v>-0.1585505133612233</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.695189219686539</v>
+        <v>2.723842124160871</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.819789226958882</v>
+        <v>-4.627903198349507</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8856465876541646</v>
+        <v>0.9624009990979145</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2063053541517755</v>
+        <v>-0.1585505133612233</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.6901354902604</v>
+        <v>2.718788394734731</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.865096046357862</v>
+        <v>-4.673210017748487</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8592996353390983</v>
+        <v>0.9360540467828482</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2471155171610063</v>
+        <v>-0.1993606763704541</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.657425167899387</v>
+        <v>2.686078072373718</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.894129151060163</v>
+        <v>-4.702243122450788</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8482382664912793</v>
+        <v>0.9249926779350293</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2471155171610063</v>
+        <v>-0.1993606763704541</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.657977040932488</v>
+        <v>2.686629945406819</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.801318669609303</v>
+        <v>-4.609432640999929</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8146351509629888</v>
+        <v>0.8913895624067387</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1543050357101469</v>
+        <v>-0.1065501949195948</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.64293602169437</v>
+        <v>2.671588926168701</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.845708138938731</v>
+        <v>-4.653822110329356</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7987528391558187</v>
+        <v>0.8755072505995685</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1986945050395746</v>
+        <v>-0.1509396642490224</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.618175816021314</v>
+        <v>2.646828720495645</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.733036920702481</v>
+        <v>-4.541150892093106</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8388970349620417</v>
+        <v>0.9156514464057917</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.08602328680332438</v>
+        <v>-0.03826844601277224</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.680854255474787</v>
+        <v>2.709507159949118</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.620659919519808</v>
+        <v>-4.428773890910433</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8893391312657781</v>
+        <v>0.9660935427095281</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.08602328680332438</v>
+        <v>-0.03826844601277224</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.686345551305454</v>
+        <v>2.714998455779785</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.64844031742116</v>
+        <v>-4.456554288811786</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8897241738737762</v>
+        <v>0.966478585317526</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1138036847046774</v>
+        <v>-0.0660488439141253</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.681174514333181</v>
+        <v>2.709827418807513</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.731441598446439</v>
+        <v>-4.539555569837065</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6948793814643179</v>
+        <v>0.7716337929080677</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1323745692318512</v>
+        <v>-0.08461972844129906</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.50838770361753</v>
+        <v>2.537040608091861</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.84005567688977</v>
+        <v>-4.648169648280396</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.771583410806191</v>
+        <v>0.8483378222499409</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1323745692318512</v>
+        <v>-0.08461972844129906</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.628537364336736</v>
+        <v>2.657190268811068</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.926654259870873</v>
+        <v>-4.734768231261499</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7514570037160728</v>
+        <v>0.8282114151598228</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1323745692318512</v>
+        <v>-0.08461972844129906</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.643050390439059</v>
+        <v>2.671703294913391</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.888270597312722</v>
+        <v>-4.696384568703348</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.764229910081702</v>
+        <v>0.8409843215254518</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.09399090667370003</v>
+        <v>-0.04623606588314788</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.663500029316318</v>
+        <v>2.69215293379065</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.711154267277556</v>
+        <v>-4.519268238668182</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8318054709410703</v>
+        <v>0.9085598823848202</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.09399090667370003</v>
+        <v>-0.04623606588314788</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.66022905816162</v>
+        <v>2.688881962635952</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.756246512111102</v>
+        <v>-4.564360483501727</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8144519647695652</v>
+        <v>0.8912063762133151</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1558869498430898</v>
+        <v>-0.1081321090525377</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.6237748240219</v>
+        <v>2.652427728496231</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.576871090872334</v>
+        <v>-4.38498506226296</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8799891085714866</v>
+        <v>0.9567435200152365</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.0008898083276288604</v>
+        <v>0.048644649118181</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.711627854230745</v>
+        <v>2.740280758705076</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.62188530439294</v>
+        <v>-4.429999275783565</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8427908784948341</v>
+        <v>0.9195452899385839</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.02945908698697575</v>
+        <v>0.0182957538035764</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.674225972373572</v>
+        <v>2.702878876847903</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.888889814665375</v>
+        <v>-4.697003786056</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7416806367248059</v>
+        <v>0.8184350481685556</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2238221250299243</v>
+        <v>-0.1760672842393722</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.563299711886749</v>
+        <v>2.59195261636108</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.990087596102548</v>
+        <v>-4.798201567493173</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7004054460464382</v>
+        <v>0.7771598574901879</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2922309385752435</v>
+        <v>-0.2444760977846914</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.521458345656058</v>
+        <v>2.55011125013039</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.957612009931776</v>
+        <v>-4.765725981322401</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7109956420690637</v>
+        <v>0.7877500535128137</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2922309385752435</v>
+        <v>-0.2444760977846914</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.519058307210376</v>
+        <v>2.547711211684707</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.938573882224478</v>
+        <v>-4.746687853615104</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7151356123602275</v>
+        <v>0.7918900238039774</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3504145499064381</v>
+        <v>-0.3026597091158859</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.480672859619903</v>
+        <v>2.509325764094235</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.969700513375097</v>
+        <v>-4.777814484765722</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8802668288386608</v>
+        <v>0.9570212402824105</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3504145499064381</v>
+        <v>-0.3026597091158859</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.658254728558584</v>
+        <v>2.686907633032916</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.983567274709015</v>
+        <v>-4.79168124609964</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8755534532912272</v>
+        <v>0.952307864734977</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.388272466640261</v>
+        <v>-0.3405176258497088</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.636373307504424</v>
+        <v>2.665026211978755</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.003824573237972</v>
+        <v>-4.811938544628598</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8734590642765698</v>
+        <v>0.9502134757203198</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.388272466640261</v>
+        <v>-0.3405176258497088</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.64238183790135</v>
+        <v>2.671034742375681</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.85608160300297</v>
+        <v>-4.664195574393595</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.011708900162593</v>
+        <v>1.088463311606343</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2204651094053778</v>
+        <v>-0.1727102686148257</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.822218900034302</v>
+        <v>2.850871804508633</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.958096285534191</v>
+        <v>-4.766210256924817</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9736966486815852</v>
+        <v>1.050451060125335</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2204651094053778</v>
+        <v>-0.1727102686148257</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.825012521565783</v>
+        <v>2.853665426040114</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.951943579481407</v>
+        <v>-4.760057550872032</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9768200794943573</v>
+        <v>1.053574490938107</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2143124033525936</v>
+        <v>-0.1665575625620414</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.829366493589112</v>
+        <v>2.858019398063443</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.968752877631909</v>
+        <v>-4.776866849022534</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9691768369742668</v>
+        <v>1.045931248418017</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2311217015030952</v>
+        <v>-0.183366860712543</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.818361391438921</v>
+        <v>2.847014295913252</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.906454878855786</v>
+        <v>-4.714568850246412</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.060431590281537</v>
+        <v>1.137186001725287</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2311217015030952</v>
+        <v>-0.183366860712543</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.884696945235742</v>
+        <v>2.913349849710073</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.704664681190629</v>
+        <v>-4.512778652581254</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.849728541736998</v>
+        <v>0.9264829531807477</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.03310350933394079</v>
+        <v>0.01465133145661135</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.712088732926632</v>
+        <v>2.740741637400964</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.644773999548035</v>
+        <v>-4.452887970938661</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9439750467162105</v>
+        <v>1.02072945815996</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.02678717230865268</v>
+        <v>0.07454201309920483</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.818313374234364</v>
+        <v>2.846966278708695</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.74251454417301</v>
+        <v>-4.550628515563635</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9195065649822642</v>
+        <v>0.9962609764260142</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.0108978941756725</v>
+        <v>0.05865273496622464</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.823407543470619</v>
+        <v>2.852060447944951</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.918852304295939</v>
+        <v>-4.726966275686564</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8475074417577644</v>
+        <v>0.9242618532015141</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1654398659472569</v>
+        <v>-0.1176850251567048</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.716140868221533</v>
+        <v>2.744793772695865</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.847305981519062</v>
+        <v>-4.655419952909687</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8746175889084435</v>
+        <v>0.9513720003521935</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1654398659472569</v>
+        <v>-0.1176850251567048</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.714632486261462</v>
+        <v>2.743285390735793</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.802932849880493</v>
+        <v>-4.611046821271119</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8922297089993072</v>
+        <v>0.9689841204430572</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1210667343086883</v>
+        <v>-0.07331189351813616</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.741119232680039</v>
+        <v>2.769772137154371</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.794978879585721</v>
+        <v>-4.603092850976346</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8954112971172161</v>
+        <v>0.9721657085609661</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1210667343086883</v>
+        <v>-0.07331189351813616</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.741119232680039</v>
+        <v>2.769772137154371</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.747323149024665</v>
+        <v>-4.555437120415291</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9208553463694431</v>
+        <v>0.9976097578131931</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.07341100374763265</v>
+        <v>-0.02565616295708051</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.776094428044477</v>
+        <v>2.804747332518808</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.619638839230369</v>
+        <v>-4.427752810620994</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9768214436618865</v>
+        <v>1.053575855105636</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.05427330604666381</v>
+        <v>0.1020281468372159</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.85759738729578</v>
+        <v>2.886250291770111</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.680305429632758</v>
+        <v>-4.488419401023384</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9393094799768029</v>
+        <v>1.016063891420553</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.02742501067186986</v>
+        <v>0.02032983011868228</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.795333069740532</v>
+        <v>2.823985974214863</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.63546702802436</v>
+        <v>-4.443580999414985</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9613425432307909</v>
+        <v>1.038096954674541</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.02288157772700039</v>
+        <v>0.02487326306355175</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.802156832118082</v>
+        <v>2.830809736592414</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.736225663781358</v>
+        <v>-4.544339635171983</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9252000285590696</v>
+        <v>1.00195444000282</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1117071464540058</v>
+        <v>-0.06395230566345367</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.753022430512957</v>
+        <v>2.781675334987288</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163217</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.692022826695458</v>
+        <v>-4.500136798086083</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9487607659212669</v>
+        <v>1.025515177365017</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.06750430936810536</v>
+        <v>-0.01974946857755322</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.785423735292334</v>
+        <v>2.814076639766665</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022902</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.7290018543589</v>
+        <v>-4.46067937315821</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9323791553251375</v>
+        <v>1.039708147805414</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.03053040757677483</v>
+        <v>-0.007103844009110016</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.80601807683638</v>
+        <v>2.820074014976979</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042138</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.749059933223741</v>
+        <v>-4.480737452023051</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9756036889622408</v>
+        <v>1.082932681442517</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.03053040757677483</v>
+        <v>-0.007103844009110016</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.85726584201942</v>
+        <v>2.871321780160019</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078277</v>
+        <v>3.865367715078279</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.709129260045851</v>
+        <v>-4.44080677884516</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9900166628276501</v>
+        <v>1.097345655307926</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.009400265601115509</v>
+        <v>0.03282682916878032</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.879664950520407</v>
+        <v>2.893720888661006</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232394</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.668658912483146</v>
+        <v>-4.400336431282455</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.001153030091002</v>
+        <v>1.108482022571278</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.04987061316382047</v>
+        <v>0.07329717673148528</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.8988953872963</v>
+        <v>2.912951325436899</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162108</v>
+        <v>3.84257639416211</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.60343473135594</v>
+        <v>-4.33511225015525</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.044430106634589</v>
+        <v>1.151759099114865</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1150947942910261</v>
+        <v>0.1385213578586909</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.955217300065328</v>
+        <v>2.969273238205927</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639814</v>
+        <v>3.840090220639816</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.653929021712996</v>
+        <v>-4.385606540512306</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.020193362791047</v>
+        <v>1.127522355271323</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.07007405716495185</v>
+        <v>0.09350062073261667</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.924165830088964</v>
+        <v>2.938221768229563</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749916</v>
+        <v>3.845198842749918</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.674040677747705</v>
+        <v>-4.405718196547014</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.013405492708404</v>
+        <v>1.12073448518868</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.08110140216237105</v>
+        <v>0.1045279657300359</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.932039029418656</v>
+        <v>2.946094967559255</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393542</v>
+        <v>3.828690479393543</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.771721257020351</v>
+        <v>-4.50339877581966</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.134891032020556</v>
+        <v>1.242220024500833</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.02960179317781775</v>
+        <v>-0.006175229610152932</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.026174883235754</v>
+        <v>3.040230821376352</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714879</v>
+        <v>3.813251854714881</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.747929688414208</v>
+        <v>-4.479607207213517</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.264520568680831</v>
+        <v>1.371849561161107</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.00581022457167546</v>
+        <v>0.01761633899598936</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.160562733617256</v>
+        <v>3.174618671757855</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756008</v>
+        <v>3.81425976175601</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.784684106975931</v>
+        <v>-4.516361625775239</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.241526777270001</v>
+        <v>1.348855769750277</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.00581022457167546</v>
+        <v>0.01761633899598936</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.152270709631115</v>
+        <v>3.166326647771714</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654183</v>
+        <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.780349803918883</v>
+        <v>-4.512027322718192</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.241453694076599</v>
+        <v>1.348782686556876</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1458398787475285</v>
+        <v>0.1692664423151933</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.241453967206417</v>
+        <v>3.255509905347016</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717113</v>
+        <v>3.796293177717115</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.7714573425256</v>
+        <v>-4.503134861324908</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.262565084360704</v>
+        <v>1.36989407684098</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1458398787475285</v>
+        <v>0.1692664423151933</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.259008372933208</v>
+        <v>3.273064311073807</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702623</v>
+        <v>3.794453975702625</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.939933459495477</v>
+        <v>-4.671610978294786</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.187029684977337</v>
+        <v>1.294358677457613</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1178920430309477</v>
+        <v>0.1413186065986125</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.234094718907844</v>
+        <v>3.248150657048443</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.753242104809164</v>
+        <v>3.752833312076606</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.106915025327306</v>
+        <v>3.191589728346512</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.939933459495477</v>
+        <v>-4.671610978294786</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.187029684977337</v>
+        <v>1.294358677457613</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1178920430309477</v>
+        <v>0.1413186065986125</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.099978822313674</v>
+        <v>3.184653525332879</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240616.xlsx
+++ b/tame_output/ON/bt/strategyON_20240616.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>6.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.8%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.3%</t>
+          <t>125.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-51.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.3%</t>
+          <t>452.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-628.7%</t>
+          <t>-621.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-41.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-271.7%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-246.8%</t>
+          <t>-243.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>1086.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-213.9%</t>
+          <t>-137.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-209.9%</t>
+          <t>-202.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-127.6%</t>
+          <t>-128.9%</t>
         </is>
       </c>
     </row>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937495</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141698</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729888</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49997173944063</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608597</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764393</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367402532254</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158918</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.85286134501705</v>
+        <v>-10.88464033576384</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.172335845241998</v>
+        <v>-1.185047441540715</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.706002154065726</v>
+        <v>-2.718576815976986</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.545563824639133</v>
+        <v>1.538019027492377</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68516138161528</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.62701619229763</v>
+        <v>-10.65879518304443</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.072418711118024</v>
+        <v>-1.085130307416742</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.664075478478563</v>
+        <v>-2.676650140389822</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.58029890302764</v>
+        <v>1.572754105880884</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812099</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.50243753596004</v>
+        <v>-10.53421652670684</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.021448104026929</v>
+        <v>-1.034159700325647</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.664075478478563</v>
+        <v>-2.676650140389822</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.581438047583698</v>
+        <v>1.573893250436943</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.55533282400433</v>
+        <v>-10.58711181475112</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.039972445082536</v>
+        <v>-1.052684041381253</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.659120132390116</v>
+        <v>-2.671694794301376</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.587045029398874</v>
+        <v>1.579500232252118</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.48319964871645</v>
+        <v>-10.51497863946324</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.005385470728747</v>
+        <v>-1.018097067027464</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.659120132390116</v>
+        <v>-2.671694794301376</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.59277873363751</v>
+        <v>1.585233936490755</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955323</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.4118332561068</v>
+        <v>-10.4436122468536</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9865761760787528</v>
+        <v>-0.9992877723774711</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.587753739780469</v>
+        <v>-2.600328401691728</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.625861306809434</v>
+        <v>1.618316509662678</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232407</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.14799638890273</v>
+        <v>-10.17977537964953</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8909249105100332</v>
+        <v>-0.9036365068087506</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.587753739780469</v>
+        <v>-2.600328401691728</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.615977825496526</v>
+        <v>1.608433028349771</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436223</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.880754588034334</v>
+        <v>-9.912533578781128</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7858627506620475</v>
+        <v>-0.7985743469607649</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.587753739780469</v>
+        <v>-2.600328401691728</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.614143264997153</v>
+        <v>1.606598467850397</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311942</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.782847549357843</v>
+        <v>-9.814626540104637</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7470002501649122</v>
+        <v>-0.7597118464636297</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.519767989919912</v>
+        <v>-2.532342651831171</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.654634399940025</v>
+        <v>1.64708960279327</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097238</v>
+        <v>3.800829354097239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.758894008381885</v>
+        <v>-9.790672999128679</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7367503276290353</v>
+        <v>-0.7494619239277527</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.495814448943955</v>
+        <v>-2.508389110855214</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.669675030671094</v>
+        <v>1.662130233524338</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.494834070059088</v>
+        <v>-9.526613060805882</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6443866684616686</v>
+        <v>-0.6570982647603865</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.231754510621159</v>
+        <v>-2.244329172532418</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.814850677503019</v>
+        <v>1.807305880356264</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.787754446554251</v>
+        <v>-8.819533437301045</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3643418527200346</v>
+        <v>-0.377053449018752</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.231754510621159</v>
+        <v>-2.244329172532418</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.812063643842718</v>
+        <v>1.804518846695963</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.747570148188061</v>
+        <v>-8.779349138934855</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3479245094857171</v>
+        <v>-0.3606361057844345</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.191570212254968</v>
+        <v>-2.204144874166227</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.836517846750274</v>
+        <v>1.828973049603519</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626468</v>
+        <v>3.856161751626469</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.584170277248699</v>
+        <v>-8.615949267995493</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2831977398892156</v>
+        <v>-0.295909336187933</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.028170341315605</v>
+        <v>-2.040745003226864</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.933924590534648</v>
+        <v>1.926379793387893</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291806</v>
+        <v>3.787330429291807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.3506890550191</v>
+        <v>-8.382468045765894</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1818808221595232</v>
+        <v>-0.194592418458241</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.794689119086007</v>
+        <v>-1.807263780997266</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.08193775271026</v>
+        <v>2.074392955563504</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785783</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.201022664011585</v>
+        <v>-8.232801654758379</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1249064760694769</v>
+        <v>-0.1376180723681943</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.701785627843471</v>
+        <v>-1.71436028975473</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.134787637142822</v>
+        <v>2.127242839996067</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390422</v>
+        <v>3.763182248390424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.068747190380698</v>
+        <v>-8.100526181127492</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.07662879987009497</v>
+        <v>-0.0893403961688124</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.569510154212584</v>
+        <v>-1.582084816123843</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.209520408068381</v>
+        <v>2.201975610921626</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105947</v>
+        <v>3.784718794105949</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.878147515707545</v>
+        <v>-7.909926506454339</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.002426130686802974</v>
+        <v>-0.0102854656119149</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.378910479539431</v>
+        <v>-1.39148514145069</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.32669527355991</v>
+        <v>2.319150476413154</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960982</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.629147717023964</v>
+        <v>-7.660926707770758</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1149323913838942</v>
+        <v>0.1022207950851763</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.378910479539431</v>
+        <v>-1.39148514145069</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.339601614783569</v>
+        <v>2.332056817636813</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69293185560764</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.734737706797069</v>
+        <v>-7.766516697543863</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.05527953412456643</v>
+        <v>-0.06799113042328386</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.484500469312536</v>
+        <v>-1.497075131223795</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.148271691320487</v>
+        <v>2.140726894173732</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987898</v>
+        <v>3.770422583987899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.753472608915666</v>
+        <v>-7.653768889318053</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.01422915309491879</v>
+        <v>0.0256523347441262</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.490096478972667</v>
+        <v>-1.395890368562883</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.193458427401495</v>
+        <v>2.249982093647365</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.605532567508066</v>
+        <v>-7.505828847910454</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.07493205922004664</v>
+        <v>-0.03505057138100165</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.469775563064109</v>
+        <v>-1.375569452654326</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.085772054258462</v>
+        <v>2.142295720504332</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.7235662294092</v>
+        <v>3.723566229409201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.552563045254078</v>
+        <v>-7.452859325656465</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.0624582365719295</v>
+        <v>-0.02257674873288451</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.41680604081012</v>
+        <v>-1.322599930400337</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.108839781357377</v>
+        <v>2.165363447603247</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098104</v>
+        <v>3.729969716098105</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.509014638483388</v>
+        <v>-7.409310918885775</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.05199948595874648</v>
+        <v>-0.01211799811970149</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.41680604081012</v>
+        <v>-1.322599930400337</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.101879169262284</v>
+        <v>2.158402835508154</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493415</v>
+        <v>3.782922533493416</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.266866245029529</v>
+        <v>-7.167162525431917</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.05932222580393987</v>
+        <v>0.09920371364298486</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.41680604081012</v>
+        <v>-1.322599930400337</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.116341523643427</v>
+        <v>2.172865189889297</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722811</v>
+        <v>3.828551486722812</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.158607107907008</v>
+        <v>-7.058903388309395</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.09715800111214357</v>
+        <v>0.1370394889511886</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.41680604081012</v>
+        <v>-1.322599930400337</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.110873644102622</v>
+        <v>2.167397310348492</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792041</v>
+        <v>3.828052928792042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.035315973089877</v>
+        <v>-6.935612253492264</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1439725490495727</v>
+        <v>0.1838540368886177</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.29351490599299</v>
+        <v>-1.199308795583207</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.182346419003477</v>
+        <v>2.238870085249347</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919902</v>
+        <v>3.812453678919903</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.014166774186434</v>
+        <v>-6.914463054588821</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1601332068482755</v>
+        <v>0.2000146946873205</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.272365707089547</v>
+        <v>-1.178159596679763</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.202736916582869</v>
+        <v>2.259260582828738</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318088</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.770401332202989</v>
+        <v>-6.670697612605377</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2534200919887035</v>
+        <v>0.2933015798277485</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.272365707089547</v>
+        <v>-1.178159596679763</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.198517624929919</v>
+        <v>2.255041291175789</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057521</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.668638511925694</v>
+        <v>-6.568934792328082</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2962495340196378</v>
+        <v>0.3361310218586828</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.259146638697118</v>
+        <v>-1.164940528287335</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.208573379885392</v>
+        <v>2.265097046131262</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427918</v>
+        <v>3.826354974279181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.41878811797662</v>
+        <v>-6.319084398379007</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3889317665829695</v>
+        <v>0.4288132544220145</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.259146638697118</v>
+        <v>-1.164940528287335</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.201315454869095</v>
+        <v>2.257839121114964</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.242896025509188</v>
+        <v>-6.143192305911574</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4628877270905911</v>
+        <v>0.5027692149296366</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.259146638697118</v>
+        <v>-1.164940528287335</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.204914578389743</v>
+        <v>2.261438244635613</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.071449562486724</v>
+        <v>-5.971745842889111</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5447938183541301</v>
+        <v>0.5846753061931755</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.087700175674655</v>
+        <v>-0.9934940652648715</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.321109962257775</v>
+        <v>2.377633628503645</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.846416562817901</v>
+        <v>-5.746712843220288</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6338274958379566</v>
+        <v>0.673708983677002</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8626671760058319</v>
+        <v>-0.7684610655960487</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.455150239675365</v>
+        <v>2.511673905921235</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.782780820583967</v>
+        <v>-5.683077100986353</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6639765937858475</v>
+        <v>0.7038580816248929</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7990314337718973</v>
+        <v>-0.7048253233621141</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.498026486070044</v>
+        <v>2.554550152315914</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.739018639278125</v>
+        <v>-5.639314919680512</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6626757250919799</v>
+        <v>0.7025572129310254</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7990314337718973</v>
+        <v>-0.7048253233621141</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.479220744853839</v>
+        <v>2.535744411099709</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.498588142473265</v>
+        <v>-5.398884422875652</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7605910004388012</v>
+        <v>0.8004724882778467</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5586009369670371</v>
+        <v>-0.4643948265572538</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.625222119561633</v>
+        <v>2.681745785807502</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.42634557430207</v>
+        <v>-5.326641854704457</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7934173415420993</v>
+        <v>0.8332988293811447</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5586009369670371</v>
+        <v>-0.4643948265572538</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.629151433396453</v>
+        <v>2.685675099642323</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.373347252020682</v>
+        <v>-5.273643532423069</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8152952543719945</v>
+        <v>0.8551767422110399</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5032646779650982</v>
+        <v>-0.409058567555315</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.663031772714956</v>
+        <v>2.719555438960826</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.264542366540955</v>
+        <v>-5.164838646943342</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8558152797838789</v>
+        <v>0.8956967676229244</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5032646779650982</v>
+        <v>-0.409058567555315</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.66002984393495</v>
+        <v>2.71655351018082</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675932</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.044521568503945</v>
+        <v>-4.944817848906331</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9454026360092973</v>
+        <v>0.9852841238483425</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.362044832897118</v>
+        <v>-0.2678387224873348</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.746340787986352</v>
+        <v>2.802864454232222</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539943</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.911653879440667</v>
+        <v>-4.811950159843054</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.014443894436432</v>
+        <v>1.054325382275477</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.362044832897118</v>
+        <v>-0.2678387224873348</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.762234970788175</v>
+        <v>2.818758637034045</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496256</v>
+        <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.791480796076169</v>
+        <v>-4.691777076478555</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.063658972222533</v>
+        <v>1.103540460061578</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.241871749532619</v>
+        <v>-0.1476656391228358</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.835484665247177</v>
+        <v>2.892008331493046</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576992</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.646808650976431</v>
+        <v>-4.547104931378818</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.131615932823868</v>
+        <v>1.171497420662913</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.09719960443288161</v>
+        <v>-0.002993494023098398</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.932376054868459</v>
+        <v>2.988899721114329</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942098</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.706683478334123</v>
+        <v>-4.60697975873651</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.093703493282217</v>
+        <v>1.133584981121262</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1570744317905737</v>
+        <v>-0.06286832138079052</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.88248864985527</v>
+        <v>2.939012316101139</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264747767451</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.619883980555114</v>
+        <v>-4.520180260957501</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.150823785716387</v>
+        <v>1.190705273555432</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1570744317905737</v>
+        <v>-0.06286832138079052</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.904889143177836</v>
+        <v>2.961412809423706</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.62235368701692</v>
+        <v>-4.522649967419307</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.149908304505076</v>
+        <v>1.189789792344122</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1595441382523799</v>
+        <v>-0.06533802784259668</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.903479720674164</v>
+        <v>2.960003386920034</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.69072387334093</v>
+        <v>-4.591020153743317</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.133567152450174</v>
+        <v>1.173448640289219</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.150268439216165</v>
+        <v>-0.05606232880638173</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.920052062570595</v>
+        <v>2.976575728816465</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.799262054257064</v>
+        <v>-4.699558334659451</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.080588588715612</v>
+        <v>1.120470076554657</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.150268439216165</v>
+        <v>-0.05606232880638173</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.910488771202486</v>
+        <v>2.967012437448356</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417698</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.83025521358577</v>
+        <v>-4.730551493988156</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8929008900245166</v>
+        <v>0.9327823778635618</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.150268439216165</v>
+        <v>-0.05606232880638173</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.735198336242873</v>
+        <v>2.791722002488743</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.654780953793301</v>
+        <v>-4.555077234195688</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9676578259332917</v>
+        <v>1.007539313772337</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.150268439216165</v>
+        <v>-0.05606232880638173</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.739765568234661</v>
+        <v>2.796289234480531</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.76571720643455</v>
+        <v>-4.666013486836937</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8990253536379993</v>
+        <v>0.9389068414770447</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.150268439216165</v>
+        <v>-0.05606232880638173</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.715507596995868</v>
+        <v>2.772031263241738</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111288</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.773999280579608</v>
+        <v>-4.674295560981995</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8988439091998814</v>
+        <v>0.9387253970389269</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1585505133612233</v>
+        <v>-0.06434440295144012</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.713669737728738</v>
+        <v>2.770193403974608</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264157</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.714146661375885</v>
+        <v>-4.614442941778272</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.932957343313503</v>
+        <v>0.9728388311525484</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1585505133612233</v>
+        <v>-0.06434440295144012</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.723842124160871</v>
+        <v>2.780365790406741</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742293</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.627903198349507</v>
+        <v>-4.528199478751894</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9624009990979145</v>
+        <v>1.00228248693696</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1585505133612233</v>
+        <v>-0.06434440295144012</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.718788394734731</v>
+        <v>2.775312060980601</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316041</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.673210017748487</v>
+        <v>-4.573506298150874</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9360540467828482</v>
+        <v>0.9759355346218934</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1993606763704541</v>
+        <v>-0.1051545659606709</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.686078072373718</v>
+        <v>2.742601738619588</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803185</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.702243122450788</v>
+        <v>-4.602539402853175</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9249926779350293</v>
+        <v>0.9648741657740745</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1993606763704541</v>
+        <v>-0.1051545659606709</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.686629945406819</v>
+        <v>2.743153611652689</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809493</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.609432640999929</v>
+        <v>-4.509728921402315</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8913895624067387</v>
+        <v>0.9312710502457842</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1065501949195948</v>
+        <v>-0.01234408450981156</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.671588926168701</v>
+        <v>2.728112592414571</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.74828581656042</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.653822110329356</v>
+        <v>-4.554118390731743</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8755072505995685</v>
+        <v>0.9153887384386139</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1509396642490224</v>
+        <v>-0.05673355383923923</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.646828720495645</v>
+        <v>2.703352386741515</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472732</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.541150892093106</v>
+        <v>-4.441447172495493</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9156514464057917</v>
+        <v>0.9555329342448369</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.03826844601277224</v>
+        <v>0.05593766439701098</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.709507159949118</v>
+        <v>2.766030826194988</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798532</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.428773890910433</v>
+        <v>-4.32907017131282</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9660935427095281</v>
+        <v>1.005975030548573</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.03826844601277224</v>
+        <v>0.05593766439701098</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.714998455779785</v>
+        <v>2.771522122025655</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498859</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.456554288811786</v>
+        <v>-4.356850569214172</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.966478585317526</v>
+        <v>1.006360073156571</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.0660488439141253</v>
+        <v>0.02815726649565792</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.709827418807513</v>
+        <v>2.766351085053383</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.539555569837065</v>
+        <v>-4.389661138885971</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7716337929080677</v>
+        <v>0.8315915652885051</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.08461972844129906</v>
+        <v>-0.03565117495428566</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.537040608091861</v>
+        <v>2.56642174018407</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729265</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.648169648280396</v>
+        <v>-4.498275217329303</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8483378222499409</v>
+        <v>0.9082955946303781</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.08461972844129906</v>
+        <v>-0.03565117495428566</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.657190268811068</v>
+        <v>2.686571400903275</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190763</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.734768231261499</v>
+        <v>-4.584873800310405</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8282114151598228</v>
+        <v>0.88816918754026</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.08461972844129906</v>
+        <v>-0.03565117495428566</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.671703294913391</v>
+        <v>2.701084427005598</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.74117406991342</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.696384568703348</v>
+        <v>-4.546490137752254</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8409843215254518</v>
+        <v>0.9009420939058892</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.04623606588314788</v>
+        <v>0.002732487603865519</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.69215293379065</v>
+        <v>2.721534065882858</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.75114719753248</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.519268238668182</v>
+        <v>-4.369373807717088</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9085598823848202</v>
+        <v>0.9685176547652574</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.04623606588314788</v>
+        <v>0.002732487603865519</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.688881962635952</v>
+        <v>2.71826309472816</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793897</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.564360483501727</v>
+        <v>-4.414466052550634</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8912063762133151</v>
+        <v>0.9511641485937523</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1081321090525377</v>
+        <v>-0.05916355556552427</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.652427728496231</v>
+        <v>2.681808860588439</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011232</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.38498506226296</v>
+        <v>-4.235090631311866</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9567435200152365</v>
+        <v>1.016701292395674</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.048644649118181</v>
+        <v>0.0976132026051944</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.740280758705076</v>
+        <v>2.769661890797285</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.429999275783565</v>
+        <v>-4.280104844832472</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9195452899385839</v>
+        <v>0.9795030623190213</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.0182957538035764</v>
+        <v>0.0672643072905898</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.702878876847903</v>
+        <v>2.732260008940111</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.697003786056</v>
+        <v>-4.547109355104907</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8184350481685556</v>
+        <v>0.878392820548993</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1760672842393722</v>
+        <v>-0.1270987307523588</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.59195261636108</v>
+        <v>2.621333748453288</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760806</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.798201567493173</v>
+        <v>-4.64830713654208</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7771598574901879</v>
+        <v>0.8371176298706253</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2444760977846914</v>
+        <v>-0.195507544297678</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.55011125013039</v>
+        <v>2.579492382222598</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815451</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.765725981322401</v>
+        <v>-4.615831550371308</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7877500535128137</v>
+        <v>0.8477078258932509</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2444760977846914</v>
+        <v>-0.195507544297678</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.547711211684707</v>
+        <v>2.577092343776915</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.746687853615104</v>
+        <v>-4.59679342266401</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7918900238039774</v>
+        <v>0.8518477961844146</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3026597091158859</v>
+        <v>-0.2536911556288725</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.509325764094235</v>
+        <v>2.538706896186443</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131247</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.777814484765722</v>
+        <v>-4.627920053814629</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9570212402824105</v>
+        <v>1.016979012662848</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3026597091158859</v>
+        <v>-0.2536911556288725</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.686907633032916</v>
+        <v>2.716288765125123</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.79168124609964</v>
+        <v>-4.641786815148547</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.952307864734977</v>
+        <v>1.012265637115414</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3405176258497088</v>
+        <v>-0.2915490723626954</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.665026211978755</v>
+        <v>2.694407344070963</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.811938544628598</v>
+        <v>-4.662044113677505</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9502134757203198</v>
+        <v>1.010171248100757</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3405176258497088</v>
+        <v>-0.2915490723626954</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.671034742375681</v>
+        <v>2.700415874467889</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.664195574393595</v>
+        <v>-4.514301143442502</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.088463311606343</v>
+        <v>1.14842108398678</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1727102686148257</v>
+        <v>-0.1237417151278123</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.850871804508633</v>
+        <v>2.880252936600841</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.766210256924817</v>
+        <v>-4.616315825973723</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.050451060125335</v>
+        <v>1.110408832505772</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1727102686148257</v>
+        <v>-0.1237417151278123</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.853665426040114</v>
+        <v>2.883046558132322</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.760057550872032</v>
+        <v>-4.610163119920939</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.053574490938107</v>
+        <v>1.113532263318544</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1665575625620414</v>
+        <v>-0.117589009075028</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.858019398063443</v>
+        <v>2.887400530155651</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.776866849022534</v>
+        <v>-4.626972418071441</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.045931248418017</v>
+        <v>1.105889020798454</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.183366860712543</v>
+        <v>-0.1343983072255296</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.847014295913252</v>
+        <v>2.87639542800546</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.714568850246412</v>
+        <v>-4.564674419295319</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.137186001725287</v>
+        <v>1.197143774105724</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.183366860712543</v>
+        <v>-0.1343983072255296</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.913349849710073</v>
+        <v>2.942730981802281</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.512778652581254</v>
+        <v>-4.362884221630161</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9264829531807477</v>
+        <v>0.9864407255611851</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.01465133145661135</v>
+        <v>0.06361988494362475</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.740741637400964</v>
+        <v>2.770122769493172</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.452887970938661</v>
+        <v>-4.302993539987567</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.02072945815996</v>
+        <v>1.080687230540398</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.07454201309920483</v>
+        <v>0.1235105665862182</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.846966278708695</v>
+        <v>2.876347410800903</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.550628515563635</v>
+        <v>-4.400734084612542</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9962609764260142</v>
+        <v>1.056218748806451</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.05865273496622464</v>
+        <v>0.107621288453238</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.852060447944951</v>
+        <v>2.881441580037158</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.726966275686564</v>
+        <v>-4.577071844735471</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9242618532015141</v>
+        <v>0.9842196255819515</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1176850251567048</v>
+        <v>-0.06871647166969136</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.744793772695865</v>
+        <v>2.774174904788072</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.655419952909687</v>
+        <v>-4.505525521958594</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9513720003521935</v>
+        <v>1.011329772732631</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1176850251567048</v>
+        <v>-0.06871647166969136</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.743285390735793</v>
+        <v>2.772666522828001</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.611046821271119</v>
+        <v>-4.461152390320025</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9689841204430572</v>
+        <v>1.028941892823494</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.07331189351813616</v>
+        <v>-0.02434334003112276</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.769772137154371</v>
+        <v>2.799153269246578</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.603092850976346</v>
+        <v>-4.453198420025253</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9721657085609661</v>
+        <v>1.032123480941403</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.07331189351813616</v>
+        <v>-0.02434334003112276</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.769772137154371</v>
+        <v>2.799153269246578</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.555437120415291</v>
+        <v>-4.405542689464197</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9976097578131931</v>
+        <v>1.05756753019363</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.02565616295708051</v>
+        <v>0.02331239052993289</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.804747332518808</v>
+        <v>2.834128464611017</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.427752810620994</v>
+        <v>-4.277858379669901</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.053575855105636</v>
+        <v>1.113533627486074</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.1020281468372159</v>
+        <v>0.1509967003242293</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.886250291770111</v>
+        <v>2.915631423862319</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.488419401023384</v>
+        <v>-4.338524970072291</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.016063891420553</v>
+        <v>1.07602166380099</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.02032983011868228</v>
+        <v>0.06929838360569568</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.823985974214863</v>
+        <v>2.853367106307071</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.443580999414985</v>
+        <v>-4.293686568463892</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.038096954674541</v>
+        <v>1.098054727054978</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.02487326306355175</v>
+        <v>0.07384181655056515</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.830809736592414</v>
+        <v>2.860190868684621</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.544339635171983</v>
+        <v>-4.39444520422089</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.00195444000282</v>
+        <v>1.061912212383257</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.06395230566345367</v>
+        <v>-0.01498375217644027</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.781675334987288</v>
+        <v>2.811056467079496</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.500136798086083</v>
+        <v>-4.35024236713499</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.025515177365017</v>
+        <v>1.085472949745454</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.01974946857755322</v>
+        <v>0.02921908490946018</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.814076639766665</v>
+        <v>2.843457771858874</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022902</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.46067937315821</v>
+        <v>-4.387221394798432</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.039708147805414</v>
+        <v>1.069091339149325</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.007103844009110016</v>
+        <v>0.06619298670079071</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.820074014976979</v>
+        <v>2.86405211340292</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042138</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.480737452023051</v>
+        <v>-4.407279473663273</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.082932681442517</v>
+        <v>1.112315872786428</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.007103844009110016</v>
+        <v>0.06619298670079071</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.871321780160019</v>
+        <v>2.915299878585959</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078279</v>
+        <v>3.865367715078277</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.44080677884516</v>
+        <v>-4.367348800485383</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.097345655307926</v>
+        <v>1.126728846651837</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.03282682916878032</v>
+        <v>0.1061236598786811</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.893720888661006</v>
+        <v>2.937698987086947</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.400336431282455</v>
+        <v>-4.326878452922678</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.108482022571278</v>
+        <v>1.137865213915189</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.07329717673148528</v>
+        <v>0.146594007441386</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.912951325436899</v>
+        <v>2.95692942386284</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84257639416211</v>
+        <v>3.842576394162109</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.33511225015525</v>
+        <v>-4.261654271795472</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.151759099114865</v>
+        <v>1.181142290458776</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1385213578586909</v>
+        <v>0.2118181885685916</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.969273238205927</v>
+        <v>3.013251336631868</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639816</v>
+        <v>3.840090220639815</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.385606540512306</v>
+        <v>-4.312148562152529</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.127522355271323</v>
+        <v>1.156905546615234</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.09350062073261667</v>
+        <v>0.1667974514425174</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.938221768229563</v>
+        <v>2.982199866655504</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.405718196547014</v>
+        <v>-4.332260218187237</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.12073448518868</v>
+        <v>1.150117676532591</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1045279657300359</v>
+        <v>0.1778247964399366</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.946094967559255</v>
+        <v>2.990073065985195</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.50339877581966</v>
+        <v>-4.429940797459883</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.242220024500833</v>
+        <v>1.271603215844743</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.006175229610152932</v>
+        <v>0.0671216010997478</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.040230821376352</v>
+        <v>3.084208919802293</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.479607207213517</v>
+        <v>-4.40614922885374</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.371849561161107</v>
+        <v>1.401232752505018</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.01761633899598936</v>
+        <v>0.09091316970589008</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.174618671757855</v>
+        <v>3.218596770183796</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.516361625775239</v>
+        <v>-4.442903647415463</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.348855769750277</v>
+        <v>1.378238961094188</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.01761633899598936</v>
+        <v>0.09091316970589008</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.166326647771714</v>
+        <v>3.210304746197655</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.512027322718192</v>
+        <v>-4.438569344358415</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.348782686556876</v>
+        <v>1.378165877900786</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1692664423151933</v>
+        <v>0.242563273025094</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.255509905347016</v>
+        <v>3.299488003772956</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.503134861324908</v>
+        <v>-4.429676882965132</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.36989407684098</v>
+        <v>1.399277268184891</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1692664423151933</v>
+        <v>0.242563273025094</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.273064311073807</v>
+        <v>3.317042409499748</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702625</v>
+        <v>3.794453975702626</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.671610978294786</v>
+        <v>-4.598152999935009</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.294358677457613</v>
+        <v>1.323741868801524</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1413186065986125</v>
+        <v>0.2146154373085132</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.248150657048443</v>
+        <v>3.292128755474383</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.752833312076606</v>
+        <v>3.718636832441183</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.191589728346512</v>
+        <v>3.178215409970814</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.671610978294786</v>
+        <v>-4.598152999935009</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.294358677457613</v>
+        <v>1.323741868801524</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1413186065986125</v>
+        <v>0.2146154373085132</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.184653525332879</v>
+        <v>3.171279206957182</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240616.xlsx
+++ b/tame_output/ON/bt/strategyON_20240616.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>106.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.1%</t>
+          <t>451.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-621.4%</t>
+          <t>-634.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-243.8%</t>
+          <t>-249.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1086.0%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-137.4%</t>
+          <t>-172.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-202.5%</t>
+          <t>-213.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495497</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178241</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006528</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330517</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108633</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.502790399141698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.68516138161528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.653768889318053</v>
+        <v>-7.78525159966246</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.0256523347441262</v>
+        <v>-0.02694074939363666</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.395890368562883</v>
+        <v>-1.502671140883926</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.249982093647365</v>
+        <v>2.185913630254739</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710807</v>
+        <v>3.760333686710808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.505828847910454</v>
+        <v>-7.637311558254861</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.03505057138100165</v>
+        <v>-0.08764365551876452</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.375569452654326</v>
+        <v>-1.482350224975368</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.142295720504332</v>
+        <v>2.078227257111707</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409201</v>
+        <v>3.723566229409202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.452859325656465</v>
+        <v>-7.584342036000872</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02257674873288451</v>
+        <v>-0.07516983287064694</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.322599930400337</v>
+        <v>-1.429380702721379</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.165363447603247</v>
+        <v>2.101294984210622</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098105</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.409310918885775</v>
+        <v>-7.540793629230182</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01211799811970149</v>
+        <v>-0.06471108225746391</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.322599930400337</v>
+        <v>-1.429380702721379</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.158402835508154</v>
+        <v>2.094334372115529</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493416</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.167162525431917</v>
+        <v>-7.298645235776323</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09920371364298486</v>
+        <v>0.04661062950522243</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.322599930400337</v>
+        <v>-1.429380702721379</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.172865189889297</v>
+        <v>2.108796726496672</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722812</v>
+        <v>3.828551486722813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.058903388309395</v>
+        <v>-7.190386098653802</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1370394889511886</v>
+        <v>0.08444640481342613</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.322599930400337</v>
+        <v>-1.429380702721379</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.167397310348492</v>
+        <v>2.103328846955867</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792042</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.935612253492264</v>
+        <v>-7.067094963836671</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1838540368886177</v>
+        <v>0.1312609527508553</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.199308795583207</v>
+        <v>-1.306089567904249</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.238870085249347</v>
+        <v>2.174801621856722</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919903</v>
+        <v>3.812453678919904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.914463054588821</v>
+        <v>-7.045945764933228</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2000146946873205</v>
+        <v>0.1474216105495576</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.178159596679763</v>
+        <v>-1.284940369000806</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.259260582828738</v>
+        <v>2.195192119436113</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.670697612605377</v>
+        <v>-6.802180322949783</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2933015798277485</v>
+        <v>0.2407084956899861</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.178159596679763</v>
+        <v>-1.284940369000806</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.255041291175789</v>
+        <v>2.190972827783164</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.568934792328082</v>
+        <v>-6.700417502672488</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3361310218586828</v>
+        <v>0.28353793772092</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.164940528287335</v>
+        <v>-1.271721300608377</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.265097046131262</v>
+        <v>2.201028582738637</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279181</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.319084398379007</v>
+        <v>-6.450567108723414</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4288132544220145</v>
+        <v>0.376220170284252</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.164940528287335</v>
+        <v>-1.271721300608377</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.257839121114964</v>
+        <v>2.193770657722339</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011493</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.143192305911574</v>
+        <v>-6.274675016255982</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5027692149296366</v>
+        <v>0.4501761307918737</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.164940528287335</v>
+        <v>-1.271721300608377</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.261438244635613</v>
+        <v>2.197369781242988</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.971745842889111</v>
+        <v>-6.103228553233518</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5846753061931755</v>
+        <v>0.5320822220554127</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9934940652648715</v>
+        <v>-1.100274837585914</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.377633628503645</v>
+        <v>2.31356516511102</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.746712843220288</v>
+        <v>-5.878195553564695</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.673708983677002</v>
+        <v>0.6211158995392387</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7684610655960487</v>
+        <v>-0.8752418379170909</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.511673905921235</v>
+        <v>2.44760544252861</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883069</v>
+        <v>3.76461787988307</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.683077100986353</v>
+        <v>-5.814559811330761</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7038580816248929</v>
+        <v>0.6512649974871301</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7048253233621141</v>
+        <v>-0.8116060956831563</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.554550152315914</v>
+        <v>2.490481688923288</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074777</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.639314919680512</v>
+        <v>-5.770797630024919</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7025572129310254</v>
+        <v>0.649964128793262</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7048253233621141</v>
+        <v>-0.8116060956831563</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.535744411099709</v>
+        <v>2.471675947707084</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242288</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.398884422875652</v>
+        <v>-5.530367133220059</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8004724882778467</v>
+        <v>0.7478794041400838</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4643948265572538</v>
+        <v>-0.5711755988782961</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.681745785807502</v>
+        <v>2.617677322414877</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367679</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.326641854704457</v>
+        <v>-5.458124565048864</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8332988293811447</v>
+        <v>0.7807057452433819</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4643948265572538</v>
+        <v>-0.5711755988782961</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.685675099642323</v>
+        <v>2.621606636249697</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.273643532423069</v>
+        <v>-5.405126242767476</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8551767422110399</v>
+        <v>0.802583658073277</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.409058567555315</v>
+        <v>-0.5158393398763572</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.719555438960826</v>
+        <v>2.655486975568201</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.164838646943342</v>
+        <v>-5.296321357287749</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8956967676229244</v>
+        <v>0.8431036834851611</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.409058567555315</v>
+        <v>-0.5158393398763572</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.71655351018082</v>
+        <v>2.652485046788194</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.944817848906331</v>
+        <v>-5.076300559250739</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9852841238483425</v>
+        <v>0.9326910397105794</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2678387224873348</v>
+        <v>-0.374619494808377</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.802864454232222</v>
+        <v>2.738795990839597</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.811950159843054</v>
+        <v>-4.943432870187461</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.054325382275477</v>
+        <v>1.001732298137714</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2678387224873348</v>
+        <v>-0.374619494808377</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.818758637034045</v>
+        <v>2.75469017364142</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496257</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.691777076478555</v>
+        <v>-4.823259786822963</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.103540460061578</v>
+        <v>1.050947375923815</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1476656391228358</v>
+        <v>-0.254446411443878</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.892008331493046</v>
+        <v>2.827939868100421</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.547104931378818</v>
+        <v>-4.678587641723225</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.171497420662913</v>
+        <v>1.11890433652515</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.002993494023098398</v>
+        <v>-0.1097742663441406</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.988899721114329</v>
+        <v>2.924831257721703</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.60697975873651</v>
+        <v>-4.738462469080917</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.133584981121262</v>
+        <v>1.080991896983499</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.06286832138079052</v>
+        <v>-0.1696490937018327</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.939012316101139</v>
+        <v>2.874943852708514</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.520180260957501</v>
+        <v>-4.651662971301908</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.190705273555432</v>
+        <v>1.138112189417669</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.06286832138079052</v>
+        <v>-0.1696490937018327</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.961412809423706</v>
+        <v>2.89734434603108</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.522649967419307</v>
+        <v>-4.654132677763714</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.189789792344122</v>
+        <v>1.137196708206359</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.06533802784259668</v>
+        <v>-0.1721188001636389</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.960003386920034</v>
+        <v>2.895934923527408</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.591020153743317</v>
+        <v>-4.722502864087724</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.173448640289219</v>
+        <v>1.120855556151457</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.05606232880638173</v>
+        <v>-0.162843101127424</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.976575728816465</v>
+        <v>2.91250726542384</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.699558334659451</v>
+        <v>-4.831041045003858</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.120470076554657</v>
+        <v>1.067876992416894</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.05606232880638173</v>
+        <v>-0.162843101127424</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.967012437448356</v>
+        <v>2.902943974055731</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.730551493988156</v>
+        <v>-4.862034204332564</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9327823778635618</v>
+        <v>0.8801892937257989</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.05606232880638173</v>
+        <v>-0.162843101127424</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.791722002488743</v>
+        <v>2.727653539096118</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.555077234195688</v>
+        <v>-4.686559944540095</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.007539313772337</v>
+        <v>0.9549462296345741</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.05606232880638173</v>
+        <v>-0.162843101127424</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.796289234480531</v>
+        <v>2.732220771087905</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.666013486836937</v>
+        <v>-4.797496197181344</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9389068414770447</v>
+        <v>0.8863137573392816</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.05606232880638173</v>
+        <v>-0.162843101127424</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.772031263241738</v>
+        <v>2.707962799849112</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.674295560981995</v>
+        <v>-4.805778271326402</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9387253970389269</v>
+        <v>0.8861323129011638</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.06434440295144012</v>
+        <v>-0.1711251752724823</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.770193403974608</v>
+        <v>2.706124940581983</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.614442941778272</v>
+        <v>-4.745925652122679</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9728388311525484</v>
+        <v>0.9202457470147856</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.06434440295144012</v>
+        <v>-0.1711251752724823</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.780365790406741</v>
+        <v>2.716297327014115</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.528199478751894</v>
+        <v>-4.659682189096301</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.00228248693696</v>
+        <v>0.9496894027991969</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.06434440295144012</v>
+        <v>-0.1711251752724823</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.775312060980601</v>
+        <v>2.711243597587976</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.573506298150874</v>
+        <v>-4.704989008495281</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9759355346218934</v>
+        <v>0.9233424504841306</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1051545659606709</v>
+        <v>-0.2119353382817131</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.742601738619588</v>
+        <v>2.678533275226963</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.602539402853175</v>
+        <v>-4.734022113197582</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9648741657740745</v>
+        <v>0.9122810816363116</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1051545659606709</v>
+        <v>-0.2119353382817131</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.743153611652689</v>
+        <v>2.679085148260064</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.509728921402315</v>
+        <v>-4.641211631746723</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9312710502457842</v>
+        <v>0.8786779661080211</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.01234408450981156</v>
+        <v>-0.1191248568308538</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.728112592414571</v>
+        <v>2.664044129021946</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.554118390731743</v>
+        <v>-4.68560110107615</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9153887384386139</v>
+        <v>0.862795654300851</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.05673355383923923</v>
+        <v>-0.1635143261602814</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.703352386741515</v>
+        <v>2.63928392334889</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.441447172495493</v>
+        <v>-4.5729298828399</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9555329342448369</v>
+        <v>0.902939850107074</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.05593766439701098</v>
+        <v>-0.05084310792403124</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.766030826194988</v>
+        <v>2.701962362802363</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.32907017131282</v>
+        <v>-4.460552881657227</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.005975030548573</v>
+        <v>0.9533819464108104</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.05593766439701098</v>
+        <v>-0.05084310792403124</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.771522122025655</v>
+        <v>2.70745365863303</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.356850569214172</v>
+        <v>-4.48833327955858</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.006360073156571</v>
+        <v>0.9537669890188085</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.02815726649565792</v>
+        <v>-0.0786235058253843</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.766351085053383</v>
+        <v>2.702282621660757</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.389661138885971</v>
+        <v>-4.52183549028127</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8315915652885051</v>
+        <v>0.7787218247303855</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.03565117495428566</v>
+        <v>-0.1420425265846758</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.56642174018407</v>
+        <v>2.502586929205836</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.498275217329303</v>
+        <v>-4.630449568724601</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9082955946303781</v>
+        <v>0.8554258540722588</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.03565117495428566</v>
+        <v>-0.1420425265846758</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.686571400903275</v>
+        <v>2.622736589925041</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.584873800310405</v>
+        <v>-4.717048151705704</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.88816918754026</v>
+        <v>0.8352994469821406</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.03565117495428566</v>
+        <v>-0.1420425265846758</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.701084427005598</v>
+        <v>2.637249616027364</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.546490137752254</v>
+        <v>-4.678664489147553</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9009420939058892</v>
+        <v>0.8480723533477696</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.002732487603865519</v>
+        <v>-0.1036588640265246</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.721534065882858</v>
+        <v>2.657699254904624</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.369373807717088</v>
+        <v>-4.501548159112387</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9685176547652574</v>
+        <v>0.9156479142071381</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.002732487603865519</v>
+        <v>-0.1036588640265246</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.71826309472816</v>
+        <v>2.654428283749926</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.414466052550634</v>
+        <v>-4.546640403945933</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9511641485937523</v>
+        <v>0.8982944080356328</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.05916355556552427</v>
+        <v>-0.1655549071959144</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.681808860588439</v>
+        <v>2.617974049610205</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011232</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.235090631311866</v>
+        <v>-4.367264982707165</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.016701292395674</v>
+        <v>0.9638315518375542</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.0976132026051944</v>
+        <v>-0.008778149025195692</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.769661890797285</v>
+        <v>2.70582707981905</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.280104844832472</v>
+        <v>-4.412279196227772</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9795030623190213</v>
+        <v>0.9266333217609013</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.0672643072905898</v>
+        <v>-0.0391270443398003</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.732260008940111</v>
+        <v>2.668425197961878</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.547109355104907</v>
+        <v>-4.679283706500207</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.878392820548993</v>
+        <v>0.825523079990873</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1270987307523588</v>
+        <v>-0.2334900823827489</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.621333748453288</v>
+        <v>2.557498937475054</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.64830713654208</v>
+        <v>-4.780481487937379</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8371176298706253</v>
+        <v>0.7842478893125056</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.195507544297678</v>
+        <v>-0.3018988959280681</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.579492382222598</v>
+        <v>2.515657571244364</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.615831550371308</v>
+        <v>-4.748005901766607</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8477078258932509</v>
+        <v>0.7948380853351311</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.195507544297678</v>
+        <v>-0.3018988959280681</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.577092343776915</v>
+        <v>2.513257532798681</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.59679342266401</v>
+        <v>-4.72896777405931</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8518477961844146</v>
+        <v>0.7989780556262949</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2536911556288725</v>
+        <v>-0.3600825072592626</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.538706896186443</v>
+        <v>2.474872085208209</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.627920053814629</v>
+        <v>-4.760094405209928</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.016979012662848</v>
+        <v>0.9641092721047282</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2536911556288725</v>
+        <v>-0.3600825072592626</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.716288765125123</v>
+        <v>2.652453954146889</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.641786815148547</v>
+        <v>-4.773961166543846</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.012265637115414</v>
+        <v>0.9593958965572944</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2915490723626954</v>
+        <v>-0.3979404239930855</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.694407344070963</v>
+        <v>2.630572533092729</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.662044113677505</v>
+        <v>-4.794218465072804</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.010171248100757</v>
+        <v>0.9573015075426372</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2915490723626954</v>
+        <v>-0.3979404239930855</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.700415874467889</v>
+        <v>2.636581063489655</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.514301143442502</v>
+        <v>-4.646475494837802</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.14842108398678</v>
+        <v>1.09555134342866</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1237417151278123</v>
+        <v>-0.2301330667582024</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.880252936600841</v>
+        <v>2.816418125622607</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.616315825973723</v>
+        <v>-4.748490177369023</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.110408832505772</v>
+        <v>1.057539091947653</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1237417151278123</v>
+        <v>-0.2301330667582024</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.883046558132322</v>
+        <v>2.819211747154088</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.610163119920939</v>
+        <v>-4.742337471316239</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.113532263318544</v>
+        <v>1.060662522760425</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.117589009075028</v>
+        <v>-0.2239803607054181</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.887400530155651</v>
+        <v>2.823565719177417</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.626972418071441</v>
+        <v>-4.75914676946674</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.105889020798454</v>
+        <v>1.053019280240334</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1343983072255296</v>
+        <v>-0.2407896588559197</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.87639542800546</v>
+        <v>2.812560617027226</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.564674419295319</v>
+        <v>-4.696848770690618</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.197143774105724</v>
+        <v>1.144274033547604</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1343983072255296</v>
+        <v>-0.2407896588559197</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.942730981802281</v>
+        <v>2.878896170824047</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.362884221630161</v>
+        <v>-4.49505857302546</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9864407255611851</v>
+        <v>0.9335709850030653</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.06361988494362475</v>
+        <v>-0.04277146668676535</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.770122769493172</v>
+        <v>2.706287958514938</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.302993539987567</v>
+        <v>-4.435167891382867</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.080687230540398</v>
+        <v>1.027817489982278</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.1235105665862182</v>
+        <v>0.01711921495582813</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.876347410800903</v>
+        <v>2.812512599822669</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.400734084612542</v>
+        <v>-4.532908436007841</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.056218748806451</v>
+        <v>1.003349008248332</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.107621288453238</v>
+        <v>0.001229936822847943</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.881441580037158</v>
+        <v>2.817606769058925</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.577071844735471</v>
+        <v>-4.709246196130771</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9842196255819515</v>
+        <v>0.9313498850238315</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.06871647166969136</v>
+        <v>-0.1751078233000815</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.774174904788072</v>
+        <v>2.710340093809839</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.505525521958594</v>
+        <v>-4.637699873353894</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.011329772732631</v>
+        <v>0.9584600321745109</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.06871647166969136</v>
+        <v>-0.1751078233000815</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.772666522828001</v>
+        <v>2.708831711849767</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024962</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.461152390320025</v>
+        <v>-4.593326741715325</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.028941892823494</v>
+        <v>0.9760721522653746</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.02434334003112276</v>
+        <v>-0.1307346916615129</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.799153269246578</v>
+        <v>2.735318458268345</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863222</v>
+        <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.453198420025253</v>
+        <v>-4.585372771420553</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.032123480941403</v>
+        <v>0.9792537403832835</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.02434334003112276</v>
+        <v>-0.1307346916615129</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.799153269246578</v>
+        <v>2.735318458268345</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947581</v>
+        <v>3.833040181947584</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.405542689464197</v>
+        <v>-4.537717040859497</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.05756753019363</v>
+        <v>1.00469778963551</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.02331239052993289</v>
+        <v>-0.0830789611004572</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.834128464611017</v>
+        <v>2.770293653632782</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326874</v>
+        <v>3.822707244326876</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.277858379669901</v>
+        <v>-4.410032731065201</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.113533627486074</v>
+        <v>1.060663886927954</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.1509967003242293</v>
+        <v>0.04460534869383925</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.915631423862319</v>
+        <v>2.851796612884085</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314549</v>
+        <v>3.828837911314552</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.338524970072291</v>
+        <v>-4.47069932146759</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.07602166380099</v>
+        <v>1.02315192324287</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.06929838360569568</v>
+        <v>-0.03709296802469442</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.853367106307071</v>
+        <v>2.789532295328837</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690025</v>
+        <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.293686568463892</v>
+        <v>-4.425860919859192</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.098054727054978</v>
+        <v>1.045184986496858</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.07384181655056515</v>
+        <v>-0.03254953507982494</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.860190868684621</v>
+        <v>2.796356057706388</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.39444520422089</v>
+        <v>-4.52661955561619</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.061912212383257</v>
+        <v>1.009042471825137</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.01498375217644027</v>
+        <v>-0.1213751038068304</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.811056467079496</v>
+        <v>2.747221656101262</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.35024236713499</v>
+        <v>-4.482416718530289</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.085472949745454</v>
+        <v>1.032603209187334</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.02921908490946018</v>
+        <v>-0.07717226672092992</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.843457771858874</v>
+        <v>2.77962296088064</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022902</v>
+        <v>3.838228663022904</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.387221394798432</v>
+        <v>-4.519395746193732</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.069091339149325</v>
+        <v>1.016221598591205</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.06619298670079071</v>
+        <v>-0.04019836492959938</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.86405211340292</v>
+        <v>2.800217302424685</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042138</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.407279473663273</v>
+        <v>-4.539453825058573</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.112315872786428</v>
+        <v>1.059446132228308</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.06619298670079071</v>
+        <v>-0.04019836492959938</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.915299878585959</v>
+        <v>2.851465067607725</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078277</v>
+        <v>3.865367715078279</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.367348800485383</v>
+        <v>-4.499523151880682</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.126728846651837</v>
+        <v>1.073859106093717</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.1061236598786811</v>
+        <v>-0.0002676917517090427</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.937698987086947</v>
+        <v>2.873864176108713</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232395</v>
+        <v>3.864518876232396</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.326878452922678</v>
+        <v>-4.459052804317977</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.137865213915189</v>
+        <v>1.084995473357069</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.146594007441386</v>
+        <v>0.04020265581099591</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.95692942386284</v>
+        <v>2.893094612884605</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162109</v>
+        <v>3.842576394162111</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.261654271795472</v>
+        <v>-4.393828623190772</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.181142290458776</v>
+        <v>1.128272549900657</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.2118181885685916</v>
+        <v>0.1054268369382015</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.013251336631868</v>
+        <v>2.949416525653634</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639815</v>
+        <v>3.840090220639817</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.312148562152529</v>
+        <v>-4.444322913547828</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.156905546615234</v>
+        <v>1.104035806057114</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1667974514425174</v>
+        <v>0.0604060998121273</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.982199866655504</v>
+        <v>2.91836505567727</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749918</v>
+        <v>3.84519884274992</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.332260218187237</v>
+        <v>-4.464434569582536</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.150117676532591</v>
+        <v>1.097247935974471</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1778247964399366</v>
+        <v>0.0714334448095465</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.990073065985195</v>
+        <v>2.926238255006961</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393543</v>
+        <v>3.828690479393545</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.429940797459883</v>
+        <v>-4.562115148855183</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.271603215844743</v>
+        <v>1.218733475286624</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.0671216010997478</v>
+        <v>-0.0392697505306423</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.084208919802293</v>
+        <v>3.020374108824059</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714881</v>
+        <v>3.813251854714883</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.40614922885374</v>
+        <v>-4.53832358024904</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.401232752505018</v>
+        <v>1.348363011946898</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.09091316970589008</v>
+        <v>-0.01547818192450001</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.218596770183796</v>
+        <v>3.154761959205561</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81425976175601</v>
+        <v>3.814259761756012</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.442903647415463</v>
+        <v>-4.575077998810762</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.378238961094188</v>
+        <v>1.325369220536068</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.09091316970589008</v>
+        <v>-0.01547818192450001</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.210304746197655</v>
+        <v>3.14646993521942</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654185</v>
+        <v>3.803426852654186</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.438569344358415</v>
+        <v>-4.570743695753714</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.378165877900786</v>
+        <v>1.325296137342667</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.242563273025094</v>
+        <v>0.1361719213947039</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.299488003772956</v>
+        <v>3.235653192794723</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717115</v>
+        <v>3.796293177717117</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.429676882965132</v>
+        <v>-4.561851234360431</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.399277268184891</v>
+        <v>1.346407527626771</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.242563273025094</v>
+        <v>0.1361719213947039</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.317042409499748</v>
+        <v>3.253207598521514</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702626</v>
+        <v>3.794453975702628</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.598152999935009</v>
+        <v>-4.730327351330309</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.323741868801524</v>
+        <v>1.270872128243404</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2146154373085132</v>
+        <v>0.1082240856781231</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.292128755474383</v>
+        <v>3.228293944496149</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,19 +47476,19 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.718636832441183</v>
+        <v>3.718636832441184</v>
       </c>
       <c r="C1997" t="n">
         <v>3.178215409970814</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.598152999935009</v>
+        <v>-4.730327351330309</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.323741868801524</v>
+        <v>1.270872128243404</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2146154373085132</v>
+        <v>0.1082240856781231</v>
       </c>
       <c r="G1997" t="n">
         <v>3.171279206957182</v>

--- a/tame_output/ON/bt/strategyON_20240616.xlsx
+++ b/tame_output/ON/bt/strategyON_20240616.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.2%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.8%</t>
+          <t>106.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.2%</t>
+          <t>125.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.9%</t>
+          <t>453.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-634.6%</t>
+          <t>-659.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>-82.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-249.1%</t>
+          <t>-258.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-172.2%</t>
+          <t>-272.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-213.2%</t>
+          <t>-208.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-128.9%</t>
+          <t>-119.7%</t>
         </is>
       </c>
     </row>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495497</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178241</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006528</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309419</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330517</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108633</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937496</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141698</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440631</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68516138161528</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.65879518304443</v>
+        <v>-10.84840625686483</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.085130307416742</v>
+        <v>-1.160974736944903</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.676650140389822</v>
+        <v>-2.654960453912385</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.572754105880884</v>
+        <v>1.585767917767346</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.53421652670684</v>
+        <v>-10.72382760052724</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.034159700325647</v>
+        <v>-1.110004129853808</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.676650140389822</v>
+        <v>-2.654960453912385</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.573893250436943</v>
+        <v>1.586907062323405</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.58711181475112</v>
+        <v>-10.77672288857153</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.052684041381253</v>
+        <v>-1.128528470909415</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.671694794301376</v>
+        <v>-2.650005107823938</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.579500232252118</v>
+        <v>1.592514044138581</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.51497863946324</v>
+        <v>-10.70458971328365</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.018097067027464</v>
+        <v>-1.093941496555626</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.671694794301376</v>
+        <v>-2.650005107823938</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.585233936490755</v>
+        <v>1.598247748377217</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.4436122468536</v>
+        <v>-10.633223320674</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9992877723774711</v>
+        <v>-1.075132201905632</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.600328401691728</v>
+        <v>-2.578638715214291</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.618316509662678</v>
+        <v>1.631330321549141</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17977537964953</v>
+        <v>-10.36938645346993</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9036365068087506</v>
+        <v>-0.9794809363369121</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.600328401691728</v>
+        <v>-2.578638715214291</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.608433028349771</v>
+        <v>1.621446840236233</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.912533578781128</v>
+        <v>-10.10214465260153</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7985743469607649</v>
+        <v>-0.8744187764889264</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.600328401691728</v>
+        <v>-2.578638715214291</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.606598467850397</v>
+        <v>1.619612279736859</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.814626540104637</v>
+        <v>-10.00423761392504</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7597118464636297</v>
+        <v>-0.8355562759917912</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.532342651831171</v>
+        <v>-2.510652965353734</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.64708960279327</v>
+        <v>1.660103414679732</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.790672999128679</v>
+        <v>-9.980284072949082</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7494619239277527</v>
+        <v>-0.8253063534559142</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.508389110855214</v>
+        <v>-2.486699424377777</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.662130233524338</v>
+        <v>1.6751440454108</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.526613060805882</v>
+        <v>-9.716224134626286</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6570982647603865</v>
+        <v>-0.7329426942885475</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.244329172532418</v>
+        <v>-2.222639486054981</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.807305880356264</v>
+        <v>1.820319692242726</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.819533437301045</v>
+        <v>-9.009144511121448</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.377053449018752</v>
+        <v>-0.4528978785469135</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.244329172532418</v>
+        <v>-2.222639486054981</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.804518846695963</v>
+        <v>1.817532658582425</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.779349138934855</v>
+        <v>-8.968960212755258</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3606361057844345</v>
+        <v>-0.436480535312596</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.204144874166227</v>
+        <v>-2.18245518768879</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.828973049603519</v>
+        <v>1.841986861489981</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.615949267995493</v>
+        <v>-8.805560341815895</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.295909336187933</v>
+        <v>-0.3717537657160936</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.040745003226864</v>
+        <v>-2.019055316749427</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.926379793387893</v>
+        <v>1.939393605274355</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.382468045765894</v>
+        <v>-8.572079119586295</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.194592418458241</v>
+        <v>-0.2704368479864017</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.807263780997266</v>
+        <v>-1.785574094519829</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.074392955563504</v>
+        <v>2.087406767449967</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.232801654758379</v>
+        <v>-8.422412728578781</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1376180723681943</v>
+        <v>-0.213462501896355</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.71436028975473</v>
+        <v>-1.692670603277293</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.127242839996067</v>
+        <v>2.140256651882529</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.100526181127492</v>
+        <v>-8.290137254947894</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.0893403961688124</v>
+        <v>-0.165184825696973</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.582084816123843</v>
+        <v>-1.560395129646406</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.201975610921626</v>
+        <v>2.214989422808088</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.909926506454339</v>
+        <v>-8.09953758027474</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0102854656119149</v>
+        <v>-0.08612989514007507</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.39148514145069</v>
+        <v>-1.369795454973253</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.319150476413154</v>
+        <v>2.332164288299617</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.660926707770758</v>
+        <v>-7.850537781591159</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1022207950851763</v>
+        <v>0.02637636555701617</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.39148514145069</v>
+        <v>-1.369795454973253</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.332056817636813</v>
+        <v>2.345070629523275</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.766516697543863</v>
+        <v>-7.956127771364264</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.06799113042328386</v>
+        <v>-0.1438355599514445</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.497075131223795</v>
+        <v>-1.475385444746358</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.140726894173732</v>
+        <v>2.153740706060194</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.78525159966246</v>
+        <v>-7.97486267348286</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.02694074939363666</v>
+        <v>-0.1027851789217968</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.502671140883926</v>
+        <v>-1.480981454406489</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.185913630254739</v>
+        <v>2.198927442141202</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710808</v>
+        <v>3.760333686710807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.637311558254861</v>
+        <v>-7.826922632075261</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.08764365551876452</v>
+        <v>-0.1634880850469247</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.482350224975368</v>
+        <v>-1.460660538497931</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.078227257111707</v>
+        <v>2.091241068998169</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409202</v>
+        <v>3.723566229409201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.584342036000872</v>
+        <v>-7.773953109821273</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.07516983287064694</v>
+        <v>-0.1510142623988076</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.429380702721379</v>
+        <v>-1.407691016243942</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.101294984210622</v>
+        <v>2.114308796097084</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098105</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.540793629230182</v>
+        <v>-7.730404703050582</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.06471108225746391</v>
+        <v>-0.1405555117856245</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.429380702721379</v>
+        <v>-1.407691016243942</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.094334372115529</v>
+        <v>2.107348184001991</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.782922533493416</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.298645235776323</v>
+        <v>-7.488256309596724</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.04661062950522243</v>
+        <v>-0.02923380002293818</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.429380702721379</v>
+        <v>-1.407691016243942</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.108796726496672</v>
+        <v>2.121810538383134</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722813</v>
+        <v>3.828551486722812</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.190386098653802</v>
+        <v>-7.379997172474202</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.08444640481342613</v>
+        <v>0.008601975285265517</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.429380702721379</v>
+        <v>-1.407691016243942</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.103328846955867</v>
+        <v>2.116342658842329</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.067094963836671</v>
+        <v>-7.256706037657072</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1312609527508553</v>
+        <v>0.05541652322269508</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.306089567904249</v>
+        <v>-1.284399881426812</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.174801621856722</v>
+        <v>2.187815433743184</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919904</v>
+        <v>3.812453678919903</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.045945764933228</v>
+        <v>-7.235556838753628</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1474216105495576</v>
+        <v>0.07157718102139743</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.284940369000806</v>
+        <v>-1.263250682523369</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.195192119436113</v>
+        <v>2.208205931322575</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.802180322949783</v>
+        <v>-6.991791396770184</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2407084956899861</v>
+        <v>0.1648640661618259</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.284940369000806</v>
+        <v>-1.263250682523369</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.190972827783164</v>
+        <v>2.203986639669626</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.700417502672488</v>
+        <v>-6.890028576492889</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.28353793772092</v>
+        <v>0.2076935081927598</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.271721300608377</v>
+        <v>-1.25003161413094</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.201028582738637</v>
+        <v>2.214042394625099</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.450567108723414</v>
+        <v>-6.640178182543814</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.376220170284252</v>
+        <v>0.3003757407560919</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.271721300608377</v>
+        <v>-1.25003161413094</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.193770657722339</v>
+        <v>2.206784469608801</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.274675016255982</v>
+        <v>-6.464286090076381</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4501761307918737</v>
+        <v>0.3743317012637135</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.271721300608377</v>
+        <v>-1.25003161413094</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.197369781242988</v>
+        <v>2.21038359312945</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.103228553233518</v>
+        <v>-6.292839627053918</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5320822220554127</v>
+        <v>0.4562377925272529</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.100274837585914</v>
+        <v>-1.078585151108477</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.31356516511102</v>
+        <v>2.326578976997482</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.878195553564695</v>
+        <v>-6.067806627385095</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6211158995392387</v>
+        <v>0.545271470011079</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8752418379170909</v>
+        <v>-0.8535521514396539</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.44760544252861</v>
+        <v>2.460619254415072</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988307</v>
+        <v>3.764617879883069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.814559811330761</v>
+        <v>-6.004170885151161</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6512649974871301</v>
+        <v>0.5754205679589699</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8116060956831563</v>
+        <v>-0.7899164092057194</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.490481688923288</v>
+        <v>2.50349550080975</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.770797630024919</v>
+        <v>-5.960408703845319</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.649964128793262</v>
+        <v>0.5741196992651023</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8116060956831563</v>
+        <v>-0.7899164092057194</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.471675947707084</v>
+        <v>2.484689759593546</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242288</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.530367133220059</v>
+        <v>-5.719978207040459</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7478794041400838</v>
+        <v>0.6720349746119236</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5711755988782961</v>
+        <v>-0.5494859124008591</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.617677322414877</v>
+        <v>2.630691134301339</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.458124565048864</v>
+        <v>-5.647735638869264</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7807057452433819</v>
+        <v>0.7048613157152217</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5711755988782961</v>
+        <v>-0.5494859124008591</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.621606636249697</v>
+        <v>2.63462044813616</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.405126242767476</v>
+        <v>-5.594737316587876</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.802583658073277</v>
+        <v>0.7267392285451169</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5158393398763572</v>
+        <v>-0.4941496533989203</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.655486975568201</v>
+        <v>2.668500787454663</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.296321357287749</v>
+        <v>-5.485932431108149</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8431036834851611</v>
+        <v>0.7672592539570013</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5158393398763572</v>
+        <v>-0.4941496533989203</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.652485046788194</v>
+        <v>2.665498858674656</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.076300559250739</v>
+        <v>-5.265911633071139</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9326910397105794</v>
+        <v>0.8568466101824197</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.374619494808377</v>
+        <v>-0.35292980833094</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.738795990839597</v>
+        <v>2.751809802726059</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.943432870187461</v>
+        <v>-5.133043944007861</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.001732298137714</v>
+        <v>0.925887868609554</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.374619494808377</v>
+        <v>-0.35292980833094</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.75469017364142</v>
+        <v>2.767703985527882</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.823259786822963</v>
+        <v>-5.012870860643362</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.050947375923815</v>
+        <v>0.9751029463956553</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.254446411443878</v>
+        <v>-0.2327567249664411</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.827939868100421</v>
+        <v>2.840953679986883</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.678587641723225</v>
+        <v>-4.868198715543625</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.11890433652515</v>
+        <v>1.04305990699699</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1097742663441406</v>
+        <v>-0.08808457986670365</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.924831257721703</v>
+        <v>2.937845069608166</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.738462469080917</v>
+        <v>-4.928073542901317</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.080991896983499</v>
+        <v>1.005147467455339</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1696490937018327</v>
+        <v>-0.1479594072243958</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.874943852708514</v>
+        <v>2.887957664594976</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.651662971301908</v>
+        <v>-4.841274045122308</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.138112189417669</v>
+        <v>1.062267759889509</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1696490937018327</v>
+        <v>-0.1479594072243958</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.89734434603108</v>
+        <v>2.910358157917542</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.654132677763714</v>
+        <v>-4.843743751584114</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.137196708206359</v>
+        <v>1.061352278678199</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1721188001636389</v>
+        <v>-0.1504291136862019</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.895934923527408</v>
+        <v>2.908948735413871</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.722502864087724</v>
+        <v>-4.912113937908124</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.120855556151457</v>
+        <v>1.045011126623297</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.141153414649987</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.91250726542384</v>
+        <v>2.925521077310302</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.831041045003858</v>
+        <v>-5.020652118824258</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.067876992416894</v>
+        <v>0.9920325628887343</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.141153414649987</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.902943974055731</v>
+        <v>2.915957785942193</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.862034204332564</v>
+        <v>-5.051645278152963</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8801892937257989</v>
+        <v>0.8043448641976392</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.141153414649987</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.727653539096118</v>
+        <v>2.74066735098258</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.686559944540095</v>
+        <v>-4.876171018360495</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9549462296345741</v>
+        <v>0.8791018001064144</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.141153414649987</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.732220771087905</v>
+        <v>2.745234582974367</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.797496197181344</v>
+        <v>-4.987107271001744</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8863137573392816</v>
+        <v>0.8104693278111217</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.141153414649987</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.707962799849112</v>
+        <v>2.720976611735574</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.805778271326402</v>
+        <v>-4.995389345146802</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8861323129011638</v>
+        <v>0.8102878833730038</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1711251752724823</v>
+        <v>-0.1494354887950454</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.706124940581983</v>
+        <v>2.719138752468445</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.745925652122679</v>
+        <v>-4.935536725943079</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9202457470147856</v>
+        <v>0.8444013174866256</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1711251752724823</v>
+        <v>-0.1494354887950454</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.716297327014115</v>
+        <v>2.729311138900577</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.659682189096301</v>
+        <v>-4.849293262916701</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9496894027991969</v>
+        <v>0.8738449732710369</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1711251752724823</v>
+        <v>-0.1494354887950454</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.711243597587976</v>
+        <v>2.724257409474438</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.704989008495281</v>
+        <v>-4.894600082315681</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9233424504841306</v>
+        <v>0.8474980209559706</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2119353382817131</v>
+        <v>-0.1902456518042762</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.678533275226963</v>
+        <v>2.691547087113425</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.734022113197582</v>
+        <v>-4.923633187017982</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9122810816363116</v>
+        <v>0.8364366521081517</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2119353382817131</v>
+        <v>-0.1902456518042762</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.679085148260064</v>
+        <v>2.692098960146526</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.641211631746723</v>
+        <v>-4.830822705567122</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8786779661080211</v>
+        <v>0.8028335365798611</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1191248568308538</v>
+        <v>-0.09743517035341681</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.664044129021946</v>
+        <v>2.677057940908408</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.68560110107615</v>
+        <v>-4.87521217489655</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.862795654300851</v>
+        <v>0.7869512247726911</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1635143261602814</v>
+        <v>-0.1418246396828445</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.63928392334889</v>
+        <v>2.652297735235352</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.5729298828399</v>
+        <v>-4.7625409566603</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.902939850107074</v>
+        <v>0.8270954205789141</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.05084310792403124</v>
+        <v>-0.02915342144659427</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.701962362802363</v>
+        <v>2.714976174688825</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.460552881657227</v>
+        <v>-4.650163955477627</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9533819464108104</v>
+        <v>0.8775375168826505</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.05084310792403124</v>
+        <v>-0.02915342144659427</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.70745365863303</v>
+        <v>2.720467470519492</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.48833327955858</v>
+        <v>-4.67794435337898</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9537669890188085</v>
+        <v>0.8779225594906486</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.0786235058253843</v>
+        <v>-0.05693381934794733</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.702282621660757</v>
+        <v>2.715296433547219</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.52183549028127</v>
+        <v>-4.760945634404258</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7787218247303855</v>
+        <v>0.6830777670811903</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1420425265846758</v>
+        <v>-0.07550470387512109</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.502586929205836</v>
+        <v>2.542509622831568</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.630449568724601</v>
+        <v>-4.86955971284759</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8554258540722588</v>
+        <v>0.7597817964230633</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1420425265846758</v>
+        <v>-0.07550470387512109</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.622736589925041</v>
+        <v>2.662659283550774</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.717048151705704</v>
+        <v>-4.956158295828692</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8352994469821406</v>
+        <v>0.7396553893329452</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1420425265846758</v>
+        <v>-0.07550470387512109</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.637249616027364</v>
+        <v>2.677172309653097</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.678664489147553</v>
+        <v>-4.917774633270541</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8480723533477696</v>
+        <v>0.7524282956985744</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1036588640265246</v>
+        <v>-0.03712104131696992</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.657699254904624</v>
+        <v>2.697621948530356</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.501548159112387</v>
+        <v>-4.740658303235375</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9156479142071381</v>
+        <v>0.8200038565579426</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1036588640265246</v>
+        <v>-0.03712104131696992</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.654428283749926</v>
+        <v>2.694350977375658</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.546640403945933</v>
+        <v>-4.785750548068921</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8982944080356328</v>
+        <v>0.8026503503864375</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1655549071959144</v>
+        <v>-0.09901708448635971</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.617974049610205</v>
+        <v>2.657896743235938</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011232</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.367264982707165</v>
+        <v>-4.606375126830153</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9638315518375542</v>
+        <v>0.8681874941883589</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.008778149025195692</v>
+        <v>0.05775967368435897</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.70582707981905</v>
+        <v>2.745749773444783</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.412279196227772</v>
+        <v>-4.651389340350759</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9266333217609013</v>
+        <v>0.8309892641117065</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.0391270443398003</v>
+        <v>0.02741077836975436</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.668425197961878</v>
+        <v>2.70834789158761</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.679283706500207</v>
+        <v>-4.918393850623194</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.825523079990873</v>
+        <v>0.7298790223416782</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2334900823827489</v>
+        <v>-0.1669522596731942</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.557498937475054</v>
+        <v>2.597421631100787</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.780481487937379</v>
+        <v>-5.019591632060367</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7842478893125056</v>
+        <v>0.6886038316633103</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3018988959280681</v>
+        <v>-0.2353610732185134</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.515657571244364</v>
+        <v>2.555580264870096</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.748005901766607</v>
+        <v>-4.987116045889595</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7948380853351311</v>
+        <v>0.6991940276859361</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3018988959280681</v>
+        <v>-0.2353610732185134</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.513257532798681</v>
+        <v>2.553180226424414</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.72896777405931</v>
+        <v>-4.968077918182297</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7989780556262949</v>
+        <v>0.7033339979770998</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3600825072592626</v>
+        <v>-0.2935446845497079</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.474872085208209</v>
+        <v>2.514794778833942</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.760094405209928</v>
+        <v>-4.999204549332916</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9641092721047282</v>
+        <v>0.8684652144555332</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3600825072592626</v>
+        <v>-0.2935446845497079</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.652453954146889</v>
+        <v>2.692376647772622</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.773961166543846</v>
+        <v>-5.013071310666834</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9593958965572944</v>
+        <v>0.8637518389080996</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3979404239930855</v>
+        <v>-0.3314026012835309</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.630572533092729</v>
+        <v>2.670495226718462</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.794218465072804</v>
+        <v>-4.992897793761884</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9573015075426372</v>
+        <v>0.8778297760670053</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3979404239930855</v>
+        <v>-0.3314026012835309</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.636581063489655</v>
+        <v>2.676503757115388</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.646475494837802</v>
+        <v>-4.845154823526881</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.09555134342866</v>
+        <v>1.016079611953028</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2301330667582024</v>
+        <v>-0.1635952440486477</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.816418125622607</v>
+        <v>2.85634081924834</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.748490177369023</v>
+        <v>-4.947169506058103</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.057539091947653</v>
+        <v>0.9780673604720207</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2301330667582024</v>
+        <v>-0.1635952440486477</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.819211747154088</v>
+        <v>2.859134440779821</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.742337471316239</v>
+        <v>-4.941016800005318</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.060662522760425</v>
+        <v>0.9811907912847928</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2239803607054181</v>
+        <v>-0.1574425379958634</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.823565719177417</v>
+        <v>2.86348841280315</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.75914676946674</v>
+        <v>-4.95782609815582</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.053019280240334</v>
+        <v>0.9735475487647023</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2407896588559197</v>
+        <v>-0.1742518361463651</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.812560617027226</v>
+        <v>2.852483310652959</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.696848770690618</v>
+        <v>-4.895528099379698</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.144274033547604</v>
+        <v>1.064802302071972</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2407896588559197</v>
+        <v>-0.1742518361463651</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.878896170824047</v>
+        <v>2.91881886444978</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.49505857302546</v>
+        <v>-4.69373790171454</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9335709850030653</v>
+        <v>0.8540992535274334</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.04277146668676535</v>
+        <v>0.02376635602278931</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.706287958514938</v>
+        <v>2.74621065214067</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.435167891382867</v>
+        <v>-4.633847220071947</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.027817489982278</v>
+        <v>0.9483457585066459</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.01711921495582813</v>
+        <v>0.08365703766538279</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.812512599822669</v>
+        <v>2.852435293448402</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.532908436007841</v>
+        <v>-4.731587764696921</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.003349008248332</v>
+        <v>0.9238772767726997</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.001229936822847943</v>
+        <v>0.0677677595324026</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.817606769058925</v>
+        <v>2.857529462684657</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.709246196130771</v>
+        <v>-4.90792552481985</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9313498850238315</v>
+        <v>0.8518781535481996</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1751078233000815</v>
+        <v>-0.1085700005905268</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.710340093809839</v>
+        <v>2.750262787435571</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.637699873353894</v>
+        <v>-4.836379202042973</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9584600321745109</v>
+        <v>0.878988300698879</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1751078233000815</v>
+        <v>-0.1085700005905268</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.708831711849767</v>
+        <v>2.7487544054755</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024962</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.593326741715325</v>
+        <v>-4.792006070404405</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9760721522653746</v>
+        <v>0.8966004207897427</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1307346916615129</v>
+        <v>-0.0641968689519582</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.735318458268345</v>
+        <v>2.775241151894077</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.585372771420553</v>
+        <v>-4.784052100109633</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9792537403832835</v>
+        <v>0.8997820089076516</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1307346916615129</v>
+        <v>-0.0641968689519582</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.735318458268345</v>
+        <v>2.775241151894077</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947584</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.537717040859497</v>
+        <v>-4.736396369548577</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.00469778963551</v>
+        <v>0.9252260581598786</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.0830789611004572</v>
+        <v>-0.01654113839090254</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.770293653632782</v>
+        <v>2.810216347258515</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326876</v>
+        <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.410032731065201</v>
+        <v>-4.60871205975428</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.060663886927954</v>
+        <v>0.981192155452322</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.04460534869383925</v>
+        <v>0.1111431714033939</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.851796612884085</v>
+        <v>2.891719306509818</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314552</v>
+        <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.47069932146759</v>
+        <v>-4.66937865015667</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.02315192324287</v>
+        <v>0.9436801917672384</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.03709296802469442</v>
+        <v>0.02944485468486024</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.789532295328837</v>
+        <v>2.82945498895457</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690025</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.425860919859192</v>
+        <v>-4.624540248548271</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.045184986496858</v>
+        <v>0.9657132550212264</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.03254953507982494</v>
+        <v>0.03398828762972972</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.796356057706388</v>
+        <v>2.83627875133212</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.52661955561619</v>
+        <v>-4.725298884305269</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.009042471825137</v>
+        <v>0.929570740349505</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1213751038068304</v>
+        <v>-0.0548372810972757</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.747221656101262</v>
+        <v>2.787144349726995</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.482416718530289</v>
+        <v>-4.681096047219369</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.032603209187334</v>
+        <v>0.9531314777117024</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.07717226672092992</v>
+        <v>-0.01063444401137525</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.77962296088064</v>
+        <v>2.819545654506372</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022904</v>
+        <v>3.838228663022902</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.519395746193732</v>
+        <v>-4.718075074882812</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.016221598591205</v>
+        <v>0.936749867115573</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.04019836492959938</v>
+        <v>0.02633945777995528</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.800217302424685</v>
+        <v>2.840139996050418</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042138</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.539453825058573</v>
+        <v>-4.738133153747652</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.059446132228308</v>
+        <v>0.9799744007526763</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.04019836492959938</v>
+        <v>0.02633945777995528</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.851465067607725</v>
+        <v>2.891387761233458</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078279</v>
+        <v>3.865367715078277</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.499523151880682</v>
+        <v>-4.698202480569762</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.073859106093717</v>
+        <v>0.9943873746180856</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.0002676917517090427</v>
+        <v>0.06627013095784562</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.873864176108713</v>
+        <v>2.913786869734445</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232396</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.459052804317977</v>
+        <v>-4.657732133007057</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.084995473357069</v>
+        <v>1.005523741881438</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.04020265581099591</v>
+        <v>0.1067404785205506</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.893094612884605</v>
+        <v>2.933017306510338</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162111</v>
+        <v>3.842576394162109</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.393828623190772</v>
+        <v>-4.592507951879852</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.128272549900657</v>
+        <v>1.048800818425025</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1054268369382015</v>
+        <v>0.1719646596477562</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.949416525653634</v>
+        <v>2.989339219279366</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639817</v>
+        <v>3.840090220639815</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.444322913547828</v>
+        <v>-4.643002242236908</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.104035806057114</v>
+        <v>1.024564074581483</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.0604060998121273</v>
+        <v>0.126943922521682</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.91836505567727</v>
+        <v>2.958287749303002</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84519884274992</v>
+        <v>3.845198842749918</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.464434569582536</v>
+        <v>-4.663113898271616</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.097247935974471</v>
+        <v>1.017776204498839</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.0714334448095465</v>
+        <v>0.1379712675191012</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.926238255006961</v>
+        <v>2.966160948632694</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393545</v>
+        <v>3.828690479393543</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.562115148855183</v>
+        <v>-4.760794477544263</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.218733475286624</v>
+        <v>1.139261743810992</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.0392697505306423</v>
+        <v>0.02726807217891236</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.020374108824059</v>
+        <v>3.060296802449792</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714883</v>
+        <v>3.813251854714881</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.53832358024904</v>
+        <v>-4.73700290893812</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.348363011946898</v>
+        <v>1.268891280471266</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.01547818192450001</v>
+        <v>0.05105964078505465</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.154761959205561</v>
+        <v>3.194684652831294</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756012</v>
+        <v>3.81425976175601</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.575077998810762</v>
+        <v>-4.773757327499842</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.325369220536068</v>
+        <v>1.245897489060436</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.01547818192450001</v>
+        <v>0.05105964078505465</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.14646993521942</v>
+        <v>3.186392628845153</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654186</v>
+        <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.570743695753714</v>
+        <v>-4.769423024442794</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.325296137342667</v>
+        <v>1.245824405867035</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1361719213947039</v>
+        <v>0.2027097441042586</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.235653192794723</v>
+        <v>3.275575886420455</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717117</v>
+        <v>3.796293177717115</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.561851234360431</v>
+        <v>-4.760530563049511</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.346407527626771</v>
+        <v>1.266935796151139</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1361719213947039</v>
+        <v>0.2027097441042586</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.253207598521514</v>
+        <v>3.293130292147247</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702628</v>
+        <v>3.794453975702627</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.730327351330309</v>
+        <v>-4.929006680019389</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.270872128243404</v>
+        <v>1.191400396767772</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1082240856781231</v>
+        <v>0.1747619083876778</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.228293944496149</v>
+        <v>3.268216638121882</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.718636832441184</v>
+        <v>3.834727014174043</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.178215409970814</v>
+        <v>3.167826705169634</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.730327351330309</v>
+        <v>-4.975066873649149</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.270872128243404</v>
+        <v>1.177443531396227</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1082240856781231</v>
+        <v>0.1592119188395509</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.171279206957182</v>
+        <v>3.263353856473365</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240616.xlsx
+++ b/tame_output/ON/bt/strategyON_20240616.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.4%</t>
+          <t>106.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.3%</t>
+          <t>125.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-51.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.1%</t>
+          <t>454.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-659.1%</t>
+          <t>-631.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>104.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-82.2%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-258.5%</t>
+          <t>-241.2%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-272.8%</t>
+          <t>-198.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-208.1%</t>
+          <t>-208.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-119.7%</t>
+          <t>-113.9%</t>
         </is>
       </c>
     </row>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495497</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178241</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006528</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330517</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108633</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.502790399141698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.84840625686483</v>
+        <v>-10.65879518304443</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.160974736944903</v>
+        <v>-1.085130307416742</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.654960453912385</v>
+        <v>-2.676650140389822</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.585767917767346</v>
+        <v>1.572754105880884</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.72382760052724</v>
+        <v>-10.53421652670684</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.110004129853808</v>
+        <v>-1.034159700325647</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.654960453912385</v>
+        <v>-2.676650140389822</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.586907062323405</v>
+        <v>1.573893250436943</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.77672288857153</v>
+        <v>-10.58711181475112</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.128528470909415</v>
+        <v>-1.052684041381253</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.650005107823938</v>
+        <v>-2.671694794301376</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.592514044138581</v>
+        <v>1.579500232252118</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.70458971328365</v>
+        <v>-10.51497863946324</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.093941496555626</v>
+        <v>-1.018097067027464</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.650005107823938</v>
+        <v>-2.671694794301376</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.598247748377217</v>
+        <v>1.585233936490755</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.633223320674</v>
+        <v>-10.4436122468536</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.075132201905632</v>
+        <v>-0.9992877723774711</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.578638715214291</v>
+        <v>-2.600328401691728</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.631330321549141</v>
+        <v>1.618316509662678</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.36938645346993</v>
+        <v>-10.17977537964953</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9794809363369121</v>
+        <v>-0.9036365068087506</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.578638715214291</v>
+        <v>-2.600328401691728</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.621446840236233</v>
+        <v>1.608433028349771</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.10214465260153</v>
+        <v>-9.912533578781128</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8744187764889264</v>
+        <v>-0.7985743469607649</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.578638715214291</v>
+        <v>-2.600328401691728</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.619612279736859</v>
+        <v>1.606598467850397</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.00423761392504</v>
+        <v>-9.814626540104637</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8355562759917912</v>
+        <v>-0.7597118464636297</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.510652965353734</v>
+        <v>-2.532342651831171</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.660103414679732</v>
+        <v>1.64708960279327</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.980284072949082</v>
+        <v>-9.790672999128679</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8253063534559142</v>
+        <v>-0.7494619239277527</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.486699424377777</v>
+        <v>-2.508389110855214</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.6751440454108</v>
+        <v>1.662130233524338</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.716224134626286</v>
+        <v>-9.526613060805882</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7329426942885475</v>
+        <v>-0.6570982647603865</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.222639486054981</v>
+        <v>-2.244329172532418</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.820319692242726</v>
+        <v>1.807305880356264</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.009144511121448</v>
+        <v>-8.819533437301045</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4528978785469135</v>
+        <v>-0.377053449018752</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.222639486054981</v>
+        <v>-2.244329172532418</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.817532658582425</v>
+        <v>1.804518846695963</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.968960212755258</v>
+        <v>-8.779349138934855</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.436480535312596</v>
+        <v>-0.3606361057844345</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.18245518768879</v>
+        <v>-2.204144874166227</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.841986861489981</v>
+        <v>1.828973049603519</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.805560341815895</v>
+        <v>-8.615949267995493</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3717537657160936</v>
+        <v>-0.295909336187933</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.019055316749427</v>
+        <v>-2.040745003226864</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.939393605274355</v>
+        <v>1.926379793387893</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.572079119586295</v>
+        <v>-8.382468045765894</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2704368479864017</v>
+        <v>-0.194592418458241</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.785574094519829</v>
+        <v>-1.807263780997266</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.087406767449967</v>
+        <v>2.074392955563504</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.422412728578781</v>
+        <v>-8.232801654758379</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.213462501896355</v>
+        <v>-0.1376180723681943</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.692670603277293</v>
+        <v>-1.71436028975473</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.140256651882529</v>
+        <v>2.127242839996067</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.290137254947894</v>
+        <v>-8.100526181127492</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.165184825696973</v>
+        <v>-0.0893403961688124</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.560395129646406</v>
+        <v>-1.582084816123843</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.214989422808088</v>
+        <v>2.201975610921626</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.09953758027474</v>
+        <v>-7.909926506454339</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.08612989514007507</v>
+        <v>-0.0102854656119149</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.369795454973253</v>
+        <v>-1.39148514145069</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.332164288299617</v>
+        <v>2.319150476413154</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.850537781591159</v>
+        <v>-7.660926707770758</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.02637636555701617</v>
+        <v>0.1022207950851763</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.369795454973253</v>
+        <v>-1.39148514145069</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.345070629523275</v>
+        <v>2.332056817636813</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.956127771364264</v>
+        <v>-7.766516697543863</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1438355599514445</v>
+        <v>-0.06799113042328386</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.475385444746358</v>
+        <v>-1.497075131223795</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.153740706060194</v>
+        <v>2.140726894173732</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.97486267348286</v>
+        <v>-7.78525159966246</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1027851789217968</v>
+        <v>-0.02694074939363666</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.480981454406489</v>
+        <v>-1.502671140883926</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.198927442141202</v>
+        <v>2.185913630254739</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710807</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>3.029055233936926</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.826922632075261</v>
+        <v>-7.637311558254861</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1634880850469247</v>
+        <v>-0.02622581367876586</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.460660538497931</v>
+        <v>-1.482350224975368</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.091241068998169</v>
+        <v>2.139645098951705</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409201</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>3.020341247683448</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.773953109821273</v>
+        <v>-7.584342036000872</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1510142623988076</v>
+        <v>-0.01375199103064828</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.407691016243942</v>
+        <v>-1.429380702721379</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.114308796097084</v>
+        <v>2.16271282605062</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098105</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>3.013380635588355</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.730404703050582</v>
+        <v>-7.540793629230182</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1405555117856245</v>
+        <v>-0.00329324041746526</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.407691016243942</v>
+        <v>-1.429380702721379</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.107348184001991</v>
+        <v>2.155752213955527</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493416</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>3.027842989969498</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.488256309596724</v>
+        <v>-7.298645235776323</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.02923380002293818</v>
+        <v>0.1080284713452211</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.407691016243942</v>
+        <v>-1.429380702721379</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.121810538383134</v>
+        <v>2.17021456833667</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722812</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>3.022375110428693</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.379997172474202</v>
+        <v>-7.190386098653802</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.008601975285265517</v>
+        <v>0.1458642466534248</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.407691016243942</v>
+        <v>-1.429380702721379</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.116342658842329</v>
+        <v>2.164746688795865</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792042</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>3.01987320443927</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.256706037657072</v>
+        <v>-7.067094963836671</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.05541652322269508</v>
+        <v>0.1926787945908539</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.284399881426812</v>
+        <v>-1.306089567904249</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.187815433743184</v>
+        <v>2.23621946369672</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919903</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>3.027574182676595</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.235556838753628</v>
+        <v>-7.045945764933228</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.07157718102139743</v>
+        <v>0.2088394523895567</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.263250682523369</v>
+        <v>-1.284940369000806</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.208205931322575</v>
+        <v>2.256609961276112</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>3.023354891023646</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.991791396770184</v>
+        <v>-6.802180322949783</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1648640661618259</v>
+        <v>0.3021263375299852</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.263250682523369</v>
+        <v>-1.284940369000806</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.203986639669626</v>
+        <v>2.252390669623163</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>3.025479204943662</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.890028576492889</v>
+        <v>-6.700417502672488</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2076935081927598</v>
+        <v>0.3449557795609191</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.25003161413094</v>
+        <v>-1.271721300608377</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.214042394625099</v>
+        <v>2.262446424578636</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279181</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>3.018221279927364</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.640178182543814</v>
+        <v>-6.450567108723414</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3003757407560919</v>
+        <v>0.4376380121242511</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.25003161413094</v>
+        <v>-1.271721300608377</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.206784469608801</v>
+        <v>2.255188499562338</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011493</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>3.021820403448013</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.464286090076381</v>
+        <v>-6.274675016255982</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3743317012637135</v>
+        <v>0.5115939726318728</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.25003161413094</v>
+        <v>-1.271721300608377</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.21038359312945</v>
+        <v>2.258787623082987</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>3.035147909502566</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.292839627053918</v>
+        <v>-6.103228553233518</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4562377925272529</v>
+        <v>0.5935000638954118</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.078585151108477</v>
+        <v>-1.100274837585914</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.326578976997482</v>
+        <v>2.374983006951019</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>3.034168387118863</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.067806627385095</v>
+        <v>-5.878195553564695</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.545271470011079</v>
+        <v>0.6825337413792378</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8535521514396539</v>
+        <v>-0.8752418379170909</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.460619254415072</v>
+        <v>2.509023284368609</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883069</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>3.038863188173181</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.004170885151161</v>
+        <v>-5.814559811330761</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5754205679589699</v>
+        <v>0.7126828393271292</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7899164092057194</v>
+        <v>-0.8116060956831563</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.50349550080975</v>
+        <v>2.551899530763287</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074777</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>3.020057446956976</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.960408703845319</v>
+        <v>-5.770797630024919</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5741196992651023</v>
+        <v>0.7113819706332611</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7899164092057194</v>
+        <v>-0.8116060956831563</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.484689759593546</v>
+        <v>2.533093789547083</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242288</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>3.021800523581854</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.719978207040459</v>
+        <v>-5.530367133220059</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6720349746119236</v>
+        <v>0.8092972459800829</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5494859124008591</v>
+        <v>-0.5711755988782961</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.630691134301339</v>
+        <v>2.679095164254876</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367679</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>3.025729837416674</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.647735638869264</v>
+        <v>-5.458124565048864</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7048613157152217</v>
+        <v>0.842123587083381</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5494859124008591</v>
+        <v>-0.5711755988782961</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.63462044813616</v>
+        <v>2.683024478089696</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>3.026408421334014</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.594737316587876</v>
+        <v>-5.405126242767476</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7267392285451169</v>
+        <v>0.8640014999132761</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4941496533989203</v>
+        <v>-0.5158393398763572</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.668500787454663</v>
+        <v>2.7169048174082</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>3.023406492554007</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.485932431108149</v>
+        <v>-5.296321357287749</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7672592539570013</v>
+        <v>0.9045215253251602</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4941496533989203</v>
+        <v>-0.5158393398763572</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.665498858674656</v>
+        <v>2.713902888628193</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>3.024985529564622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.265911633071139</v>
+        <v>-5.076300559250739</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8568466101824197</v>
+        <v>0.9941088815505785</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.35292980833094</v>
+        <v>-0.374619494808377</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.751809802726059</v>
+        <v>2.800213832679596</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>3.040879712366445</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.133043944007861</v>
+        <v>-4.943432870187461</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.925887868609554</v>
+        <v>1.063150139977713</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.35292980833094</v>
+        <v>-0.374619494808377</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.767703985527882</v>
+        <v>2.816108015481419</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>3.042025556806747</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.012870860643362</v>
+        <v>-4.823259786822963</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9751029463956553</v>
+        <v>1.112365217763814</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2327567249664411</v>
+        <v>-0.254446411443878</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.840953679986883</v>
+        <v>2.88935770994042</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>3.052113659368187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.868198715543625</v>
+        <v>-4.678587641723225</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.04305990699699</v>
+        <v>1.180322178365149</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.08808457986670365</v>
+        <v>-0.1097742663441406</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.937845069608166</v>
+        <v>2.986249099561702</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>3.038151150769612</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.928073542901317</v>
+        <v>-4.738462469080917</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.005147467455339</v>
+        <v>1.142409738823498</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1479594072243958</v>
+        <v>-0.1696490937018327</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.887957664594976</v>
+        <v>2.936361694548513</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.999133802252179</v>
+        <v>3.060551644092179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.841274045122308</v>
+        <v>-4.651662971301908</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.062267759889509</v>
+        <v>1.199530031257668</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1479594072243958</v>
+        <v>-0.1696490937018327</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.910358157917542</v>
+        <v>2.958762187871079</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>3.060624045465591</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.843743751584114</v>
+        <v>-4.654132677763714</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.061352278678199</v>
+        <v>1.198614550046358</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1504291136862019</v>
+        <v>-0.1721188001636389</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.908948735413871</v>
+        <v>2.957352765367407</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>3.071630967940293</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.912113937908124</v>
+        <v>-4.722502864087724</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.045011126623297</v>
+        <v>1.182273397991456</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.141153414649987</v>
+        <v>-0.162843101127424</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.925521077310302</v>
+        <v>2.973925107263839</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>3.062067676572184</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.020652118824258</v>
+        <v>-4.76006773963849</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9920325628887343</v>
+        <v>1.15768415640304</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.141153414649987</v>
+        <v>-0.162843101127424</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.915957785942193</v>
+        <v>2.96436181589573</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>2.886777241612571</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.051645278152963</v>
+        <v>-4.791060898967196</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8043448641976392</v>
+        <v>0.9699964577119453</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.141153414649987</v>
+        <v>-0.162843101127424</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.74066735098258</v>
+        <v>2.789071380936117</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>2.891344473604359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.876171018360495</v>
+        <v>-4.615586639174726</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8791018001064144</v>
+        <v>1.044753393620721</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.141153414649987</v>
+        <v>-0.162843101127424</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.745234582974367</v>
+        <v>2.793638612927904</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>2.867086502365566</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.987107271001744</v>
+        <v>-4.726522891815975</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8104693278111217</v>
+        <v>0.9761209213254283</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.141153414649987</v>
+        <v>-0.162843101127424</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.720976611735574</v>
+        <v>2.769380641689112</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.870217887585471</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.995389345146802</v>
+        <v>-4.734804965961033</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8102878833730038</v>
+        <v>0.9759394768873104</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1494354887950454</v>
+        <v>-0.1711251752724823</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.719138752468445</v>
+        <v>2.767542782421982</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.880390274017604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.935536725943079</v>
+        <v>-4.67495234675731</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8444013174866256</v>
+        <v>1.010052911000932</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1494354887950454</v>
+        <v>-0.1711251752724823</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.729311138900577</v>
+        <v>2.777715168854114</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.875336544591464</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.849293262916701</v>
+        <v>-4.588708883730932</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8738449732710369</v>
+        <v>1.039496566785344</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1494354887950454</v>
+        <v>-0.1711251752724823</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.724257409474438</v>
+        <v>2.772661439427975</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.867112320035989</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.894600082315681</v>
+        <v>-4.634015703129912</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8474980209559706</v>
+        <v>1.013149614470277</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1902456518042762</v>
+        <v>-0.2119353382817131</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.691547087113425</v>
+        <v>2.739951117066962</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.867664193069091</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.923633187017982</v>
+        <v>-4.663048807832213</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8364366521081517</v>
+        <v>1.002088245622458</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1902456518042762</v>
+        <v>-0.2119353382817131</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.692098960146526</v>
+        <v>2.740502990100063</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.796936884960457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.830822705567122</v>
+        <v>-4.570238326381354</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8028335365798611</v>
+        <v>0.9684851300941677</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.09743517035341681</v>
+        <v>-0.1191248568308538</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.677057940908408</v>
+        <v>2.725461970861945</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.798810360885057</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.87521217489655</v>
+        <v>-4.614627795710781</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7869512247726911</v>
+        <v>0.9526028182869977</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1418246396828445</v>
+        <v>-0.1635143261602814</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.652297735235352</v>
+        <v>2.700701765188889</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.79388606939678</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.7625409566603</v>
+        <v>-4.501956577474531</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8270954205789141</v>
+        <v>0.9927470140932206</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.02915342144659427</v>
+        <v>-0.05084310792403124</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.714976174688825</v>
+        <v>2.763380204642362</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.799377365227448</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.650163955477627</v>
+        <v>-4.389579576291858</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8775375168826505</v>
+        <v>1.043189110396957</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.02915342144659427</v>
+        <v>-0.05084310792403124</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.720467470519492</v>
+        <v>2.768871500473029</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.810874566995987</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.67794435337898</v>
+        <v>-4.417359974193211</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8779225594906486</v>
+        <v>1.043574153004955</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.05693381934794733</v>
+        <v>-0.0786235058253843</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.715296433547219</v>
+        <v>2.763700463500756</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.64923028699664</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.760945634404258</v>
+        <v>-4.50036125521849</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6830777670811903</v>
+        <v>0.8487293605954969</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.07550470387512109</v>
+        <v>-0.09719439035255806</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.542509622831568</v>
+        <v>2.590913652785106</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.769379947715846</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.86955971284759</v>
+        <v>-4.608975333661821</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7597817964230633</v>
+        <v>0.9254333899373699</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.07550470387512109</v>
+        <v>-0.09719439035255806</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.662659283550774</v>
+        <v>2.711063313504311</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.783892973818169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.956158295828692</v>
+        <v>-4.695573916642924</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7396553893329452</v>
+        <v>0.9053069828472518</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.07550470387512109</v>
+        <v>-0.09719439035255806</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.677172309653097</v>
+        <v>2.725576339606634</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.781312415160537</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.917774633270541</v>
+        <v>-4.657190254084773</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7524282956985744</v>
+        <v>0.918079889212881</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.03712104131696992</v>
+        <v>-0.05881072779440688</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.697621948530356</v>
+        <v>2.746025978483893</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.778041444005839</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.740658303235375</v>
+        <v>-4.480073924049607</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8200038565579426</v>
+        <v>0.9856554500722492</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.03712104131696992</v>
+        <v>-0.05881072779440688</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.694350977375658</v>
+        <v>2.742755007329195</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.778724835767752</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.785750548068921</v>
+        <v>-4.525166168883152</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8026503503864375</v>
+        <v>0.9683019439007441</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.09901708448635971</v>
+        <v>-0.1207067709637967</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.657896743235938</v>
+        <v>2.706300773189474</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011232</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.772511811074167</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.606375126830153</v>
+        <v>-4.345790747644385</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8681874941883589</v>
+        <v>1.033839087702666</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.05775967368435897</v>
+        <v>0.03606998720692201</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.745749773444783</v>
+        <v>2.79415380339832</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.753319266405756</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.651389340350759</v>
+        <v>-4.39080496116499</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8309892641117065</v>
+        <v>0.9966408576260131</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.02741077836975436</v>
+        <v>0.005721091892317398</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.70834789158761</v>
+        <v>2.756751921541147</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.759010828744702</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.918393850623194</v>
+        <v>-4.657809471437425</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7298790223416782</v>
+        <v>0.8955306158559848</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1669522596731942</v>
+        <v>-0.1886419461506312</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.597421631100787</v>
+        <v>2.645825661054324</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.758214750641204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.019591632060367</v>
+        <v>-4.759007252874598</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6886038316633103</v>
+        <v>0.8542554251776171</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2353610732185134</v>
+        <v>-0.2570507596959504</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.555580264870096</v>
+        <v>2.603984294823634</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.75581471219552</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.987116045889595</v>
+        <v>-4.726531666703826</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6991940276859361</v>
+        <v>0.8648456212002427</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2353610732185134</v>
+        <v>-0.2570507596959504</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.553180226424414</v>
+        <v>2.60158425637795</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.752339431403765</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.968077918182297</v>
+        <v>-4.707493538996529</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7033339979770998</v>
+        <v>0.8689855914914064</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2935446845497079</v>
+        <v>-0.3152343710271449</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.514794778833942</v>
+        <v>2.563198808787479</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.929921300342446</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.999204549332916</v>
+        <v>-4.738620170147147</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8684652144555332</v>
+        <v>1.03411680796984</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2935446845497079</v>
+        <v>-0.3152343710271449</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.692376647772622</v>
+        <v>2.740780677726159</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.930754629328579</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.013071310666834</v>
+        <v>-4.752486931481065</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8637518389080996</v>
+        <v>1.029403432422406</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3314026012835309</v>
+        <v>-0.3530922877609678</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.670495226718462</v>
+        <v>2.718899256671999</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.936763159725505</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.992897793761884</v>
+        <v>-4.772744230010023</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8778297760670053</v>
+        <v>1.027309043407749</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3314026012835309</v>
+        <v>-0.3530922877609678</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.676503757115388</v>
+        <v>2.724907787068925</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>3.015915807517527</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.845154823526881</v>
+        <v>-4.62500125977502</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.016079611953028</v>
+        <v>1.165558879293772</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1635952440486477</v>
+        <v>-0.1852849305260847</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.85634081924834</v>
+        <v>2.904744849201877</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.018709429049008</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.947169506058103</v>
+        <v>-4.727015942306242</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9780673604720207</v>
+        <v>1.127546627812764</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1635952440486477</v>
+        <v>-0.1852849305260847</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.859134440779821</v>
+        <v>2.907538470733358</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.019371777440667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.941016800005318</v>
+        <v>-4.720863236253457</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9811907912847928</v>
+        <v>1.130670058625536</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1574425379958634</v>
+        <v>-0.1791322244733004</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.86348841280315</v>
+        <v>2.911892442756686</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.018452254180777</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.95782609815582</v>
+        <v>-4.737672534403959</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9735475487647023</v>
+        <v>1.123026816105446</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1742518361463651</v>
+        <v>-0.195941522623802</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.852483310652959</v>
+        <v>2.900887340606496</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.084787807977598</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.895528099379698</v>
+        <v>-4.675374535627837</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.064802302071972</v>
+        <v>1.214281569412716</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1742518361463651</v>
+        <v>-0.195941522623802</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.91881886444978</v>
+        <v>2.967222894403317</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.793368680366996</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.69373790171454</v>
+        <v>-4.473584337962679</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8540992535274334</v>
+        <v>1.003578520868177</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.02376635602278931</v>
+        <v>0.00207666954535235</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.74621065214067</v>
+        <v>2.794614682094207</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.863658912689171</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.633847220071947</v>
+        <v>-4.413693656320086</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9483457585066459</v>
+        <v>1.097825025847389</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.08365703766538279</v>
+        <v>0.06196735118794583</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.852435293448402</v>
+        <v>2.900839323401939</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.878286648805215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.731587764696921</v>
+        <v>-4.51143420094506</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9238772767726997</v>
+        <v>1.073356544113443</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.0677677595324026</v>
+        <v>0.04607807305496564</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.857529462684657</v>
+        <v>2.905933492638194</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.876822629629886</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.90792552481985</v>
+        <v>-4.687771961067989</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8518781535481996</v>
+        <v>1.001357420888943</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1085700005905268</v>
+        <v>-0.1302596870679638</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.750262787435571</v>
+        <v>2.798666817389108</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.875314247669815</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.836379202042973</v>
+        <v>-4.616225638291112</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.878988300698879</v>
+        <v>1.028467568039622</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1085700005905268</v>
+        <v>-0.1302596870679638</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.7487544054755</v>
+        <v>2.797158435429037</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.875177115105251</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.792006070404405</v>
+        <v>-4.571852506652544</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8966004207897427</v>
+        <v>1.046079688130486</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.0641968689519582</v>
+        <v>-0.08588655542939516</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.775241151894077</v>
+        <v>2.823645181847614</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.875177115105251</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.784052100109633</v>
+        <v>-4.563898536357772</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8997820089076516</v>
+        <v>1.049261276248395</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.0641968689519582</v>
+        <v>-0.08588655542939516</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.775241151894077</v>
+        <v>2.823645181847614</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.881558872133056</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.736396369548577</v>
+        <v>-4.516242805796716</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9252260581598786</v>
+        <v>1.074705325500622</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.01654113839090254</v>
+        <v>-0.03823082486833951</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.810216347258515</v>
+        <v>2.858620377212052</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.88645124550778</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.60871205975428</v>
+        <v>-4.388558496002419</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.981192155452322</v>
+        <v>1.130671422793065</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.1111431714033939</v>
+        <v>0.08945348492595695</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.891719306509818</v>
+        <v>2.940123336463355</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.873205917983653</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.66937865015667</v>
+        <v>-4.449225086404809</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9436801917672384</v>
+        <v>1.093159459107982</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.02944485468486024</v>
+        <v>0.00775516820742328</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.82945498895457</v>
+        <v>2.877859018908107</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690025</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.877303620594281</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.624540248548271</v>
+        <v>-4.40438668479641</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9657132550212264</v>
+        <v>1.11519252236197</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.03398828762972972</v>
+        <v>0.01229860115229275</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.83627875133212</v>
+        <v>2.884682781285657</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.881464560225359</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.725298884305269</v>
+        <v>-4.505145320553408</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.929570740349505</v>
+        <v>1.079050007690249</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.0548372810972757</v>
+        <v>-0.07652696757471267</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.787144349726995</v>
+        <v>2.835548379680532</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.887344162753196</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.681096047219369</v>
+        <v>-4.460942483467508</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9531314777117024</v>
+        <v>1.102610745052446</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.01063444401137525</v>
+        <v>-0.03232413048881222</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.819545654506372</v>
+        <v>2.867949684459909</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022902</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.885754163222444</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.718075074882812</v>
+        <v>-4.497921511130951</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.936749867115573</v>
+        <v>1.086229134456316</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.02633945777995528</v>
+        <v>0.004649771302518313</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.840139996050418</v>
+        <v>2.888544026003955</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.937001928405484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.738133153747652</v>
+        <v>-4.436258007375465</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9799744007526763</v>
+        <v>1.16214230114155</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.02633945777995528</v>
+        <v>0.004649771302518313</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.891387761233458</v>
+        <v>2.939791791186995</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865367715078277</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.935442632999737</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.698202480569762</v>
+        <v>-4.396327334197575</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9943873746180856</v>
+        <v>1.176555275006959</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.06627013095784562</v>
+        <v>0.04458044448040865</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.913786869734445</v>
+        <v>2.962190899687982</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.930390861238007</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.657732133007057</v>
+        <v>-4.35585698663487</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.005523741881438</v>
+        <v>1.187691642270311</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.1067404785205506</v>
+        <v>0.08505079204311361</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.933017306510338</v>
+        <v>2.981421336463875</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842576394162109</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.947578265330712</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.592507951879852</v>
+        <v>-4.290632805507665</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.048800818425025</v>
+        <v>1.230968718813898</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1719646596477562</v>
+        <v>0.1502749731703192</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.989339219279366</v>
+        <v>3.037743249232904</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840090220639815</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.943539237629992</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.643002242236908</v>
+        <v>-4.341127095864721</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.024564074581483</v>
+        <v>1.206731974970356</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.126943922521682</v>
+        <v>0.105254236044245</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.958287749303002</v>
+        <v>3.006691779256539</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845198842749918</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.944796029961232</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.663113898271616</v>
+        <v>-4.361238751899429</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.017776204498839</v>
+        <v>1.199944104887714</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1379712675191012</v>
+        <v>0.1162815810416642</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.966160948632694</v>
+        <v>3.014564978586231</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828690479393543</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>3.105353800982443</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.760794477544263</v>
+        <v>-4.458919331172075</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.139261743810992</v>
+        <v>1.321429644199866</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.02726807217891236</v>
+        <v>0.005578385701475397</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.060296802449792</v>
+        <v>3.108700832403329</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813251854714881</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.22546671020026</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.73700290893812</v>
+        <v>-4.435127762565932</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.268891280471266</v>
+        <v>1.45105918086014</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.05105964078505465</v>
+        <v>0.02936995430761768</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.194684652831294</v>
+        <v>3.243088682784831</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.81425976175601</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.217174686214119</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.773757327499842</v>
+        <v>-4.471882181127654</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.245897489060436</v>
+        <v>1.42806538944931</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.05105964078505465</v>
+        <v>0.02936995430761768</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.186392628845153</v>
+        <v>3.23479665879869</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.215367881797899</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.769423024442794</v>
+        <v>-4.467547878070606</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.245824405867035</v>
+        <v>1.427992306255909</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2027097441042586</v>
+        <v>0.1810200576268216</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.275575886420455</v>
+        <v>3.323979916373992</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796293177717115</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.171504445684691</v>
+        <v>3.23292228752469</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.760530563049511</v>
+        <v>-4.458655416677323</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.266935796151139</v>
+        <v>1.449103696540014</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2027097441042586</v>
+        <v>0.1810200576268216</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.293130292147247</v>
+        <v>3.341534322100783</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794453975702627</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.163359493089275</v>
+        <v>3.224777334929274</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.929006680019389</v>
+        <v>-4.627131533647201</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.191400396767772</v>
+        <v>1.373568297156647</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1747619083876778</v>
+        <v>0.1530722219102408</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.268216638121882</v>
+        <v>3.316620668075419</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.834727014174043</v>
+        <v>3.846732428258855</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.167826705169634</v>
+        <v>3.229244547009633</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.975066873649149</v>
+        <v>-4.695707901312182</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.177443531396227</v>
+        <v>1.350604962171013</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1592119188395509</v>
+        <v>0.1530722219102408</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.263353856473365</v>
+        <v>3.321087880155777</v>
       </c>
     </row>
   </sheetData>
